--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -11,58 +11,22 @@
     <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -129,7 +93,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -156,12 +120,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -172,17 +130,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -190,20 +154,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -231,15 +188,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="15">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -251,14 +208,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -276,10 +233,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -290,13 +247,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -451,37 +425,37 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -490,16 +464,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -508,67 +479,78 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -580,20 +562,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -601,6 +583,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -864,190 +850,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46049.5962615741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2115,188 +2097,184 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+      <x:c r="H6" s="13">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46066.6040162037</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3364,190 +3342,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46078.2888888889</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46078.2901041667</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46089.2508680556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -154,7 +154,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -188,7 +188,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -233,10 +233,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -247,30 +247,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -452,10 +435,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -464,22 +450,19 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -546,11 +529,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -562,11 +549,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -574,8 +557,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -583,10 +570,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -852,7 +835,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46023</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -984,14 +967,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -1000,41 +981,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2015,13 +2004,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2099,7 +2089,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -2229,14 +2219,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -2245,41 +2233,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3260,13 +3256,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3476,14 +3473,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -3492,41 +3487,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4507,13 +4510,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -466,7 +466,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -502,27 +502,31 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -896,7 +900,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -952,20 +956,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -983,44 +987,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2150,7 +2154,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -2204,20 +2208,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2235,44 +2239,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3402,7 +3406,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3458,20 +3462,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3489,44 +3493,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -870,7 +870,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -940,7 +940,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -2124,7 +2124,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2192,7 +2192,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -3376,7 +3376,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3446,7 +3446,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,9 +24,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -93,7 +129,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -138,15 +174,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -161,6 +197,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -408,27 +451,24 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -450,10 +490,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -466,7 +509,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -497,36 +540,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -553,15 +580,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -872,18 +899,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -901,75 +916,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46049.5725925926</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46049.5726273148</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46049.5962615741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46049.5725925926</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46049.5726273148</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46049.5962615741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -987,44 +1014,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2126,18 +2153,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2155,73 +2170,85 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46066.6004513889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46066.6024652778</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46066.6040162037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46066.6004513889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46066.6024652778</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46066.6040162037</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2239,44 +2266,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3378,18 +3405,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3407,75 +3422,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3493,44 +3520,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -440,11 +440,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -509,7 +512,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -539,6 +542,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -849,7 +856,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46023</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -921,80 +930,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
+      <x:c r="J8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -1014,44 +1023,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2103,7 +2112,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46054</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2175,78 +2186,78 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
+      <x:c r="J8" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46066.6040162037</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -2266,44 +2277,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3355,7 +3366,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3427,80 +3440,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46078.2888888889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46078.2901041667</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
+      <x:c r="J8" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46089.2508680556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3520,44 +3533,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,9 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIV | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -101,6 +104,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>XIV | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -116,6 +122,9 @@
     <x:t>test</x:t>
   </x:si>
   <x:si>
+    <x:t>XIV | March 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-06446</x:t>
   </x:si>
   <x:si>
@@ -129,7 +138,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -169,6 +178,22 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -440,12 +465,15 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -463,56 +491,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -543,71 +571,75 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -836,40 +868,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -930,81 +962,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="G8" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="J8" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1023,44 +1055,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="22" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2092,40 +2124,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -2186,79 +2218,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="J8" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>46066.6040162037</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2277,44 +2309,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="22" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3346,40 +3378,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -3440,81 +3472,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="E8" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H8" s="13">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I8" s="13">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>46089.2508680556</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3533,44 +3565,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="22" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -66,6 +66,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -135,10 +171,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -183,7 +221,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -191,15 +229,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -207,7 +237,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -222,13 +252,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -465,20 +488,20 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -491,56 +514,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -571,75 +597,87 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -868,74 +906,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -960,7 +996,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1000,104 +1036,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I10" s="16">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L10" s="18">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="14" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="19" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="22" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2077,13 +2150,13 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2124,74 +2197,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -2216,7 +2287,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -2256,102 +2327,139 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="13" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="s"/>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="F10" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I10" s="16">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L10" s="18">
         <x:v>46066.6040162037</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="14" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="19" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="22" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="25" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3331,13 +3439,13 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3378,74 +3486,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -3470,7 +3576,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -3510,104 +3616,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="19" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H8" s="14">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L8" s="14">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="22" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
-        <x:v>24</x:v>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4587,13 +4730,13 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -66,42 +66,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -176,7 +140,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -220,7 +184,7 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -229,7 +193,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -237,7 +201,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -252,6 +216,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -496,12 +467,12 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -514,24 +485,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -550,10 +518,13 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -566,7 +537,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -597,24 +568,16 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -629,10 +592,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -657,15 +616,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -996,7 +955,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1036,138 +995,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="14">
+        <x:v>46049.5725925926</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46049.5726273148</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="K8" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46049.5962615741</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46049.5725925926</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46049.5726273148</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46049.5962615741</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
+      <x:c r="B13" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s"/>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="18" t="s"/>
+      <x:c r="F13" s="18" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="21" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="22" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2250,7 +2172,7 @@
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
       <x:c r="B4" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -2287,7 +2209,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -2327,136 +2249,99 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="F8" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
+        <x:v>46066.6004513889</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46066.6024652778</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46066.6040162037</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46066.6004513889</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46066.6024652778</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46066.6040162037</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
+      <x:c r="B13" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s"/>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="18" t="s"/>
+      <x:c r="F13" s="18" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="21" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="22" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3539,7 +3424,7 @@
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
       <x:c r="B4" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -3576,7 +3461,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -3616,138 +3501,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="F8" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
+      <x:c r="B13" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s"/>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="18" t="s"/>
+      <x:c r="F13" s="18" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="21" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="22" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -1049,50 +1049,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="16" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="16" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s"/>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="18" t="s"/>
-      <x:c r="F13" s="18" t="s"/>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="21" t="s">
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="22" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="25" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2075,10 +2075,10 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2301,50 +2301,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="16" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="16" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s"/>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="18" t="s"/>
-      <x:c r="F13" s="18" t="s"/>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="21" t="s">
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="25" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3327,10 +3327,10 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3555,50 +3555,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="16" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="16" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s"/>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="18" t="s"/>
-      <x:c r="F13" s="18" t="s"/>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="21" t="s">
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="22" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="25" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4581,10 +4581,10 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -1016,10 +1016,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="14">
-        <x:v>46049.5725925926</x:v>
+        <x:v>46049.5726010069</x:v>
       </x:c>
       <x:c r="I8" s="14">
-        <x:v>46049.5726273148</x:v>
+        <x:v>46049.5726341898</x:v>
       </x:c>
       <x:c r="J8" s="13" t="s">
         <x:v>20</x:v>
@@ -1028,7 +1028,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="14">
-        <x:v>46049.5962615741</x:v>
+        <x:v>46049.5962660532</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>21</x:v>
@@ -2268,10 +2268,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H8" s="14">
-        <x:v>46066.6004513889</x:v>
+        <x:v>46066.6004589236</x:v>
       </x:c>
       <x:c r="I8" s="14">
-        <x:v>46066.6024652778</x:v>
+        <x:v>46066.6024709375</x:v>
       </x:c>
       <x:c r="J8" s="13" t="s">
         <x:v>31</x:v>
@@ -2280,7 +2280,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L8" s="14">
-        <x:v>46066.6040162037</x:v>
+        <x:v>46066.6040195139</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>21</x:v>
@@ -3522,10 +3522,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H8" s="14">
-        <x:v>46078.2888888889</x:v>
+        <x:v>46078.2888967361</x:v>
       </x:c>
       <x:c r="I8" s="14">
-        <x:v>46078.2901041667</x:v>
+        <x:v>46078.2901145602</x:v>
       </x:c>
       <x:c r="J8" s="13" t="s">
         <x:v>31</x:v>
@@ -3534,7 +3534,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="14">
-        <x:v>46089.2508680556</x:v>
+        <x:v>46089.2508762037</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>21</x:v>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -123,6 +123,24 @@
   </x:si>
   <x:si>
     <x:t>XIV | March 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1161-496</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07584</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1160-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1159-185</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-06446</x:t>
@@ -459,7 +477,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -536,8 +554,14 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -638,6 +662,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -3503,103 +3547,201 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="28" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="28" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="H8" s="30">
+        <x:v>46106.5066742245</x:v>
+      </x:c>
+      <x:c r="I8" s="30">
+        <x:v>46106.5082381134</x:v>
+      </x:c>
+      <x:c r="J8" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="32">
+        <x:v>46106.5099302546</x:v>
+      </x:c>
+      <x:c r="M8" s="28" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G9" s="28" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H9" s="30">
+        <x:v>46105.676846794</x:v>
+      </x:c>
+      <x:c r="I9" s="30">
+        <x:v>46106.5084437037</x:v>
+      </x:c>
+      <x:c r="J9" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="32">
+        <x:v>46106.5101144792</x:v>
+      </x:c>
+      <x:c r="M9" s="28" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G10" s="28" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H10" s="30">
+        <x:v>46105.6741278125</x:v>
+      </x:c>
+      <x:c r="I10" s="30">
+        <x:v>46106.5086548727</x:v>
+      </x:c>
+      <x:c r="J10" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="32">
+        <x:v>46106.5103567593</x:v>
+      </x:c>
+      <x:c r="M10" s="28" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="30">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I11" s="30">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="s">
+      <x:c r="J11" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L11" s="32">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s"/>
+      <x:c r="D14" s="17" t="s"/>
+      <x:c r="E14" s="18" t="s"/>
+      <x:c r="F14" s="18" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
-        <x:v>24</x:v>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="22" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
-        <x:v>1</x:v>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="25" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4581,10 +4723,10 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -999,7 +999,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1039,7 +1039,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
@@ -2253,7 +2253,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -2293,7 +2293,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>27</x:v>
@@ -3505,7 +3505,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -3545,7 +3545,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="28" t="s">
         <x:v>14</x:v>
@@ -3584,7 +3584,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -3622,7 +3622,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -3660,7 +3660,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="28" t="s">
         <x:v>14</x:v>
       </x:c>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -24,12 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIV | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -104,9 +101,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>XIV | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -120,9 +114,6 @@
   </x:si>
   <x:si>
     <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIV | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-07610</x:t>
@@ -961,8 +952,8 @@
     </x:row>
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="11" t="s">
-        <x:v>1</x:v>
+      <x:c r="B4" s="11">
+        <x:v>46023</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -1002,62 +993,62 @@
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="M7" s="12" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="G8" s="13" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="14">
         <x:v>46049.5726010069</x:v>
@@ -1066,7 +1057,7 @@
         <x:v>46049.5726341898</x:v>
       </x:c>
       <x:c r="J8" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K8" s="15" t="n">
         <x:v>210</x:v>
@@ -1075,7 +1066,7 @@
         <x:v>46049.5962660532</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1095,7 +1086,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s"/>
       <x:c r="D11" s="17" t="s"/>
@@ -1104,18 +1095,18 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="20" t="s"/>
       <x:c r="D12" s="20" t="s"/>
       <x:c r="E12" s="20" t="s"/>
       <x:c r="F12" s="21" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
       <x:c r="B13" s="22" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="23" t="s"/>
       <x:c r="D13" s="23" t="s"/>
@@ -1126,7 +1117,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="25" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="26" t="s"/>
       <x:c r="D14" s="26" t="s"/>
@@ -2215,8 +2206,8 @@
     </x:row>
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="11" t="s">
-        <x:v>26</x:v>
+      <x:c r="B4" s="11">
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -2256,60 +2247,60 @@
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="M7" s="12" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="13" t="s"/>
       <x:c r="E8" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F8" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G8" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H8" s="14">
         <x:v>46066.6004589236</x:v>
@@ -2318,7 +2309,7 @@
         <x:v>46066.6024709375</x:v>
       </x:c>
       <x:c r="J8" s="13" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K8" s="15" t="n">
         <x:v>130</x:v>
@@ -2327,7 +2318,7 @@
         <x:v>46066.6040195139</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2347,7 +2338,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s"/>
       <x:c r="D11" s="17" t="s"/>
@@ -2356,18 +2347,18 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="20" t="s"/>
       <x:c r="D12" s="20" t="s"/>
       <x:c r="E12" s="20" t="s"/>
       <x:c r="F12" s="21" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
       <x:c r="B13" s="22" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="23" t="s"/>
       <x:c r="D13" s="23" t="s"/>
@@ -2378,7 +2369,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="25" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="26" t="s"/>
       <x:c r="D14" s="26" t="s"/>
@@ -3467,8 +3458,8 @@
     </x:row>
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="B4" s="11">
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -3508,62 +3499,62 @@
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="M7" s="12" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="s">
+      <x:c r="D8" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="29" t="s">
+      <x:c r="E8" s="28" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="28" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F8" s="28" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G8" s="28" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H8" s="30">
         <x:v>46106.5066742245</x:v>
@@ -3572,7 +3563,7 @@
         <x:v>46106.5082381134</x:v>
       </x:c>
       <x:c r="J8" s="29" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K8" s="31" t="n">
         <x:v>210</x:v>
@@ -3581,27 +3572,27 @@
         <x:v>46106.5099302546</x:v>
       </x:c>
       <x:c r="M8" s="28" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="s">
+      <x:c r="D9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="29" t="s">
+      <x:c r="E9" s="28" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F9" s="28" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G9" s="28" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="30">
         <x:v>46105.676846794</x:v>
@@ -3610,7 +3601,7 @@
         <x:v>46106.5084437037</x:v>
       </x:c>
       <x:c r="J9" s="29" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K9" s="31" t="n">
         <x:v>210</x:v>
@@ -3619,27 +3610,27 @@
         <x:v>46106.5101144792</x:v>
       </x:c>
       <x:c r="M9" s="28" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F10" s="28" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G10" s="28" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H10" s="30">
         <x:v>46105.6741278125</x:v>
@@ -3648,7 +3639,7 @@
         <x:v>46106.5086548727</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>210</x:v>
@@ -3657,27 +3648,27 @@
         <x:v>46106.5103567593</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H11" s="30">
         <x:v>46078.2888967361</x:v>
@@ -3686,7 +3677,7 @@
         <x:v>46078.2901145602</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
@@ -3695,14 +3686,14 @@
         <x:v>46089.2508762037</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s"/>
       <x:c r="D14" s="17" t="s"/>
@@ -3711,18 +3702,18 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
       <x:c r="B15" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="20" t="s"/>
       <x:c r="D15" s="20" t="s"/>
       <x:c r="E15" s="20" t="s"/>
       <x:c r="F15" s="21" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="22" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="23" t="s"/>
       <x:c r="D16" s="23" t="s"/>
@@ -3733,7 +3724,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
       <x:c r="B17" s="25" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="26" t="s"/>
       <x:c r="D17" s="26" t="s"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -9,6 +9,7 @@
     <x:sheet name="January 2026" sheetId="7" r:id="rId7"/>
     <x:sheet name="February 2026" sheetId="8" r:id="rId8"/>
     <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
+    <x:sheet name="April 2026" sheetId="10" r:id="rId10"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -138,6 +139,24 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1085-817</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Operator Certificate (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWARD LANCE LORILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sarphil subdivision celica, s, Baungon, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1220-376</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4732,4 +4751,1258 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
+        <x:v>46118.3222074537</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46118.3241166898</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s"/>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="18" t="s"/>
+      <x:c r="F11" s="18" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -157,6 +157,120 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08037-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1226-211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08039-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1227-973</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AASXXCXC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08041-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1229-879</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASDQWE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08042-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1230-779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08040-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1228-788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4909,113 +5023,527 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="28" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="28" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="28" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="28" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="H8" s="30">
         <x:v>46118.3222074537</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="30">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="s">
+      <x:c r="J8" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="31" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L8" s="32">
         <x:v>46118.3241166898</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M8" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G9" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H9" s="30">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I9" s="30">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J9" s="29" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="32">
+        <x:v>46118.7577859143</x:v>
+      </x:c>
+      <x:c r="M9" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G10" s="28" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H10" s="30">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I10" s="30">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J10" s="29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K10" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="32">
+        <x:v>46118.743899213</x:v>
+      </x:c>
+      <x:c r="M10" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+      <x:c r="B11" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H11" s="30">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I11" s="30">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J11" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K11" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="32">
+        <x:v>46118.4241364815</x:v>
+      </x:c>
+      <x:c r="M11" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
-        <x:v>23</x:v>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H12" s="30">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J12" s="29" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="32">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M12" s="28" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
-        <x:v>1</x:v>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H13" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J13" s="29" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="32">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M13" s="28" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D14" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F14" s="28" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H14" s="30">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I14" s="30">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J14" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="32">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M14" s="28" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D15" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F15" s="28" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H15" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J15" s="29" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="32">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M15" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D16" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F16" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H16" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L16" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M16" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D17" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F17" s="28" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H17" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J17" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K17" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L17" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M17" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D18" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F18" s="28" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H18" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K18" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L18" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M18" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D19" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F19" s="28" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H19" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J19" s="29" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M19" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s"/>
+      <x:c r="D22" s="17" t="s"/>
+      <x:c r="E22" s="18" t="s"/>
+      <x:c r="F22" s="18" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="s"/>
+      <x:c r="D23" s="20" t="s"/>
+      <x:c r="E23" s="20" t="s"/>
+      <x:c r="F23" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="s"/>
+      <x:c r="D25" s="23" t="s"/>
+      <x:c r="E25" s="23" t="s"/>
+      <x:c r="F25" s="24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5983,14 +6511,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B22:F22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -157,6 +157,24 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08044</x:t>
@@ -5080,10 +5098,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H9" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I9" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J9" s="29" t="s">
         <x:v>46</x:v>
@@ -5092,7 +5110,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M9" s="28" t="s">
         <x:v>20</x:v>
@@ -5118,10 +5136,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
         <x:v>49</x:v>
@@ -5130,7 +5148,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5156,10 +5174,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
         <x:v>52</x:v>
@@ -5168,7 +5186,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5194,10 +5212,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>55</x:v>
@@ -5206,7 +5224,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5214,10 +5232,10 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
@@ -5226,25 +5244,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H13" s="30">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J13" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5252,10 +5270,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="28" t="s">
-        <x:v>61</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D14" s="29" t="s">
         <x:v>15</x:v>
@@ -5264,25 +5282,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G14" s="28" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5290,10 +5308,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C15" s="28" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
@@ -5302,25 +5320,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G15" s="28" t="s">
+      <x:c r="H15" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J15" s="29" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I15" s="30">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5328,10 +5346,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C16" s="28" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
@@ -5340,25 +5358,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H16" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5366,10 +5384,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C17" s="28" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D17" s="29" t="s">
         <x:v>15</x:v>
@@ -5378,25 +5396,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H17" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J17" s="29" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="G17" s="28" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I17" s="30">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J17" s="29" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5404,10 +5422,10 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C18" s="28" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D18" s="29" t="s">
         <x:v>15</x:v>
@@ -5416,25 +5434,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H18" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="G18" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5442,10 +5460,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C19" s="28" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D19" s="29" t="s">
         <x:v>15</x:v>
@@ -5460,10 +5478,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>81</x:v>
@@ -5472,80 +5490,154 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="16" t="s">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="28" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D20" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F20" s="28" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H20" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I20" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J20" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K20" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M20" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="28" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D21" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F21" s="28" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H21" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J21" s="29" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K21" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M21" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="s"/>
-      <x:c r="D22" s="17" t="s"/>
-      <x:c r="E22" s="18" t="s"/>
-      <x:c r="F22" s="18" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="19" t="s">
+      <x:c r="C24" s="17" t="s"/>
+      <x:c r="D24" s="17" t="s"/>
+      <x:c r="E24" s="18" t="s"/>
+      <x:c r="F24" s="18" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C23" s="20" t="s"/>
-      <x:c r="D23" s="20" t="s"/>
-      <x:c r="E23" s="20" t="s"/>
-      <x:c r="F23" s="21" t="s">
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="20" t="s"/>
+      <x:c r="F25" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s"/>
-      <x:c r="D24" s="23" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s"/>
-      <x:c r="D25" s="23" t="s"/>
-      <x:c r="E25" s="23" t="s"/>
-      <x:c r="F25" s="24" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="22" t="s">
-        <x:v>56</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C26" s="23" t="s"/>
       <x:c r="D26" s="23" t="s"/>
       <x:c r="E26" s="23" t="s"/>
       <x:c r="F26" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="22" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="25" t="s">
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C27" s="26" t="s"/>
-      <x:c r="D27" s="26" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="27" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6515,12 +6607,12 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B24:F24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -157,6 +157,15 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08048</x:t>
@@ -5098,10 +5107,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H9" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I9" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J9" s="29" t="s">
         <x:v>46</x:v>
@@ -5110,7 +5119,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M9" s="28" t="s">
         <x:v>20</x:v>
@@ -5136,10 +5145,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
         <x:v>49</x:v>
@@ -5148,7 +5157,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5174,10 +5183,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
         <x:v>52</x:v>
@@ -5186,7 +5195,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5212,10 +5221,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>55</x:v>
@@ -5224,7 +5233,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5250,10 +5259,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>58</x:v>
@@ -5262,7 +5271,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5288,10 +5297,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>61</x:v>
@@ -5300,7 +5309,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5308,10 +5317,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="28" t="s">
-        <x:v>63</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
@@ -5320,25 +5329,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H15" s="30">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J15" s="29" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I15" s="30">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="K15" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5346,10 +5355,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="28" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
@@ -5358,25 +5367,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="H16" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5384,7 +5393,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C17" s="28" t="s">
         <x:v>70</x:v>
@@ -5402,19 +5411,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5422,10 +5431,10 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="28" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D18" s="29" t="s">
         <x:v>15</x:v>
@@ -5434,25 +5443,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G18" s="28" t="s">
+      <x:c r="H18" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5460,10 +5469,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C19" s="28" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D19" s="29" t="s">
         <x:v>15</x:v>
@@ -5472,25 +5481,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G19" s="28" t="s">
+      <x:c r="H19" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J19" s="29" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="H19" s="30">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I19" s="30">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J19" s="29" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5498,10 +5507,10 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C20" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D20" s="29" t="s">
         <x:v>15</x:v>
@@ -5510,25 +5519,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G20" s="28" t="s">
+      <x:c r="H20" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I20" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J20" s="29" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="H20" s="30">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I20" s="30">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J20" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5536,10 +5545,10 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C21" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D21" s="29" t="s">
         <x:v>15</x:v>
@@ -5548,77 +5557,104 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="28" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D22" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F22" s="28" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H22" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I22" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J22" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K22" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M22" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="16" t="s">
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="s"/>
-      <x:c r="D24" s="17" t="s"/>
-      <x:c r="E24" s="18" t="s"/>
-      <x:c r="F24" s="18" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="19" t="s">
+      <x:c r="C25" s="17" t="s"/>
+      <x:c r="D25" s="17" t="s"/>
+      <x:c r="E25" s="18" t="s"/>
+      <x:c r="F25" s="18" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C25" s="20" t="s"/>
-      <x:c r="D25" s="20" t="s"/>
-      <x:c r="E25" s="20" t="s"/>
-      <x:c r="F25" s="21" t="s">
+      <x:c r="C26" s="20" t="s"/>
+      <x:c r="D26" s="20" t="s"/>
+      <x:c r="E26" s="20" t="s"/>
+      <x:c r="F26" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C26" s="23" t="s"/>
-      <x:c r="D26" s="23" t="s"/>
-      <x:c r="E26" s="23" t="s"/>
-      <x:c r="F26" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="23" t="s"/>
       <x:c r="D27" s="23" t="s"/>
       <x:c r="E27" s="23" t="s"/>
       <x:c r="F27" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="22" t="s">
-        <x:v>62</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C28" s="23" t="s"/>
       <x:c r="D28" s="23" t="s"/>
@@ -5627,18 +5663,28 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="25" t="s">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="22" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="s"/>
+      <x:c r="D29" s="23" t="s"/>
+      <x:c r="E29" s="23" t="s"/>
+      <x:c r="F29" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B30" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6607,12 +6653,12 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B24:F24"/>
-    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -159,6 +159,126 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>Amateur Radio Station Permit to PURCHASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZXCASD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-ROXIV-08090-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1241-111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
   </x:si>
   <x:si>
@@ -168,60 +288,6 @@
     <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -279,25 +345,28 @@
     <x:t>61-4-2026-1228-788</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08045-26</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
-    <x:t>MPDP-ROXIV-08034-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1223-617</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123431</x:t>
+    <x:t>MPDP-ROXIV-08088-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1239-459</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5089,37 +5158,35 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="28" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D9" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="s"/>
       <x:c r="E9" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F9" s="28" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5290592824</x:v>
       </x:c>
       <x:c r="I9" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5300361458</x:v>
       </x:c>
       <x:c r="J9" s="29" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K9" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5304719792</x:v>
       </x:c>
       <x:c r="M9" s="28" t="s">
         <x:v>20</x:v>
@@ -5139,25 +5206,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="28" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="28" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5177,25 +5244,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5215,10 +5282,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F12" s="28" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="28" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="30">
         <x:v>46118.7562945255</x:v>
@@ -5227,7 +5294,7 @@
         <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
@@ -5253,25 +5320,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G13" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5291,25 +5358,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G14" s="28" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5329,25 +5396,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G15" s="28" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5355,10 +5422,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="28" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
@@ -5373,19 +5440,19 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5393,10 +5460,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="28" t="s">
-        <x:v>70</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D17" s="29" t="s">
         <x:v>15</x:v>
@@ -5405,25 +5472,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G17" s="28" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="H17" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5431,10 +5498,10 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="28" t="s">
-        <x:v>73</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D18" s="29" t="s">
         <x:v>15</x:v>
@@ -5443,25 +5510,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H18" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G18" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="K18" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5469,10 +5536,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="28" t="s">
-        <x:v>77</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D19" s="29" t="s">
         <x:v>15</x:v>
@@ -5481,25 +5548,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G19" s="28" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5507,10 +5574,10 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C20" s="28" t="s">
-        <x:v>81</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D20" s="29" t="s">
         <x:v>15</x:v>
@@ -5519,25 +5586,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G20" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5545,10 +5612,10 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="28" t="s">
-        <x:v>85</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D21" s="29" t="s">
         <x:v>15</x:v>
@@ -5557,25 +5624,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5583,10 +5650,10 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C22" s="28" t="s">
-        <x:v>85</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D22" s="29" t="s">
         <x:v>15</x:v>
@@ -5595,105 +5662,411 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G22" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D23" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E23" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F23" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H23" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K23" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="32">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M23" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C24" s="28" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D24" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E24" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F24" s="28" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G24" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H24" s="30">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I24" s="30">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J24" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K24" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="32">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M24" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s"/>
-      <x:c r="D25" s="17" t="s"/>
-      <x:c r="E25" s="18" t="s"/>
-      <x:c r="F25" s="18" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="19" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C26" s="20" t="s"/>
-      <x:c r="D26" s="20" t="s"/>
-      <x:c r="E26" s="20" t="s"/>
-      <x:c r="F26" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C29" s="23" t="s"/>
-      <x:c r="D29" s="23" t="s"/>
-      <x:c r="E29" s="23" t="s"/>
-      <x:c r="F29" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
+      <x:c r="B25" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D25" s="29" t="s">
         <x:v>15</x:v>
+      </x:c>
+      <x:c r="E25" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F25" s="28" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H25" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I25" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J25" s="29" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K25" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L25" s="32">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M25" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D26" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E26" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F26" s="28" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H26" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I26" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K26" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L26" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M26" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D27" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E27" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F27" s="28" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G27" s="28" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H27" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I27" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J27" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K27" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M27" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D28" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E28" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F28" s="28" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H28" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I28" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J28" s="29" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K28" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L28" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M28" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D29" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E29" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F29" s="28" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G29" s="28" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H29" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I29" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J29" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K29" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L29" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M29" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C30" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D30" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E30" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F30" s="28" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G30" s="28" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H30" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I30" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J30" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K30" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L30" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M30" s="28" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s"/>
+      <x:c r="D33" s="17" t="s"/>
+      <x:c r="E33" s="18" t="s"/>
+      <x:c r="F33" s="18" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="s"/>
+      <x:c r="D34" s="20" t="s"/>
+      <x:c r="E34" s="20" t="s"/>
+      <x:c r="F34" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C35" s="23" t="s"/>
+      <x:c r="D35" s="23" t="s"/>
+      <x:c r="E35" s="23" t="s"/>
+      <x:c r="F35" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="22" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C36" s="23" t="s"/>
+      <x:c r="D36" s="23" t="s"/>
+      <x:c r="E36" s="23" t="s"/>
+      <x:c r="F36" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C37" s="23" t="s"/>
+      <x:c r="D37" s="23" t="s"/>
+      <x:c r="E37" s="23" t="s"/>
+      <x:c r="F37" s="24" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="22" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C38" s="23" t="s"/>
+      <x:c r="D38" s="23" t="s"/>
+      <x:c r="E38" s="23" t="s"/>
+      <x:c r="F38" s="24" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C39" s="26" t="s"/>
+      <x:c r="D39" s="26" t="s"/>
+      <x:c r="E39" s="26" t="s"/>
+      <x:c r="F39" s="27" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6649,16 +7022,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B25:F25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B33:F33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -201,6 +201,15 @@
     <x:t>zxcasdqweq2</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -210,13 +219,19 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08048</x:t>
@@ -228,6 +243,42 @@
     <x:t>123wezxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
   </x:si>
   <x:si>
@@ -237,10 +288,28 @@
     <x:t>zczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
@@ -250,42 +319,6 @@
   </x:si>
   <x:si>
     <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5326,10 +5359,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>60</x:v>
@@ -5338,7 +5371,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5364,10 +5397,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>63</x:v>
@@ -5376,7 +5409,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5402,10 +5435,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
         <x:v>66</x:v>
@@ -5414,7 +5447,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5440,19 +5473,19 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5472,25 +5505,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G17" s="28" t="s">
+      <x:c r="H17" s="30">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J17" s="29" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I17" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J17" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5516,10 +5549,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>74</x:v>
@@ -5528,7 +5561,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5668,10 +5701,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
         <x:v>86</x:v>
@@ -5680,7 +5713,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5688,10 +5721,10 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C23" s="28" t="s">
-        <x:v>88</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D23" s="29" t="s">
         <x:v>15</x:v>
@@ -5700,25 +5733,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H23" s="30">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I23" s="30">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="K23" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5726,10 +5759,10 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C24" s="28" t="s">
-        <x:v>92</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D24" s="29" t="s">
         <x:v>15</x:v>
@@ -5738,25 +5771,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G24" s="28" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5764,10 +5797,10 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C25" s="28" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D25" s="29" t="s">
         <x:v>15</x:v>
@@ -5776,25 +5809,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="28" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5802,10 +5835,10 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C26" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D26" s="29" t="s">
         <x:v>15</x:v>
@@ -5814,25 +5847,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G26" s="28" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5840,10 +5873,10 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C27" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D27" s="29" t="s">
         <x:v>15</x:v>
@@ -5852,25 +5885,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G27" s="28" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -5878,10 +5911,10 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C28" s="28" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D28" s="29" t="s">
         <x:v>15</x:v>
@@ -5890,25 +5923,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G28" s="28" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>109</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -5916,7 +5949,7 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C29" s="28" t="s">
         <x:v>106</x:v>
@@ -5928,25 +5961,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G29" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -5954,10 +5987,10 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C30" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D30" s="29" t="s">
         <x:v>15</x:v>
@@ -5966,111 +5999,259 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G30" s="28" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G30" s="28" t="s">
+      <x:c r="H30" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I30" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J30" s="29" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="H30" s="30">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I30" s="30">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J30" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="28" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C31" s="28" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D31" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E31" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F31" s="28" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G31" s="28" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H31" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I31" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J31" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K31" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L31" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M31" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="28" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C32" s="28" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D32" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E32" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F32" s="28" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G32" s="28" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H32" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I32" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J32" s="29" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K32" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L32" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M32" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="16" t="s">
+      <x:c r="B33" s="28" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C33" s="28" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D33" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E33" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F33" s="28" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G33" s="28" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H33" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I33" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J33" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K33" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M33" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="28" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C34" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D34" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E34" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F34" s="28" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G34" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H34" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I34" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J34" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K34" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M34" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C33" s="17" t="s"/>
-      <x:c r="D33" s="17" t="s"/>
-      <x:c r="E33" s="18" t="s"/>
-      <x:c r="F33" s="18" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="19" t="s">
+      <x:c r="C37" s="17" t="s"/>
+      <x:c r="D37" s="17" t="s"/>
+      <x:c r="E37" s="18" t="s"/>
+      <x:c r="F37" s="18" t="s"/>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B38" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C34" s="20" t="s"/>
-      <x:c r="D34" s="20" t="s"/>
-      <x:c r="E34" s="20" t="s"/>
-      <x:c r="F34" s="21" t="s">
+      <x:c r="C38" s="20" t="s"/>
+      <x:c r="D38" s="20" t="s"/>
+      <x:c r="E38" s="20" t="s"/>
+      <x:c r="F38" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="22" t="s">
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C35" s="23" t="s"/>
-      <x:c r="D35" s="23" t="s"/>
-      <x:c r="E35" s="23" t="s"/>
-      <x:c r="F35" s="24" t="n">
+      <x:c r="C39" s="23" t="s"/>
+      <x:c r="D39" s="23" t="s"/>
+      <x:c r="E39" s="23" t="s"/>
+      <x:c r="F39" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="22" t="s">
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C36" s="23" t="s"/>
-      <x:c r="D36" s="23" t="s"/>
-      <x:c r="E36" s="23" t="s"/>
-      <x:c r="F36" s="24" t="n">
+      <x:c r="C40" s="23" t="s"/>
+      <x:c r="D40" s="23" t="s"/>
+      <x:c r="E40" s="23" t="s"/>
+      <x:c r="F40" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="22" t="s">
+    <x:row r="41" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B41" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C37" s="23" t="s"/>
-      <x:c r="D37" s="23" t="s"/>
-      <x:c r="E37" s="23" t="s"/>
-      <x:c r="F37" s="24" t="n">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="22" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C38" s="23" t="s"/>
-      <x:c r="D38" s="23" t="s"/>
-      <x:c r="E38" s="23" t="s"/>
-      <x:c r="F38" s="24" t="n">
+      <x:c r="C41" s="23" t="s"/>
+      <x:c r="D41" s="23" t="s"/>
+      <x:c r="E41" s="23" t="s"/>
+      <x:c r="F41" s="24" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B42" s="22" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C42" s="23" t="s"/>
+      <x:c r="D42" s="23" t="s"/>
+      <x:c r="E42" s="23" t="s"/>
+      <x:c r="F42" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="25" t="s">
+    <x:row r="43" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B43" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C39" s="26" t="s"/>
-      <x:c r="D39" s="26" t="s"/>
-      <x:c r="E39" s="26" t="s"/>
-      <x:c r="F39" s="27" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C43" s="26" t="s"/>
+      <x:c r="D43" s="26" t="s"/>
+      <x:c r="E43" s="26" t="s"/>
+      <x:c r="F43" s="27" t="n">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7026,13 +7207,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B33:F33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B37:F37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B42:E42"/>
+    <x:mergeCell ref="B43:E43"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -210,6 +210,15 @@
     <x:t>123qwe123qwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -219,6 +228,21 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
   </x:si>
   <x:si>
@@ -228,19 +252,46 @@
     <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
@@ -252,22 +303,13 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
@@ -279,46 +321,16 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -381,6 +393,12 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08034-26</x:t>
   </x:si>
   <x:si>
@@ -388,12 +406,6 @@
   </x:si>
   <x:si>
     <x:t>123431</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08045-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5397,10 +5409,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>63</x:v>
@@ -5409,7 +5421,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5435,10 +5447,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
         <x:v>66</x:v>
@@ -5447,7 +5459,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5511,10 +5523,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>71</x:v>
@@ -5523,7 +5535,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5549,10 +5561,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>74</x:v>
@@ -5561,7 +5573,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5587,10 +5599,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>77</x:v>
@@ -5599,7 +5611,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5625,10 +5637,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
         <x:v>80</x:v>
@@ -5637,7 +5649,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5663,10 +5675,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
         <x:v>83</x:v>
@@ -5675,7 +5687,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5701,10 +5713,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
         <x:v>86</x:v>
@@ -5713,7 +5725,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5739,19 +5751,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>89</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5771,25 +5783,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G24" s="28" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G24" s="28" t="s">
+      <x:c r="H24" s="30">
+        <x:v>46119.7297941435</x:v>
+      </x:c>
+      <x:c r="I24" s="30">
+        <x:v>46119.731450544</x:v>
+      </x:c>
+      <x:c r="J24" s="29" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H24" s="30">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I24" s="30">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J24" s="29" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5809,25 +5821,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G25" s="28" t="s">
+      <x:c r="H25" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I25" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J25" s="29" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="H25" s="30">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I25" s="30">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J25" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5853,10 +5865,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
         <x:v>97</x:v>
@@ -5865,7 +5877,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5873,10 +5885,10 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C27" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D27" s="29" t="s">
         <x:v>15</x:v>
@@ -5885,25 +5897,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G27" s="28" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
-        <x:v>102</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -5911,10 +5923,10 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C28" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D28" s="29" t="s">
         <x:v>15</x:v>
@@ -5923,25 +5935,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G28" s="28" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -5949,10 +5961,10 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C29" s="28" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D29" s="29" t="s">
         <x:v>15</x:v>
@@ -5961,25 +5973,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G29" s="28" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -5987,10 +5999,10 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C30" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D30" s="29" t="s">
         <x:v>15</x:v>
@@ -5999,25 +6011,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G30" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6025,10 +6037,10 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C31" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D31" s="29" t="s">
         <x:v>15</x:v>
@@ -6037,25 +6049,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G31" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6063,10 +6075,10 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C32" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D32" s="29" t="s">
         <x:v>15</x:v>
@@ -6075,25 +6087,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G32" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7372774306</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7373236806</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6101,10 +6113,10 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C33" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D33" s="29" t="s">
         <x:v>15</x:v>
@@ -6113,25 +6125,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6139,10 +6151,10 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C34" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D34" s="29" t="s">
         <x:v>15</x:v>
@@ -6151,109 +6163,183 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G34" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G34" s="28" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="H34" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="16" t="s">
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="28" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C35" s="28" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D35" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E35" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F35" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G35" s="28" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H35" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I35" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J35" s="29" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K35" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L35" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M35" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="28" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C36" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D36" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E36" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F36" s="28" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G36" s="28" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H36" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I36" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J36" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K36" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L36" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M36" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C37" s="17" t="s"/>
-      <x:c r="D37" s="17" t="s"/>
-      <x:c r="E37" s="18" t="s"/>
-      <x:c r="F37" s="18" t="s"/>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B38" s="19" t="s">
+      <x:c r="C39" s="17" t="s"/>
+      <x:c r="D39" s="17" t="s"/>
+      <x:c r="E39" s="18" t="s"/>
+      <x:c r="F39" s="18" t="s"/>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B40" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C38" s="20" t="s"/>
-      <x:c r="D38" s="20" t="s"/>
-      <x:c r="E38" s="20" t="s"/>
-      <x:c r="F38" s="21" t="s">
+      <x:c r="C40" s="20" t="s"/>
+      <x:c r="D40" s="20" t="s"/>
+      <x:c r="E40" s="20" t="s"/>
+      <x:c r="F40" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C39" s="23" t="s"/>
-      <x:c r="D39" s="23" t="s"/>
-      <x:c r="E39" s="23" t="s"/>
-      <x:c r="F39" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C40" s="23" t="s"/>
-      <x:c r="D40" s="23" t="s"/>
-      <x:c r="E40" s="23" t="s"/>
-      <x:c r="F40" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="18" customHeight="1">
       <x:c r="B41" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C41" s="23" t="s"/>
       <x:c r="D41" s="23" t="s"/>
       <x:c r="E41" s="23" t="s"/>
       <x:c r="F41" s="24" t="n">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="18" customHeight="1">
       <x:c r="B42" s="22" t="s">
-        <x:v>98</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C42" s="23" t="s"/>
       <x:c r="D42" s="23" t="s"/>
       <x:c r="E42" s="23" t="s"/>
       <x:c r="F42" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B43" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C43" s="23" t="s"/>
+      <x:c r="D43" s="23" t="s"/>
+      <x:c r="E43" s="23" t="s"/>
+      <x:c r="F43" s="24" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B44" s="22" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C44" s="23" t="s"/>
+      <x:c r="D44" s="23" t="s"/>
+      <x:c r="E44" s="23" t="s"/>
+      <x:c r="F44" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B43" s="25" t="s">
+    <x:row r="45" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B45" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C43" s="26" t="s"/>
-      <x:c r="D43" s="26" t="s"/>
-      <x:c r="E43" s="26" t="s"/>
-      <x:c r="F43" s="27" t="n">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C45" s="26" t="s"/>
+      <x:c r="D45" s="26" t="s"/>
+      <x:c r="E45" s="26" t="s"/>
+      <x:c r="F45" s="27" t="n">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7207,13 +7293,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B37:F37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B39:F39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
     <x:mergeCell ref="B42:E42"/>
     <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B44:E44"/>
+    <x:mergeCell ref="B45:E45"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -219,6 +219,21 @@
     <x:t>123wezxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -228,12 +243,6 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -243,13 +252,46 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08092</x:t>
@@ -261,6 +303,12 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
@@ -270,13 +318,10 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08097</x:t>
@@ -294,43 +339,25 @@
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5447,10 +5474,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
         <x:v>66</x:v>
@@ -5459,7 +5486,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5523,10 +5550,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>71</x:v>
@@ -5535,7 +5562,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5561,10 +5588,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>74</x:v>
@@ -5573,7 +5600,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5599,10 +5626,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>77</x:v>
@@ -5611,7 +5638,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5637,10 +5664,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
         <x:v>80</x:v>
@@ -5649,7 +5676,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5675,10 +5702,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
         <x:v>83</x:v>
@@ -5687,7 +5714,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5713,10 +5740,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
         <x:v>86</x:v>
@@ -5725,7 +5752,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5751,19 +5778,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5789,10 +5816,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
         <x:v>91</x:v>
@@ -5801,7 +5828,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5827,19 +5854,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5859,25 +5886,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G26" s="28" t="s">
+      <x:c r="H26" s="30">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I26" s="30">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="H26" s="30">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I26" s="30">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J26" s="29" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5897,25 +5924,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G27" s="28" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G27" s="28" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="H27" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -5935,25 +5962,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G28" s="28" t="s">
+      <x:c r="H28" s="30">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I28" s="30">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J28" s="29" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H28" s="30">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I28" s="30">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J28" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -5961,10 +5988,10 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C29" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="29" t="s">
         <x:v>15</x:v>
@@ -5973,25 +6000,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G29" s="28" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -5999,10 +6026,10 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C30" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D30" s="29" t="s">
         <x:v>15</x:v>
@@ -6011,25 +6038,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G30" s="28" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6037,10 +6064,10 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C31" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="29" t="s">
         <x:v>15</x:v>
@@ -6049,25 +6076,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G31" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6075,10 +6102,10 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C32" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D32" s="29" t="s">
         <x:v>15</x:v>
@@ -6087,25 +6114,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G32" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6113,10 +6140,10 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C33" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D33" s="29" t="s">
         <x:v>15</x:v>
@@ -6125,25 +6152,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6151,10 +6178,10 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C34" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D34" s="29" t="s">
         <x:v>15</x:v>
@@ -6163,16 +6190,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
         <x:v>29</x:v>
@@ -6181,7 +6208,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6189,10 +6216,10 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C35" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D35" s="29" t="s">
         <x:v>15</x:v>
@@ -6201,25 +6228,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6227,10 +6254,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C36" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D36" s="29" t="s">
         <x:v>15</x:v>
@@ -6239,111 +6266,259 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7372774306</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7373236806</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="28" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C37" s="28" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D37" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E37" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F37" s="28" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G37" s="28" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H37" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I37" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J37" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K37" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M37" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="28" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C38" s="28" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D38" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E38" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F38" s="28" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G38" s="28" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H38" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I38" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J38" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K38" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M38" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="16" t="s">
+      <x:c r="B39" s="28" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C39" s="28" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D39" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E39" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F39" s="28" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G39" s="28" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H39" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I39" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J39" s="29" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K39" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M39" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="28" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C40" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D40" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E40" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F40" s="28" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H40" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I40" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J40" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K40" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M40" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C39" s="17" t="s"/>
-      <x:c r="D39" s="17" t="s"/>
-      <x:c r="E39" s="18" t="s"/>
-      <x:c r="F39" s="18" t="s"/>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B40" s="19" t="s">
+      <x:c r="C43" s="17" t="s"/>
+      <x:c r="D43" s="17" t="s"/>
+      <x:c r="E43" s="18" t="s"/>
+      <x:c r="F43" s="18" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B44" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C40" s="20" t="s"/>
-      <x:c r="D40" s="20" t="s"/>
-      <x:c r="E40" s="20" t="s"/>
-      <x:c r="F40" s="21" t="s">
+      <x:c r="C44" s="20" t="s"/>
+      <x:c r="D44" s="20" t="s"/>
+      <x:c r="E44" s="20" t="s"/>
+      <x:c r="F44" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B41" s="22" t="s">
+    <x:row r="45" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B45" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C41" s="23" t="s"/>
-      <x:c r="D41" s="23" t="s"/>
-      <x:c r="E41" s="23" t="s"/>
-      <x:c r="F41" s="24" t="n">
+      <x:c r="C45" s="23" t="s"/>
+      <x:c r="D45" s="23" t="s"/>
+      <x:c r="E45" s="23" t="s"/>
+      <x:c r="F45" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B42" s="22" t="s">
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C42" s="23" t="s"/>
-      <x:c r="D42" s="23" t="s"/>
-      <x:c r="E42" s="23" t="s"/>
-      <x:c r="F42" s="24" t="n">
+      <x:c r="C46" s="23" t="s"/>
+      <x:c r="D46" s="23" t="s"/>
+      <x:c r="E46" s="23" t="s"/>
+      <x:c r="F46" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B43" s="22" t="s">
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C43" s="23" t="s"/>
-      <x:c r="D43" s="23" t="s"/>
-      <x:c r="E43" s="23" t="s"/>
-      <x:c r="F43" s="24" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B44" s="22" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C44" s="23" t="s"/>
-      <x:c r="D44" s="23" t="s"/>
-      <x:c r="E44" s="23" t="s"/>
-      <x:c r="F44" s="24" t="n">
+      <x:c r="C47" s="23" t="s"/>
+      <x:c r="D47" s="23" t="s"/>
+      <x:c r="E47" s="23" t="s"/>
+      <x:c r="F47" s="24" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="22" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C48" s="23" t="s"/>
+      <x:c r="D48" s="23" t="s"/>
+      <x:c r="E48" s="23" t="s"/>
+      <x:c r="F48" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B45" s="25" t="s">
+    <x:row r="49" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B49" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C45" s="26" t="s"/>
-      <x:c r="D45" s="26" t="s"/>
-      <x:c r="E45" s="26" t="s"/>
-      <x:c r="F45" s="27" t="n">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C49" s="26" t="s"/>
+      <x:c r="D49" s="26" t="s"/>
+      <x:c r="E49" s="26" t="s"/>
+      <x:c r="F49" s="27" t="n">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7293,13 +7468,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B39:F39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
-    <x:mergeCell ref="B42:E42"/>
-    <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B43:F43"/>
     <x:mergeCell ref="B44:E44"/>
     <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -243,6 +243,33 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -252,13 +279,19 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08120</x:t>
@@ -270,13 +303,28 @@
     <x:t>test123</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08118</x:t>
@@ -285,22 +333,31 @@
     <x:t>61-4-2026-1256-775</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
@@ -309,55 +366,13 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5588,10 +5603,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>74</x:v>
@@ -5600,7 +5615,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5626,10 +5641,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>77</x:v>
@@ -5638,7 +5653,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5664,10 +5679,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
         <x:v>80</x:v>
@@ -5676,7 +5691,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5702,10 +5717,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
         <x:v>83</x:v>
@@ -5714,7 +5729,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5740,10 +5755,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
         <x:v>86</x:v>
@@ -5752,7 +5767,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5778,19 +5793,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5816,10 +5831,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
         <x:v>91</x:v>
@@ -5828,7 +5843,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5854,19 +5869,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5886,25 +5901,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G26" s="28" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5924,10 +5939,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G27" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="30">
         <x:v>46119.8029380671</x:v>
@@ -5962,25 +5977,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G28" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6006,19 +6021,19 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6044,19 +6059,19 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6082,10 +6097,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
         <x:v>108</x:v>
@@ -6094,7 +6109,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6120,19 +6135,19 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6140,10 +6155,10 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C33" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D33" s="29" t="s">
         <x:v>15</x:v>
@@ -6152,25 +6167,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6178,10 +6193,10 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C34" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D34" s="29" t="s">
         <x:v>15</x:v>
@@ -6190,25 +6205,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6216,10 +6231,10 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C35" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D35" s="29" t="s">
         <x:v>15</x:v>
@@ -6228,25 +6243,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G35" s="28" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H35" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I35" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J35" s="29" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="G35" s="28" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H35" s="30">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I35" s="30">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J35" s="29" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6254,10 +6269,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C36" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D36" s="29" t="s">
         <x:v>15</x:v>
@@ -6266,25 +6281,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6292,10 +6307,10 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C37" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D37" s="29" t="s">
         <x:v>15</x:v>
@@ -6304,25 +6319,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6330,10 +6345,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C38" s="28" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D38" s="29" t="s">
         <x:v>15</x:v>
@@ -6342,25 +6357,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G38" s="28" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H38" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I38" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J38" s="29" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="G38" s="28" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H38" s="30">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I38" s="30">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J38" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6368,10 +6383,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C39" s="28" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D39" s="29" t="s">
         <x:v>15</x:v>
@@ -6386,19 +6401,19 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6406,10 +6421,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C40" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D40" s="29" t="s">
         <x:v>15</x:v>
@@ -6424,103 +6439,177 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="16" t="s">
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="28" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C41" s="28" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D41" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E41" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F41" s="28" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G41" s="28" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H41" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I41" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J41" s="29" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K41" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L41" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M41" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B42" s="28" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C42" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D42" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E42" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F42" s="28" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G42" s="28" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H42" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I42" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J42" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K42" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L42" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M42" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C43" s="17" t="s"/>
-      <x:c r="D43" s="17" t="s"/>
-      <x:c r="E43" s="18" t="s"/>
-      <x:c r="F43" s="18" t="s"/>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B44" s="19" t="s">
+      <x:c r="C45" s="17" t="s"/>
+      <x:c r="D45" s="17" t="s"/>
+      <x:c r="E45" s="18" t="s"/>
+      <x:c r="F45" s="18" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C44" s="20" t="s"/>
-      <x:c r="D44" s="20" t="s"/>
-      <x:c r="E44" s="20" t="s"/>
-      <x:c r="F44" s="21" t="s">
+      <x:c r="C46" s="20" t="s"/>
+      <x:c r="D46" s="20" t="s"/>
+      <x:c r="E46" s="20" t="s"/>
+      <x:c r="F46" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C45" s="23" t="s"/>
-      <x:c r="D45" s="23" t="s"/>
-      <x:c r="E45" s="23" t="s"/>
-      <x:c r="F45" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C46" s="23" t="s"/>
-      <x:c r="D46" s="23" t="s"/>
-      <x:c r="E46" s="23" t="s"/>
-      <x:c r="F46" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C47" s="23" t="s"/>
       <x:c r="D47" s="23" t="s"/>
       <x:c r="E47" s="23" t="s"/>
       <x:c r="F47" s="24" t="n">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="22" t="s">
-        <x:v>111</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C48" s="23" t="s"/>
       <x:c r="D48" s="23" t="s"/>
       <x:c r="E48" s="23" t="s"/>
       <x:c r="F48" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C49" s="23" t="s"/>
+      <x:c r="D49" s="23" t="s"/>
+      <x:c r="E49" s="23" t="s"/>
+      <x:c r="F49" s="24" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="22" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C50" s="23" t="s"/>
+      <x:c r="D50" s="23" t="s"/>
+      <x:c r="E50" s="23" t="s"/>
+      <x:c r="F50" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B49" s="25" t="s">
+    <x:row r="51" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B51" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C49" s="26" t="s"/>
-      <x:c r="D49" s="26" t="s"/>
-      <x:c r="E49" s="26" t="s"/>
-      <x:c r="F49" s="27" t="n">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C51" s="26" t="s"/>
+      <x:c r="D51" s="26" t="s"/>
+      <x:c r="E51" s="26" t="s"/>
+      <x:c r="F51" s="27" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7468,13 +7557,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B43:F43"/>
-    <x:mergeCell ref="B44:E44"/>
-    <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B45:F45"/>
     <x:mergeCell ref="B46:E46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,6 +174,12 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08033</x:t>
   </x:si>
   <x:si>
@@ -234,6 +240,15 @@
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -261,6 +276,42 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
   </x:si>
   <x:si>
@@ -270,13 +321,43 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
@@ -288,91 +369,16 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5299,19 +5305,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5331,25 +5337,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G11" s="28" t="s">
+      <x:c r="H11" s="30">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I11" s="30">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J11" s="29" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5369,25 +5375,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F12" s="28" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G12" s="28" t="s">
+      <x:c r="H12" s="30">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J12" s="29" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5407,25 +5413,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G13" s="28" t="s">
+      <x:c r="H13" s="30">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J13" s="29" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5445,25 +5451,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G14" s="28" t="s">
+      <x:c r="H14" s="30">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I14" s="30">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J14" s="29" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="H14" s="30">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I14" s="30">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J14" s="29" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5483,25 +5489,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G15" s="28" t="s">
+      <x:c r="H15" s="30">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J15" s="29" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I15" s="30">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5521,25 +5527,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="H16" s="30">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5565,19 +5571,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5597,25 +5603,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G18" s="28" t="s">
+      <x:c r="H18" s="30">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5635,25 +5641,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G19" s="28" t="s">
+      <x:c r="H19" s="30">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J19" s="29" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="H19" s="30">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I19" s="30">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J19" s="29" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5673,25 +5679,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G20" s="28" t="s">
+      <x:c r="H20" s="30">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I20" s="30">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J20" s="29" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="H20" s="30">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I20" s="30">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J20" s="29" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5711,25 +5717,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G21" s="28" t="s">
+      <x:c r="H21" s="30">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J21" s="29" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5749,25 +5755,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G22" s="28" t="s">
+      <x:c r="H22" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I22" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J22" s="29" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="H22" s="30">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I22" s="30">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J22" s="29" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5787,25 +5793,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G23" s="28" t="s">
+      <x:c r="H23" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I23" s="30">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5869,10 +5875,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
         <x:v>94</x:v>
@@ -5881,7 +5887,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5907,19 +5913,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5983,19 +5989,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>97</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6021,19 +6027,19 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6065,7 +6071,7 @@
         <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
@@ -6173,19 +6179,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6205,25 +6211,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G34" s="28" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H34" s="30">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I34" s="30">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J34" s="29" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="G34" s="28" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H34" s="30">
-        <x:v>46121.0999663542</x:v>
-      </x:c>
-      <x:c r="I34" s="30">
-        <x:v>46121.1007466204</x:v>
-      </x:c>
-      <x:c r="J34" s="29" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6231,10 +6237,10 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C35" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D35" s="29" t="s">
         <x:v>15</x:v>
@@ -6243,25 +6249,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6269,10 +6275,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C36" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D36" s="29" t="s">
         <x:v>15</x:v>
@@ -6281,25 +6287,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G36" s="28" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H36" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I36" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J36" s="29" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="G36" s="28" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H36" s="30">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I36" s="30">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J36" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6307,10 +6313,10 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C37" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D37" s="29" t="s">
         <x:v>15</x:v>
@@ -6319,25 +6325,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G37" s="28" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G37" s="28" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="H37" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6345,10 +6351,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C38" s="28" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D38" s="29" t="s">
         <x:v>15</x:v>
@@ -6357,25 +6363,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G38" s="28" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H38" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I38" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J38" s="29" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="G38" s="28" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H38" s="30">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I38" s="30">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J38" s="29" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6383,10 +6389,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C39" s="28" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D39" s="29" t="s">
         <x:v>15</x:v>
@@ -6395,25 +6401,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G39" s="28" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H39" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I39" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J39" s="29" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="G39" s="28" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H39" s="30">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I39" s="30">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J39" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6421,10 +6427,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C40" s="28" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D40" s="29" t="s">
         <x:v>15</x:v>
@@ -6433,25 +6439,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G40" s="28" t="s">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="H40" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6459,10 +6465,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C41" s="28" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D41" s="29" t="s">
         <x:v>15</x:v>
@@ -6477,19 +6483,19 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6497,10 +6503,10 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C42" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D42" s="29" t="s">
         <x:v>15</x:v>
@@ -6509,66 +6515,93 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G42" s="28" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G42" s="28" t="s">
+      <x:c r="H42" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I42" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J42" s="29" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="H42" s="30">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I42" s="30">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J42" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="28" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C43" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D43" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E43" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F43" s="28" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G43" s="28" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H43" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I43" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J43" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K43" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L43" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M43" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="16" t="s">
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C45" s="17" t="s"/>
-      <x:c r="D45" s="17" t="s"/>
-      <x:c r="E45" s="18" t="s"/>
-      <x:c r="F45" s="18" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="19" t="s">
+      <x:c r="C46" s="17" t="s"/>
+      <x:c r="D46" s="17" t="s"/>
+      <x:c r="E46" s="18" t="s"/>
+      <x:c r="F46" s="18" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C46" s="20" t="s"/>
-      <x:c r="D46" s="20" t="s"/>
-      <x:c r="E46" s="20" t="s"/>
-      <x:c r="F46" s="21" t="s">
+      <x:c r="C47" s="20" t="s"/>
+      <x:c r="D47" s="20" t="s"/>
+      <x:c r="E47" s="20" t="s"/>
+      <x:c r="F47" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C47" s="23" t="s"/>
-      <x:c r="D47" s="23" t="s"/>
-      <x:c r="E47" s="23" t="s"/>
-      <x:c r="F47" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="22" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C48" s="23" t="s"/>
       <x:c r="D48" s="23" t="s"/>
@@ -6579,38 +6612,48 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C49" s="23" t="s"/>
       <x:c r="D49" s="23" t="s"/>
       <x:c r="E49" s="23" t="s"/>
       <x:c r="F49" s="24" t="n">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="22" t="s">
-        <x:v>116</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C50" s="23" t="s"/>
       <x:c r="D50" s="23" t="s"/>
       <x:c r="E50" s="23" t="s"/>
       <x:c r="F50" s="24" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="22" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C51" s="23" t="s"/>
+      <x:c r="D51" s="23" t="s"/>
+      <x:c r="E51" s="23" t="s"/>
+      <x:c r="F51" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B51" s="25" t="s">
+    <x:row r="52" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B52" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C51" s="26" t="s"/>
-      <x:c r="D51" s="26" t="s"/>
-      <x:c r="E51" s="26" t="s"/>
-      <x:c r="F51" s="27" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C52" s="26" t="s"/>
+      <x:c r="D52" s="26" t="s"/>
+      <x:c r="E52" s="26" t="s"/>
+      <x:c r="F52" s="27" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
     <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7557,13 +7600,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B46:F46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,126 +174,165 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08120</x:t>
   </x:si>
   <x:si>
@@ -312,13 +351,13 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -333,54 +372,33 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -441,19 +459,19 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08045-26</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1233-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08034-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1223-617</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123431</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5305,19 +5323,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5337,25 +5355,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5375,25 +5393,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F12" s="28" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="28" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5413,25 +5431,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G13" s="28" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5451,25 +5469,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G14" s="28" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5489,25 +5507,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G15" s="28" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5527,25 +5545,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G16" s="28" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
-        <x:v>68</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5571,19 +5589,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5603,25 +5621,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G18" s="28" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5641,25 +5659,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G19" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5679,25 +5697,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G20" s="28" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5717,25 +5735,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5755,25 +5773,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G22" s="28" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5793,25 +5811,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G23" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5837,10 +5855,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
         <x:v>91</x:v>
@@ -5849,7 +5867,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5875,19 +5893,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5907,25 +5925,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G26" s="28" t="s">
+      <x:c r="H26" s="30">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I26" s="30">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="H26" s="30">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I26" s="30">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J26" s="29" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5945,25 +5963,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G27" s="28" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G27" s="28" t="s">
+      <x:c r="H27" s="30">
+        <x:v>46119.7254171991</x:v>
+      </x:c>
+      <x:c r="I27" s="30">
+        <x:v>46119.7262936574</x:v>
+      </x:c>
+      <x:c r="J27" s="29" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="H27" s="30">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I27" s="30">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J27" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -5989,19 +6007,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6027,19 +6045,19 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6059,25 +6077,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G30" s="28" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6097,25 +6115,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G31" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6135,16 +6153,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G32" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
         <x:v>48</x:v>
@@ -6153,7 +6171,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6173,25 +6191,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6211,10 +6229,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H34" s="30">
         <x:v>46119.8017436343</x:v>
@@ -6223,7 +6241,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
@@ -6249,25 +6267,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6275,10 +6293,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C36" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D36" s="29" t="s">
         <x:v>15</x:v>
@@ -6287,25 +6305,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G36" s="28" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G36" s="28" t="s">
+      <x:c r="H36" s="30">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I36" s="30">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J36" s="29" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="H36" s="30">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I36" s="30">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J36" s="29" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="K36" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6313,10 +6331,10 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C37" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D37" s="29" t="s">
         <x:v>15</x:v>
@@ -6325,25 +6343,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6351,10 +6369,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C38" s="28" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D38" s="29" t="s">
         <x:v>15</x:v>
@@ -6363,25 +6381,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G38" s="28" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G38" s="28" t="s">
+      <x:c r="H38" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I38" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J38" s="29" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="H38" s="30">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I38" s="30">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J38" s="29" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6389,10 +6407,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C39" s="28" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D39" s="29" t="s">
         <x:v>15</x:v>
@@ -6401,25 +6419,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G39" s="28" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G39" s="28" t="s">
-        <x:v>132</x:v>
-      </x:c>
       <x:c r="H39" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6427,10 +6445,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C40" s="28" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D40" s="29" t="s">
         <x:v>15</x:v>
@@ -6439,25 +6457,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H40" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I40" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J40" s="29" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="G40" s="28" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H40" s="30">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I40" s="30">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J40" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6465,10 +6483,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C41" s="28" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D41" s="29" t="s">
         <x:v>15</x:v>
@@ -6477,25 +6495,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G41" s="28" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G41" s="28" t="s">
+      <x:c r="H41" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I41" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J41" s="29" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="H41" s="30">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I41" s="30">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J41" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6503,10 +6521,10 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C42" s="28" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D42" s="29" t="s">
         <x:v>15</x:v>
@@ -6515,25 +6533,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G42" s="28" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6541,10 +6559,10 @@
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
       <x:c r="B43" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C43" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D43" s="29" t="s">
         <x:v>15</x:v>
@@ -6553,109 +6571,183 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G43" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.439490081</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="16" t="s">
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B44" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C44" s="28" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D44" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E44" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F44" s="28" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G44" s="28" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H44" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I44" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J44" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K44" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L44" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M44" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C45" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D45" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E45" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F45" s="28" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G45" s="28" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H45" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I45" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J45" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K45" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L45" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M45" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C46" s="17" t="s"/>
-      <x:c r="D46" s="17" t="s"/>
-      <x:c r="E46" s="18" t="s"/>
-      <x:c r="F46" s="18" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="19" t="s">
+      <x:c r="C48" s="17" t="s"/>
+      <x:c r="D48" s="17" t="s"/>
+      <x:c r="E48" s="18" t="s"/>
+      <x:c r="F48" s="18" t="s"/>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B49" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C47" s="20" t="s"/>
-      <x:c r="D47" s="20" t="s"/>
-      <x:c r="E47" s="20" t="s"/>
-      <x:c r="F47" s="21" t="s">
+      <x:c r="C49" s="20" t="s"/>
+      <x:c r="D49" s="20" t="s"/>
+      <x:c r="E49" s="20" t="s"/>
+      <x:c r="F49" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C48" s="23" t="s"/>
-      <x:c r="D48" s="23" t="s"/>
-      <x:c r="E48" s="23" t="s"/>
-      <x:c r="F48" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C49" s="23" t="s"/>
-      <x:c r="D49" s="23" t="s"/>
-      <x:c r="E49" s="23" t="s"/>
-      <x:c r="F49" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C50" s="23" t="s"/>
       <x:c r="D50" s="23" t="s"/>
       <x:c r="E50" s="23" t="s"/>
       <x:c r="F50" s="24" t="n">
-        <x:v>26</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="22" t="s">
-        <x:v>118</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C51" s="23" t="s"/>
       <x:c r="D51" s="23" t="s"/>
       <x:c r="E51" s="23" t="s"/>
       <x:c r="F51" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C52" s="23" t="s"/>
+      <x:c r="D52" s="23" t="s"/>
+      <x:c r="E52" s="23" t="s"/>
+      <x:c r="F52" s="24" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="22" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C53" s="23" t="s"/>
+      <x:c r="D53" s="23" t="s"/>
+      <x:c r="E53" s="23" t="s"/>
+      <x:c r="F53" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B52" s="25" t="s">
+    <x:row r="54" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B54" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C52" s="26" t="s"/>
-      <x:c r="D52" s="26" t="s"/>
-      <x:c r="E52" s="26" t="s"/>
-      <x:c r="F52" s="27" t="n">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C54" s="26" t="s"/>
+      <x:c r="D54" s="26" t="s"/>
+      <x:c r="E54" s="26" t="s"/>
+      <x:c r="F54" s="27" t="n">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7600,13 +7692,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B46:F46"/>
-    <x:mergeCell ref="B47:E47"/>
-    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B48:F48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,6 +174,111 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08033</x:t>
   </x:si>
   <x:si>
@@ -183,91 +288,19 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08087</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
@@ -279,19 +312,61 @@
     <x:t>zczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
@@ -303,100 +378,73 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5323,10 +5371,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
         <x:v>51</x:v>
@@ -5335,7 +5383,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5361,10 +5409,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
         <x:v>54</x:v>
@@ -5373,7 +5421,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5399,10 +5447,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>57</x:v>
@@ -5411,7 +5459,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5437,10 +5485,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>60</x:v>
@@ -5449,7 +5497,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5475,10 +5523,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>63</x:v>
@@ -5487,7 +5535,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5513,19 +5561,19 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5545,25 +5593,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="H16" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5589,10 +5637,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>71</x:v>
@@ -5601,7 +5649,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5627,10 +5675,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>74</x:v>
@@ -5639,7 +5687,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5665,10 +5713,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>77</x:v>
@@ -5677,7 +5725,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5703,10 +5751,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
         <x:v>80</x:v>
@@ -5715,7 +5763,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5741,10 +5789,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
         <x:v>83</x:v>
@@ -5753,7 +5801,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5779,10 +5827,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
         <x:v>86</x:v>
@@ -5791,7 +5839,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5817,19 +5865,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5855,10 +5903,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
         <x:v>91</x:v>
@@ -5867,7 +5915,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5893,19 +5941,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5925,25 +5973,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G26" s="28" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
-        <x:v>96</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -5969,10 +6017,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
         <x:v>99</x:v>
@@ -5981,7 +6029,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6007,19 +6055,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6045,10 +6093,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
         <x:v>104</x:v>
@@ -6057,7 +6105,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6083,10 +6131,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
         <x:v>107</x:v>
@@ -6095,7 +6143,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6121,10 +6169,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
         <x:v>110</x:v>
@@ -6133,7 +6181,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6159,19 +6207,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6191,25 +6239,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6229,25 +6277,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>99</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6267,25 +6315,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6305,25 +6353,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>120</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6343,25 +6391,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6369,10 +6417,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C38" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D38" s="29" t="s">
         <x:v>15</x:v>
@@ -6381,25 +6429,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G38" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6407,10 +6455,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C39" s="28" t="s">
-        <x:v>129</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D39" s="29" t="s">
         <x:v>15</x:v>
@@ -6425,19 +6473,19 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6445,10 +6493,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C40" s="28" t="s">
-        <x:v>132</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D40" s="29" t="s">
         <x:v>15</x:v>
@@ -6457,25 +6505,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G40" s="28" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="H40" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6483,10 +6531,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C41" s="28" t="s">
-        <x:v>136</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D41" s="29" t="s">
         <x:v>15</x:v>
@@ -6495,25 +6543,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G41" s="28" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6521,10 +6569,10 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C42" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D42" s="29" t="s">
         <x:v>15</x:v>
@@ -6533,25 +6581,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="28" t="s">
-        <x:v>141</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G42" s="28" t="s">
-        <x:v>142</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6559,10 +6607,10 @@
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
       <x:c r="B43" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C43" s="28" t="s">
-        <x:v>143</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D43" s="29" t="s">
         <x:v>15</x:v>
@@ -6571,25 +6619,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G43" s="28" t="s">
-        <x:v>145</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6597,10 +6645,10 @@
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C44" s="28" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D44" s="29" t="s">
         <x:v>15</x:v>
@@ -6609,25 +6657,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="28" t="s">
-        <x:v>147</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G44" s="28" t="s">
-        <x:v>148</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -6635,10 +6683,10 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
       <x:c r="B45" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C45" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D45" s="29" t="s">
         <x:v>15</x:v>
@@ -6647,113 +6695,335 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G45" s="28" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H45" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C46" s="28" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D46" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E46" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F46" s="28" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G46" s="28" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H46" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I46" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J46" s="29" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="K46" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L46" s="32">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M46" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C47" s="28" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D47" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E47" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F47" s="28" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G47" s="28" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H47" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I47" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J47" s="29" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="K47" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L47" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M47" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="16" t="s">
+      <x:c r="B48" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C48" s="28" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D48" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E48" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F48" s="28" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G48" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H48" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I48" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J48" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K48" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L48" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M48" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B49" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C49" s="28" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D49" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E49" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F49" s="28" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G49" s="28" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H49" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I49" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J49" s="29" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K49" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L49" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M49" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C50" s="28" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D50" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E50" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F50" s="28" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G50" s="28" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H50" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I50" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J50" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K50" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L50" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M50" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="28" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C51" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D51" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E51" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F51" s="28" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G51" s="28" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H51" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I51" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J51" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K51" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L51" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M51" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C48" s="17" t="s"/>
-      <x:c r="D48" s="17" t="s"/>
-      <x:c r="E48" s="18" t="s"/>
-      <x:c r="F48" s="18" t="s"/>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B49" s="19" t="s">
+      <x:c r="C54" s="17" t="s"/>
+      <x:c r="D54" s="17" t="s"/>
+      <x:c r="E54" s="18" t="s"/>
+      <x:c r="F54" s="18" t="s"/>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B55" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C49" s="20" t="s"/>
-      <x:c r="D49" s="20" t="s"/>
-      <x:c r="E49" s="20" t="s"/>
-      <x:c r="F49" s="21" t="s">
+      <x:c r="C55" s="20" t="s"/>
+      <x:c r="D55" s="20" t="s"/>
+      <x:c r="E55" s="20" t="s"/>
+      <x:c r="F55" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="22" t="s">
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C50" s="23" t="s"/>
-      <x:c r="D50" s="23" t="s"/>
-      <x:c r="E50" s="23" t="s"/>
-      <x:c r="F50" s="24" t="n">
+      <x:c r="C56" s="23" t="s"/>
+      <x:c r="D56" s="23" t="s"/>
+      <x:c r="E56" s="23" t="s"/>
+      <x:c r="F56" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="22" t="s">
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C51" s="23" t="s"/>
-      <x:c r="D51" s="23" t="s"/>
-      <x:c r="E51" s="23" t="s"/>
-      <x:c r="F51" s="24" t="n">
+      <x:c r="C57" s="23" t="s"/>
+      <x:c r="D57" s="23" t="s"/>
+      <x:c r="E57" s="23" t="s"/>
+      <x:c r="F57" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="22" t="s">
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C52" s="23" t="s"/>
-      <x:c r="D52" s="23" t="s"/>
-      <x:c r="E52" s="23" t="s"/>
-      <x:c r="F52" s="24" t="n">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="22" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C53" s="23" t="s"/>
-      <x:c r="D53" s="23" t="s"/>
-      <x:c r="E53" s="23" t="s"/>
-      <x:c r="F53" s="24" t="n">
+      <x:c r="C58" s="23" t="s"/>
+      <x:c r="D58" s="23" t="s"/>
+      <x:c r="E58" s="23" t="s"/>
+      <x:c r="F58" s="24" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="22" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C59" s="23" t="s"/>
+      <x:c r="D59" s="23" t="s"/>
+      <x:c r="E59" s="23" t="s"/>
+      <x:c r="F59" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B54" s="25" t="s">
+    <x:row r="60" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B60" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C54" s="26" t="s"/>
-      <x:c r="D54" s="26" t="s"/>
-      <x:c r="E54" s="26" t="s"/>
-      <x:c r="F54" s="27" t="n">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C60" s="26" t="s"/>
+      <x:c r="D60" s="26" t="s"/>
+      <x:c r="E60" s="26" t="s"/>
+      <x:c r="F60" s="27" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7692,13 +7962,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B48:F48"/>
-    <x:mergeCell ref="B49:E49"/>
-    <x:mergeCell ref="B50:E50"/>
-    <x:mergeCell ref="B51:E51"/>
-    <x:mergeCell ref="B52:E52"/>
-    <x:mergeCell ref="B53:E53"/>
-    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B54:F54"/>
+    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B58:E58"/>
+    <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,22 +174,52 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
@@ -219,12 +249,6 @@
     <x:t>zdd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -234,6 +258,12 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
   </x:si>
   <x:si>
@@ -288,34 +318,88 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -327,19 +411,70 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08147</x:t>
@@ -351,24 +486,6 @@
     <x:t>zxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
   </x:si>
   <x:si>
@@ -378,73 +495,10 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -507,6 +561,12 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08034-26</x:t>
   </x:si>
   <x:si>
@@ -514,12 +574,6 @@
   </x:si>
   <x:si>
     <x:t>123431</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08045-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5371,10 +5425,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
         <x:v>51</x:v>
@@ -5383,7 +5437,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5447,10 +5501,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>57</x:v>
@@ -5459,7 +5513,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5485,19 +5539,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5517,25 +5571,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5555,25 +5609,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H15" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J15" s="29" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I15" s="30">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5593,25 +5647,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="H16" s="30">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5631,25 +5685,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G17" s="28" t="s">
+      <x:c r="H17" s="30">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J17" s="29" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I17" s="30">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J17" s="29" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5669,25 +5723,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G18" s="28" t="s">
+      <x:c r="H18" s="30">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5707,25 +5761,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G19" s="28" t="s">
+      <x:c r="H19" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J19" s="29" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="H19" s="30">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I19" s="30">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J19" s="29" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5745,25 +5799,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G20" s="28" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="H20" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5783,25 +5837,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H21" s="30">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J21" s="29" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G21" s="28" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5821,25 +5875,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H22" s="30">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I22" s="30">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J22" s="29" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="G22" s="28" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H22" s="30">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I22" s="30">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J22" s="29" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5859,25 +5913,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H23" s="30">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I23" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5897,25 +5951,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G24" s="28" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G24" s="28" t="s">
+      <x:c r="H24" s="30">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I24" s="30">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J24" s="29" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="H24" s="30">
-        <x:v>46119.729231331</x:v>
-      </x:c>
-      <x:c r="I24" s="30">
-        <x:v>46119.7316308565</x:v>
-      </x:c>
-      <x:c r="J24" s="29" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5935,25 +5989,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G25" s="28" t="s">
+      <x:c r="H25" s="30">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I25" s="30">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J25" s="29" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="H25" s="30">
-        <x:v>46119.5439653357</x:v>
-      </x:c>
-      <x:c r="I25" s="30">
-        <x:v>46119.5452984143</x:v>
-      </x:c>
-      <x:c r="J25" s="29" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -5973,25 +6027,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G26" s="28" t="s">
+      <x:c r="H26" s="30">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I26" s="30">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="H26" s="30">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I26" s="30">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J26" s="29" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6017,19 +6071,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6049,16 +6103,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G28" s="28" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="H28" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
         <x:v>48</x:v>
@@ -6067,7 +6121,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6087,25 +6141,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G29" s="28" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G29" s="28" t="s">
+      <x:c r="H29" s="30">
+        <x:v>46119.7297941435</x:v>
+      </x:c>
+      <x:c r="I29" s="30">
+        <x:v>46119.731450544</x:v>
+      </x:c>
+      <x:c r="J29" s="29" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="H29" s="30">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I29" s="30">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J29" s="29" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6125,25 +6179,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G30" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G30" s="28" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="H30" s="30">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6163,25 +6217,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G31" s="28" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H31" s="30">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I31" s="30">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J31" s="29" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="G31" s="28" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H31" s="30">
-        <x:v>46119.7297941435</x:v>
-      </x:c>
-      <x:c r="I31" s="30">
-        <x:v>46119.731450544</x:v>
-      </x:c>
-      <x:c r="J31" s="29" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6201,25 +6255,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G32" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6239,25 +6293,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6277,25 +6331,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6315,25 +6369,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6353,25 +6407,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6391,25 +6445,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6429,25 +6483,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G38" s="28" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6467,25 +6521,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
-        <x:v>130</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G39" s="28" t="s">
-        <x:v>131</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6505,25 +6559,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G40" s="28" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6543,25 +6597,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G41" s="28" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6581,25 +6635,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="28" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G42" s="28" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6619,25 +6673,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G43" s="28" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6645,10 +6699,10 @@
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C44" s="28" t="s">
-        <x:v>141</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D44" s="29" t="s">
         <x:v>15</x:v>
@@ -6657,25 +6711,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="28" t="s">
-        <x:v>142</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G44" s="28" t="s">
-        <x:v>143</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>144</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -6683,10 +6737,10 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
       <x:c r="B45" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C45" s="28" t="s">
-        <x:v>145</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D45" s="29" t="s">
         <x:v>15</x:v>
@@ -6695,25 +6749,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
-        <x:v>146</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G45" s="28" t="s">
-        <x:v>147</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H45" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -6721,10 +6775,10 @@
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
       <x:c r="B46" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C46" s="28" t="s">
-        <x:v>148</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D46" s="29" t="s">
         <x:v>15</x:v>
@@ -6733,25 +6787,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="28" t="s">
-        <x:v>149</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G46" s="28" t="s">
-        <x:v>150</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H46" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
-        <x:v>151</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -6759,10 +6813,10 @@
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
       <x:c r="B47" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C47" s="28" t="s">
-        <x:v>152</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D47" s="29" t="s">
         <x:v>15</x:v>
@@ -6771,25 +6825,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="28" t="s">
-        <x:v>153</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G47" s="28" t="s">
-        <x:v>154</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H47" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
-        <x:v>155</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -6797,10 +6851,10 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
       <x:c r="B48" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C48" s="28" t="s">
-        <x:v>156</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D48" s="29" t="s">
         <x:v>15</x:v>
@@ -6809,25 +6863,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="28" t="s">
-        <x:v>157</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G48" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H48" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I48" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -6835,10 +6889,10 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
       <x:c r="B49" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C49" s="28" t="s">
-        <x:v>159</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D49" s="29" t="s">
         <x:v>15</x:v>
@@ -6847,25 +6901,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G49" s="28" t="s">
-        <x:v>161</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H49" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I49" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J49" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -6873,10 +6927,10 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
       <x:c r="B50" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C50" s="28" t="s">
-        <x:v>159</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D50" s="29" t="s">
         <x:v>15</x:v>
@@ -6885,25 +6939,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="28" t="s">
-        <x:v>163</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G50" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H50" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I50" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -6911,10 +6965,10 @@
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
       <x:c r="B51" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C51" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="29" t="s">
         <x:v>15</x:v>
@@ -6923,115 +6977,411 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="28" t="s">
-        <x:v>165</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G51" s="28" t="s">
-        <x:v>166</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H51" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I51" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J51" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C52" s="28" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D52" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E52" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F52" s="28" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G52" s="28" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H52" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I52" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J52" s="29" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K52" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L52" s="32">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M52" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C53" s="28" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D53" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E53" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F53" s="28" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G53" s="28" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H53" s="30">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I53" s="30">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J53" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K53" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L53" s="32">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M53" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="16" t="s">
+      <x:c r="B54" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C54" s="28" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D54" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E54" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F54" s="28" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G54" s="28" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H54" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I54" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J54" s="29" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="K54" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L54" s="32">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M54" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B55" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C55" s="28" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D55" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E55" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F55" s="28" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G55" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H55" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I55" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J55" s="29" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="K55" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L55" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M55" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C56" s="28" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D56" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E56" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F56" s="28" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G56" s="28" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H56" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I56" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J56" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K56" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L56" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M56" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B57" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C57" s="28" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D57" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E57" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F57" s="28" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G57" s="28" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H57" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I57" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J57" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K57" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L57" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M57" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B58" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C58" s="28" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D58" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E58" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F58" s="28" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G58" s="28" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H58" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I58" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J58" s="29" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="K58" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L58" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M58" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B59" s="28" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C59" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D59" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E59" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F59" s="28" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G59" s="28" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H59" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I59" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J59" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K59" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L59" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M59" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B62" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C54" s="17" t="s"/>
-      <x:c r="D54" s="17" t="s"/>
-      <x:c r="E54" s="18" t="s"/>
-      <x:c r="F54" s="18" t="s"/>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B55" s="19" t="s">
+      <x:c r="C62" s="17" t="s"/>
+      <x:c r="D62" s="17" t="s"/>
+      <x:c r="E62" s="18" t="s"/>
+      <x:c r="F62" s="18" t="s"/>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B63" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C55" s="20" t="s"/>
-      <x:c r="D55" s="20" t="s"/>
-      <x:c r="E55" s="20" t="s"/>
-      <x:c r="F55" s="21" t="s">
+      <x:c r="C63" s="20" t="s"/>
+      <x:c r="D63" s="20" t="s"/>
+      <x:c r="E63" s="20" t="s"/>
+      <x:c r="F63" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="22" t="s">
+    <x:row r="64" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B64" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C56" s="23" t="s"/>
-      <x:c r="D56" s="23" t="s"/>
-      <x:c r="E56" s="23" t="s"/>
-      <x:c r="F56" s="24" t="n">
+      <x:c r="C64" s="23" t="s"/>
+      <x:c r="D64" s="23" t="s"/>
+      <x:c r="E64" s="23" t="s"/>
+      <x:c r="F64" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="22" t="s">
+    <x:row r="65" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B65" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C57" s="23" t="s"/>
-      <x:c r="D57" s="23" t="s"/>
-      <x:c r="E57" s="23" t="s"/>
-      <x:c r="F57" s="24" t="n">
+      <x:c r="C65" s="23" t="s"/>
+      <x:c r="D65" s="23" t="s"/>
+      <x:c r="E65" s="23" t="s"/>
+      <x:c r="F65" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="22" t="s">
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C58" s="23" t="s"/>
-      <x:c r="D58" s="23" t="s"/>
-      <x:c r="E58" s="23" t="s"/>
-      <x:c r="F58" s="24" t="n">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B59" s="22" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C59" s="23" t="s"/>
-      <x:c r="D59" s="23" t="s"/>
-      <x:c r="E59" s="23" t="s"/>
-      <x:c r="F59" s="24" t="n">
+      <x:c r="C66" s="23" t="s"/>
+      <x:c r="D66" s="23" t="s"/>
+      <x:c r="E66" s="23" t="s"/>
+      <x:c r="F66" s="24" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="22" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C67" s="23" t="s"/>
+      <x:c r="D67" s="23" t="s"/>
+      <x:c r="E67" s="23" t="s"/>
+      <x:c r="F67" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B60" s="25" t="s">
+    <x:row r="68" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B68" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C60" s="26" t="s"/>
-      <x:c r="D60" s="26" t="s"/>
-      <x:c r="E60" s="26" t="s"/>
-      <x:c r="F60" s="27" t="n">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C68" s="26" t="s"/>
+      <x:c r="D68" s="26" t="s"/>
+      <x:c r="E68" s="26" t="s"/>
+      <x:c r="F68" s="27" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
     <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7962,13 +8312,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B54:F54"/>
-    <x:mergeCell ref="B55:E55"/>
-    <x:mergeCell ref="B56:E56"/>
-    <x:mergeCell ref="B57:E57"/>
-    <x:mergeCell ref="B58:E58"/>
-    <x:mergeCell ref="B59:E59"/>
-    <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B62:F62"/>
+    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
+    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B68:E68"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,6 +174,30 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
@@ -183,13 +207,10 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08097</x:t>
@@ -318,10 +339,19 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -330,19 +360,55 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08173</x:t>
@@ -354,6 +420,12 @@
     <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
@@ -372,6 +444,33 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
   </x:si>
   <x:si>
@@ -381,16 +480,46 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
@@ -399,18 +528,6 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
@@ -424,81 +541,6 @@
   </x:si>
   <x:si>
     <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5425,19 +5467,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5501,19 +5543,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5533,25 +5575,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G13" s="28" t="s">
+      <x:c r="H13" s="30">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J13" s="29" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5577,10 +5619,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>51</x:v>
@@ -5589,7 +5631,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5615,10 +5657,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
         <x:v>64</x:v>
@@ -5627,7 +5669,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5653,19 +5695,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
-        <x:v>67</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5685,25 +5727,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G17" s="28" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="H17" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5723,25 +5765,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H18" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J18" s="29" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="G18" s="28" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I18" s="30">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5761,25 +5803,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="30">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J19" s="29" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="G19" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H19" s="30">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I19" s="30">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J19" s="29" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5799,25 +5841,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H20" s="30">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I20" s="30">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J20" s="29" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="G20" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H20" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I20" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J20" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5837,25 +5879,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G21" s="28" t="s">
+      <x:c r="H21" s="30">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J21" s="29" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5875,25 +5917,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G22" s="28" t="s">
+      <x:c r="H22" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I22" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J22" s="29" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="H22" s="30">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I22" s="30">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J22" s="29" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5913,25 +5955,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="H23" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5951,25 +5993,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G24" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H24" s="30">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I24" s="30">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J24" s="29" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="G24" s="28" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H24" s="30">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I24" s="30">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J24" s="29" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -5989,25 +6031,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H25" s="30">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I25" s="30">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J25" s="29" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="G25" s="28" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H25" s="30">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I25" s="30">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J25" s="29" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6027,25 +6069,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H26" s="30">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I26" s="30">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="G26" s="28" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H26" s="30">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I26" s="30">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J26" s="29" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6065,25 +6107,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G27" s="28" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H27" s="30">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I27" s="30">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J27" s="29" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="G27" s="28" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H27" s="30">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I27" s="30">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J27" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6103,25 +6145,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G28" s="28" t="s">
+      <x:c r="H28" s="30">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I28" s="30">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J28" s="29" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="H28" s="30">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I28" s="30">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J28" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6147,10 +6189,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
         <x:v>103</x:v>
@@ -6159,7 +6201,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6191,7 +6233,7 @@
         <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
@@ -6223,10 +6265,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
         <x:v>108</x:v>
@@ -6235,7 +6277,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6261,19 +6303,19 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46122.398526713</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6299,19 +6341,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6331,25 +6373,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6369,25 +6411,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6407,25 +6449,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6445,25 +6487,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6483,25 +6525,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G38" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6521,25 +6563,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G39" s="28" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6565,19 +6607,19 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6597,25 +6639,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G41" s="28" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6641,19 +6683,19 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6679,10 +6721,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
         <x:v>48</x:v>
@@ -6691,7 +6733,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6717,19 +6759,19 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -6749,16 +6791,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G45" s="28" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G45" s="28" t="s">
-        <x:v>141</x:v>
-      </x:c>
       <x:c r="H45" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
         <x:v>29</x:v>
@@ -6767,7 +6809,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -6787,25 +6829,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="28" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G46" s="28" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G46" s="28" t="s">
-        <x:v>143</x:v>
-      </x:c>
       <x:c r="H46" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -6825,25 +6867,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="28" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G47" s="28" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G47" s="28" t="s">
-        <x:v>145</x:v>
-      </x:c>
       <x:c r="H47" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -6863,25 +6905,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="28" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G48" s="28" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H48" s="30">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I48" s="30">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J48" s="29" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="G48" s="28" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H48" s="30">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I48" s="30">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J48" s="29" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -6901,25 +6943,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="28" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G49" s="28" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H49" s="30">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I49" s="30">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J49" s="29" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="G49" s="28" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H49" s="30">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I49" s="30">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J49" s="29" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -6939,25 +6981,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="28" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G50" s="28" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H50" s="30">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I50" s="30">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J50" s="29" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="G50" s="28" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H50" s="30">
-        <x:v>46121.2464636111</x:v>
-      </x:c>
-      <x:c r="I50" s="30">
-        <x:v>46121.3217277662</x:v>
-      </x:c>
-      <x:c r="J50" s="29" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -6977,25 +7019,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="28" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G51" s="28" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H51" s="30">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I51" s="30">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J51" s="29" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="G51" s="28" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H51" s="30">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I51" s="30">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J51" s="29" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
@@ -7003,10 +7045,10 @@
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
       <x:c r="B52" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C52" s="28" t="s">
-        <x:v>159</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D52" s="29" t="s">
         <x:v>15</x:v>
@@ -7015,25 +7057,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G52" s="28" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H52" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I52" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J52" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M52" s="28" t="s">
         <x:v>20</x:v>
@@ -7041,10 +7083,10 @@
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
       <x:c r="B53" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C53" s="28" t="s">
-        <x:v>163</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D53" s="29" t="s">
         <x:v>15</x:v>
@@ -7053,25 +7095,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G53" s="28" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H53" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I53" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J53" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M53" s="28" t="s">
         <x:v>20</x:v>
@@ -7079,10 +7121,10 @@
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
       <x:c r="B54" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C54" s="28" t="s">
-        <x:v>166</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D54" s="29" t="s">
         <x:v>15</x:v>
@@ -7091,25 +7133,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="28" t="s">
-        <x:v>167</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G54" s="28" t="s">
-        <x:v>168</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7117,10 +7159,10 @@
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
       <x:c r="B55" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C55" s="28" t="s">
-        <x:v>170</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D55" s="29" t="s">
         <x:v>15</x:v>
@@ -7129,25 +7171,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
-        <x:v>171</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G55" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H55" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I55" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J55" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7155,10 +7197,10 @@
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
       <x:c r="B56" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C56" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D56" s="29" t="s">
         <x:v>15</x:v>
@@ -7167,25 +7209,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G56" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H56" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7193,10 +7235,10 @@
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
       <x:c r="B57" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C57" s="28" t="s">
-        <x:v>177</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D57" s="29" t="s">
         <x:v>15</x:v>
@@ -7205,25 +7247,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
-        <x:v>178</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G57" s="28" t="s">
-        <x:v>179</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H57" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I57" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J57" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7231,10 +7273,10 @@
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
       <x:c r="B58" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s">
-        <x:v>177</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D58" s="29" t="s">
         <x:v>15</x:v>
@@ -7243,25 +7285,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="28" t="s">
-        <x:v>180</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G58" s="28" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H58" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I58" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J58" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K58" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7269,10 +7311,10 @@
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
       <x:c r="B59" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C59" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D59" s="29" t="s">
         <x:v>15</x:v>
@@ -7281,113 +7323,335 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="28" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G59" s="28" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H59" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I59" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J59" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K59" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B60" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C60" s="28" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D60" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E60" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F60" s="28" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G60" s="28" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H60" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I60" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J60" s="29" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="K60" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L60" s="32">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M60" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B61" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C61" s="28" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D61" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E61" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F61" s="28" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G61" s="28" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H61" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I61" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J61" s="29" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="K61" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L61" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M61" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="16" t="s">
+      <x:c r="B62" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C62" s="28" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D62" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E62" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F62" s="28" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G62" s="28" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H62" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I62" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J62" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K62" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L62" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M62" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B63" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C63" s="28" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D63" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E63" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F63" s="28" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G63" s="28" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H63" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I63" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J63" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K63" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L63" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M63" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B64" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C64" s="28" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D64" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E64" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F64" s="28" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G64" s="28" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H64" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I64" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J64" s="29" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K64" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L64" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M64" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B65" s="28" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C65" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D65" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E65" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F65" s="28" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G65" s="28" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H65" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I65" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J65" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K65" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L65" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M65" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B68" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C62" s="17" t="s"/>
-      <x:c r="D62" s="17" t="s"/>
-      <x:c r="E62" s="18" t="s"/>
-      <x:c r="F62" s="18" t="s"/>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B63" s="19" t="s">
+      <x:c r="C68" s="17" t="s"/>
+      <x:c r="D68" s="17" t="s"/>
+      <x:c r="E68" s="18" t="s"/>
+      <x:c r="F68" s="18" t="s"/>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B69" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C63" s="20" t="s"/>
-      <x:c r="D63" s="20" t="s"/>
-      <x:c r="E63" s="20" t="s"/>
-      <x:c r="F63" s="21" t="s">
+      <x:c r="C69" s="20" t="s"/>
+      <x:c r="D69" s="20" t="s"/>
+      <x:c r="E69" s="20" t="s"/>
+      <x:c r="F69" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B64" s="22" t="s">
+    <x:row r="70" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B70" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C64" s="23" t="s"/>
-      <x:c r="D64" s="23" t="s"/>
-      <x:c r="E64" s="23" t="s"/>
-      <x:c r="F64" s="24" t="n">
+      <x:c r="C70" s="23" t="s"/>
+      <x:c r="D70" s="23" t="s"/>
+      <x:c r="E70" s="23" t="s"/>
+      <x:c r="F70" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B65" s="22" t="s">
+    <x:row r="71" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B71" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C65" s="23" t="s"/>
-      <x:c r="D65" s="23" t="s"/>
-      <x:c r="E65" s="23" t="s"/>
-      <x:c r="F65" s="24" t="n">
+      <x:c r="C71" s="23" t="s"/>
+      <x:c r="D71" s="23" t="s"/>
+      <x:c r="E71" s="23" t="s"/>
+      <x:c r="F71" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="22" t="s">
+    <x:row r="72" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B72" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C66" s="23" t="s"/>
-      <x:c r="D66" s="23" t="s"/>
-      <x:c r="E66" s="23" t="s"/>
-      <x:c r="F66" s="24" t="n">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="22" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C67" s="23" t="s"/>
-      <x:c r="D67" s="23" t="s"/>
-      <x:c r="E67" s="23" t="s"/>
-      <x:c r="F67" s="24" t="n">
+      <x:c r="C72" s="23" t="s"/>
+      <x:c r="D72" s="23" t="s"/>
+      <x:c r="E72" s="23" t="s"/>
+      <x:c r="F72" s="24" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B73" s="22" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C73" s="23" t="s"/>
+      <x:c r="D73" s="23" t="s"/>
+      <x:c r="E73" s="23" t="s"/>
+      <x:c r="F73" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B68" s="25" t="s">
+    <x:row r="74" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B74" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C68" s="26" t="s"/>
-      <x:c r="D68" s="26" t="s"/>
-      <x:c r="E68" s="26" t="s"/>
-      <x:c r="F68" s="27" t="n">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C74" s="26" t="s"/>
+      <x:c r="D74" s="26" t="s"/>
+      <x:c r="E74" s="26" t="s"/>
+      <x:c r="F74" s="27" t="n">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8312,13 +8576,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B62:F62"/>
-    <x:mergeCell ref="B63:E63"/>
-    <x:mergeCell ref="B64:E64"/>
-    <x:mergeCell ref="B65:E65"/>
-    <x:mergeCell ref="B66:E66"/>
-    <x:mergeCell ref="B67:E67"/>
-    <x:mergeCell ref="B68:E68"/>
+    <x:mergeCell ref="B68:F68"/>
+    <x:mergeCell ref="B69:E69"/>
+    <x:mergeCell ref="B70:E70"/>
+    <x:mergeCell ref="B71:E71"/>
+    <x:mergeCell ref="B72:E72"/>
+    <x:mergeCell ref="B73:E73"/>
+    <x:mergeCell ref="B74:E74"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,6 +174,30 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
@@ -183,13 +207,10 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
@@ -339,34 +360,76 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08118</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1256-775</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08179</x:t>
@@ -384,46 +447,73 @@
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08177</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
@@ -432,10 +522,49 @@
     <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -444,103 +573,19 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5467,19 +5512,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5499,25 +5544,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G11" s="28" t="s">
+      <x:c r="H11" s="30">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I11" s="30">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J11" s="29" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5537,25 +5582,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F12" s="28" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G12" s="28" t="s">
+      <x:c r="H12" s="30">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J12" s="29" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5581,19 +5626,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5619,19 +5664,19 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5657,19 +5702,19 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5689,25 +5734,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="H16" s="30">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5733,10 +5778,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>59</x:v>
@@ -5745,7 +5790,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5771,10 +5816,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>71</x:v>
@@ -5783,7 +5828,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5809,19 +5854,19 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5841,25 +5886,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G20" s="28" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5879,25 +5924,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H21" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J21" s="29" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="G21" s="28" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5917,25 +5962,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H22" s="30">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I22" s="30">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J22" s="29" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G22" s="28" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H22" s="30">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I22" s="30">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J22" s="29" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -5955,25 +6000,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H23" s="30">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I23" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -5993,25 +6038,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G24" s="28" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G24" s="28" t="s">
+      <x:c r="H24" s="30">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I24" s="30">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J24" s="29" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="H24" s="30">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I24" s="30">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J24" s="29" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -6031,25 +6076,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G25" s="28" t="s">
+      <x:c r="H25" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I25" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J25" s="29" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="H25" s="30">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I25" s="30">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J25" s="29" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6069,25 +6114,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G26" s="28" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="H26" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6107,25 +6152,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G27" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H27" s="30">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I27" s="30">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J27" s="29" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="G27" s="28" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H27" s="30">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I27" s="30">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J27" s="29" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6145,25 +6190,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H28" s="30">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I28" s="30">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J28" s="29" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G28" s="28" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H28" s="30">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I28" s="30">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J28" s="29" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6183,25 +6228,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G29" s="28" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H29" s="30">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I29" s="30">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J29" s="29" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="G29" s="28" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H29" s="30">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I29" s="30">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J29" s="29" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6221,25 +6266,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G30" s="28" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H30" s="30">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I30" s="30">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J30" s="29" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="G30" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H30" s="30">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I30" s="30">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J30" s="29" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6259,25 +6304,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G31" s="28" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G31" s="28" t="s">
+      <x:c r="H31" s="30">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I31" s="30">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J31" s="29" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="H31" s="30">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I31" s="30">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J31" s="29" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6297,25 +6342,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G32" s="28" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G32" s="28" t="s">
+      <x:c r="H32" s="30">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I32" s="30">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J32" s="29" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="H32" s="30">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I32" s="30">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J32" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6379,19 +6424,19 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6411,25 +6456,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G35" s="28" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G35" s="28" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="H35" s="30">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6449,25 +6494,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G36" s="28" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G36" s="28" t="s">
+      <x:c r="H36" s="30">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I36" s="30">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J36" s="29" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="H36" s="30">
-        <x:v>46122.6182774306</x:v>
-      </x:c>
-      <x:c r="I36" s="30">
-        <x:v>46122.6193276968</x:v>
-      </x:c>
-      <x:c r="J36" s="29" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6493,19 +6538,19 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6525,25 +6570,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G38" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6563,25 +6608,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G39" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6601,25 +6646,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G40" s="28" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6639,16 +6684,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G41" s="28" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
         <x:v>29</x:v>
@@ -6657,7 +6702,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6677,25 +6722,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="28" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G42" s="28" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6715,25 +6760,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G43" s="28" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6753,25 +6798,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="28" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G44" s="28" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -6791,16 +6836,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G45" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H45" s="30">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
         <x:v>29</x:v>
@@ -6809,7 +6854,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -6829,25 +6874,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="28" t="s">
-        <x:v>141</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G46" s="28" t="s">
-        <x:v>142</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H46" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -6867,25 +6912,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="28" t="s">
-        <x:v>143</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G47" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H47" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -6905,25 +6950,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="28" t="s">
-        <x:v>145</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G48" s="28" t="s">
-        <x:v>146</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H48" s="30">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I48" s="30">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>147</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -6943,25 +6988,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="28" t="s">
-        <x:v>148</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G49" s="28" t="s">
-        <x:v>149</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H49" s="30">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I49" s="30">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J49" s="29" t="s">
-        <x:v>150</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -6981,25 +7026,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="28" t="s">
-        <x:v>151</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G50" s="28" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H50" s="30">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I50" s="30">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>153</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -7019,25 +7064,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="28" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G51" s="28" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H51" s="30">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I51" s="30">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J51" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
@@ -7057,25 +7102,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="28" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G52" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H52" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I52" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J52" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M52" s="28" t="s">
         <x:v>20</x:v>
@@ -7095,25 +7140,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G53" s="28" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H53" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I53" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J53" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M53" s="28" t="s">
         <x:v>20</x:v>
@@ -7133,25 +7178,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="28" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G54" s="28" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7171,25 +7216,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G55" s="28" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H55" s="30">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I55" s="30">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J55" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7209,25 +7254,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G56" s="28" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H56" s="30">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7247,25 +7292,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
-        <x:v>169</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G57" s="28" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H57" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I57" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J57" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7273,10 +7318,10 @@
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
       <x:c r="B58" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s">
-        <x:v>173</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D58" s="29" t="s">
         <x:v>15</x:v>
@@ -7285,25 +7330,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G58" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H58" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I58" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J58" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K58" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7311,10 +7356,10 @@
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
       <x:c r="B59" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C59" s="28" t="s">
-        <x:v>177</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D59" s="29" t="s">
         <x:v>15</x:v>
@@ -7323,25 +7368,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="28" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G59" s="28" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G59" s="28" t="s">
+      <x:c r="H59" s="30">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I59" s="30">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J59" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H59" s="30">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I59" s="30">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J59" s="29" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="K59" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
@@ -7349,10 +7394,10 @@
     </x:row>
     <x:row r="60" spans="1:28" ht="30" customHeight="1">
       <x:c r="B60" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C60" s="28" t="s">
-        <x:v>180</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D60" s="29" t="s">
         <x:v>15</x:v>
@@ -7361,25 +7406,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="28" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G60" s="28" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="G60" s="28" t="s">
-        <x:v>182</x:v>
-      </x:c>
       <x:c r="H60" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I60" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J60" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K60" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M60" s="28" t="s">
         <x:v>20</x:v>
@@ -7387,10 +7432,10 @@
     </x:row>
     <x:row r="61" spans="1:28" ht="30" customHeight="1">
       <x:c r="B61" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C61" s="28" t="s">
-        <x:v>184</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D61" s="29" t="s">
         <x:v>15</x:v>
@@ -7399,25 +7444,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="28" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G61" s="28" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H61" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I61" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J61" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K61" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M61" s="28" t="s">
         <x:v>20</x:v>
@@ -7425,10 +7470,10 @@
     </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
       <x:c r="B62" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C62" s="28" t="s">
-        <x:v>188</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D62" s="29" t="s">
         <x:v>15</x:v>
@@ -7437,25 +7482,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="28" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G62" s="28" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H62" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I62" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J62" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K62" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M62" s="28" t="s">
         <x:v>20</x:v>
@@ -7463,10 +7508,10 @@
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
       <x:c r="B63" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C63" s="28" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D63" s="29" t="s">
         <x:v>15</x:v>
@@ -7475,25 +7520,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="28" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G63" s="28" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H63" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I63" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J63" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K63" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L63" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M63" s="28" t="s">
         <x:v>20</x:v>
@@ -7501,10 +7546,10 @@
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
       <x:c r="B64" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C64" s="28" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D64" s="29" t="s">
         <x:v>15</x:v>
@@ -7513,25 +7558,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="28" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G64" s="28" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G64" s="28" t="s">
-        <x:v>195</x:v>
-      </x:c>
       <x:c r="H64" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I64" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J64" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K64" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L64" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M64" s="28" t="s">
         <x:v>20</x:v>
@@ -7539,10 +7584,10 @@
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
       <x:c r="B65" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C65" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D65" s="29" t="s">
         <x:v>15</x:v>
@@ -7551,112 +7596,297 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="28" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G65" s="28" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G65" s="28" t="s">
+      <x:c r="H65" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I65" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J65" s="29" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="H65" s="30">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I65" s="30">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J65" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K65" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L65" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M65" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B66" s="28" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C66" s="28" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D66" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E66" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F66" s="28" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G66" s="28" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H66" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I66" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J66" s="29" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K66" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L66" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M66" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B67" s="28" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C67" s="28" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D67" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E67" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F67" s="28" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G67" s="28" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H67" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I67" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J67" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K67" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L67" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M67" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B68" s="16" t="s">
+      <x:c r="B68" s="28" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C68" s="28" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D68" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E68" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F68" s="28" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G68" s="28" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H68" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I68" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J68" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K68" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L68" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M68" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B69" s="28" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C69" s="28" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D69" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E69" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F69" s="28" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G69" s="28" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H69" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I69" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J69" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K69" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L69" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M69" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B70" s="28" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C70" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D70" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E70" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F70" s="28" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G70" s="28" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H70" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I70" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J70" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K70" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L70" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M70" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B73" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C68" s="17" t="s"/>
-      <x:c r="D68" s="17" t="s"/>
-      <x:c r="E68" s="18" t="s"/>
-      <x:c r="F68" s="18" t="s"/>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B69" s="19" t="s">
+      <x:c r="C73" s="17" t="s"/>
+      <x:c r="D73" s="17" t="s"/>
+      <x:c r="E73" s="18" t="s"/>
+      <x:c r="F73" s="18" t="s"/>
+    </x:row>
+    <x:row r="74" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B74" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C69" s="20" t="s"/>
-      <x:c r="D69" s="20" t="s"/>
-      <x:c r="E69" s="20" t="s"/>
-      <x:c r="F69" s="21" t="s">
+      <x:c r="C74" s="20" t="s"/>
+      <x:c r="D74" s="20" t="s"/>
+      <x:c r="E74" s="20" t="s"/>
+      <x:c r="F74" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B70" s="22" t="s">
+    <x:row r="75" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B75" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C70" s="23" t="s"/>
-      <x:c r="D70" s="23" t="s"/>
-      <x:c r="E70" s="23" t="s"/>
-      <x:c r="F70" s="24" t="n">
+      <x:c r="C75" s="23" t="s"/>
+      <x:c r="D75" s="23" t="s"/>
+      <x:c r="E75" s="23" t="s"/>
+      <x:c r="F75" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B71" s="22" t="s">
+    <x:row r="76" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B76" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C71" s="23" t="s"/>
-      <x:c r="D71" s="23" t="s"/>
-      <x:c r="E71" s="23" t="s"/>
-      <x:c r="F71" s="24" t="n">
+      <x:c r="C76" s="23" t="s"/>
+      <x:c r="D76" s="23" t="s"/>
+      <x:c r="E76" s="23" t="s"/>
+      <x:c r="F76" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B72" s="22" t="s">
+    <x:row r="77" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B77" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C72" s="23" t="s"/>
-      <x:c r="D72" s="23" t="s"/>
-      <x:c r="E72" s="23" t="s"/>
-      <x:c r="F72" s="24" t="n">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B73" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C73" s="23" t="s"/>
-      <x:c r="D73" s="23" t="s"/>
-      <x:c r="E73" s="23" t="s"/>
-      <x:c r="F73" s="24" t="n">
+      <x:c r="C77" s="23" t="s"/>
+      <x:c r="D77" s="23" t="s"/>
+      <x:c r="E77" s="23" t="s"/>
+      <x:c r="F77" s="24" t="n">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B78" s="22" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C78" s="23" t="s"/>
+      <x:c r="D78" s="23" t="s"/>
+      <x:c r="E78" s="23" t="s"/>
+      <x:c r="F78" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B74" s="25" t="s">
+    <x:row r="79" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B79" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C74" s="26" t="s"/>
-      <x:c r="D74" s="26" t="s"/>
-      <x:c r="E74" s="26" t="s"/>
-      <x:c r="F74" s="27" t="n">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C79" s="26" t="s"/>
+      <x:c r="D79" s="26" t="s"/>
+      <x:c r="E79" s="26" t="s"/>
+      <x:c r="F79" s="27" t="n">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
     <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8576,13 +8806,13 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B68:F68"/>
-    <x:mergeCell ref="B69:E69"/>
-    <x:mergeCell ref="B70:E70"/>
-    <x:mergeCell ref="B71:E71"/>
-    <x:mergeCell ref="B72:E72"/>
-    <x:mergeCell ref="B73:E73"/>
+    <x:mergeCell ref="B73:F73"/>
     <x:mergeCell ref="B74:E74"/>
+    <x:mergeCell ref="B75:E75"/>
+    <x:mergeCell ref="B76:E76"/>
+    <x:mergeCell ref="B77:E77"/>
+    <x:mergeCell ref="B78:E78"/>
+    <x:mergeCell ref="B79:E79"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -174,19 +174,82 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -198,25 +261,25 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -243,54 +306,123 @@
     <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08096</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -300,94 +432,142 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -399,6 +579,48 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
   </x:si>
   <x:si>
@@ -408,13 +630,28 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08181</x:t>
@@ -426,168 +663,39 @@
     <x:t>tesg213</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08180</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -667,6 +775,51 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1239-459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permit to PURCHASE/POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAASD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIV-08193-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1304-273</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqweqaas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AASD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1305-075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ST. JOSEPH CATHEDRAL DIOCESAN SHRINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n/a E.Luna St., Brgy. Diego Silang, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NRSL-MM-0078-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1105-090</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asasdasd</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5512,19 +5665,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5550,19 +5703,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5588,19 +5741,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5620,25 +5773,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G13" s="28" t="s">
+      <x:c r="H13" s="30">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J13" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46120.2349196412</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>46120.5229746296</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5658,25 +5811,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H14" s="30">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5696,10 +5849,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="30">
         <x:v>46119.8023724884</x:v>
@@ -5734,25 +5887,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="H16" s="30">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J16" s="29" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5772,25 +5925,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G17" s="28" t="s">
+      <x:c r="H17" s="30">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J17" s="29" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
-        <x:v>46119.7297941435</x:v>
-      </x:c>
-      <x:c r="I17" s="30">
-        <x:v>46119.731450544</x:v>
-      </x:c>
-      <x:c r="J17" s="29" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5816,10 +5969,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>71</x:v>
@@ -5828,7 +5981,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -5854,19 +6007,19 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -5886,25 +6039,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G20" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>66</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -5924,25 +6077,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -5962,25 +6115,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G22" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>81</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -6000,25 +6153,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G23" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -6044,10 +6197,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
         <x:v>87</x:v>
@@ -6056,7 +6209,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -6082,19 +6235,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>90</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6114,25 +6267,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G26" s="28" t="s">
+      <x:c r="H26" s="30">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I26" s="30">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J26" s="29" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="H26" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I26" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J26" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6158,10 +6311,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
         <x:v>95</x:v>
@@ -6170,7 +6323,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6196,10 +6349,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
         <x:v>98</x:v>
@@ -6208,7 +6361,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6234,10 +6387,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
         <x:v>101</x:v>
@@ -6246,7 +6399,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6272,10 +6425,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
         <x:v>104</x:v>
@@ -6284,7 +6437,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6310,10 +6463,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
         <x:v>107</x:v>
@@ -6322,7 +6475,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6348,10 +6501,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
         <x:v>110</x:v>
@@ -6360,7 +6513,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6386,10 +6539,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
         <x:v>113</x:v>
@@ -6398,7 +6551,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6424,10 +6577,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
         <x:v>29</x:v>
@@ -6436,7 +6589,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6462,19 +6615,19 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6494,25 +6647,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6532,25 +6685,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46123.417862662</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6570,25 +6723,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G38" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46123.061368912</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6608,25 +6761,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G39" s="28" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46123.049084375</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6652,19 +6805,19 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6684,25 +6837,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G41" s="28" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G41" s="28" t="s">
+      <x:c r="H41" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I41" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J41" s="29" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="H41" s="30">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I41" s="30">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J41" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6728,19 +6881,19 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6760,25 +6913,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G43" s="28" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G43" s="28" t="s">
+      <x:c r="H43" s="30">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I43" s="30">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J43" s="29" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="H43" s="30">
-        <x:v>46122.6795081481</x:v>
-      </x:c>
-      <x:c r="I43" s="30">
-        <x:v>46122.6802186921</x:v>
-      </x:c>
-      <x:c r="J43" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6804,19 +6957,19 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -6836,25 +6989,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G45" s="28" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G45" s="28" t="s">
+      <x:c r="H45" s="30">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I45" s="30">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J45" s="29" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="H45" s="30">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I45" s="30">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J45" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -6880,10 +7033,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="H46" s="30">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
         <x:v>147</x:v>
@@ -6892,7 +7045,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -6918,19 +7071,19 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H47" s="30">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
-        <x:v>90</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -6950,25 +7103,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="28" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G48" s="28" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H48" s="30">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I48" s="30">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -6994,19 +7147,19 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H49" s="30">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I49" s="30">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J49" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -7026,25 +7179,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="28" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G50" s="28" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H50" s="30">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I50" s="30">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -7064,25 +7217,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="28" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G51" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H51" s="30">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I51" s="30">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J51" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
@@ -7102,25 +7255,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G52" s="28" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H52" s="30">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I52" s="30">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J52" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M52" s="28" t="s">
         <x:v>20</x:v>
@@ -7140,25 +7293,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="28" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G53" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H53" s="30">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I53" s="30">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J53" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="32">
-        <x:v>46122.398526713</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M53" s="28" t="s">
         <x:v>20</x:v>
@@ -7178,25 +7331,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="28" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G54" s="28" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7216,25 +7369,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G55" s="28" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H55" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I55" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J55" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7254,25 +7407,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G56" s="28" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H56" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7292,25 +7445,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G57" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H57" s="30">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I57" s="30">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J57" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7330,25 +7483,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G58" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H58" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I58" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J58" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K58" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7368,25 +7521,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="28" t="s">
-        <x:v>177</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G59" s="28" t="s">
-        <x:v>178</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H59" s="30">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I59" s="30">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J59" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K59" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
@@ -7406,25 +7559,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="28" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G60" s="28" t="s">
-        <x:v>181</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H60" s="30">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I60" s="30">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J60" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K60" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="32">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M60" s="28" t="s">
         <x:v>20</x:v>
@@ -7444,25 +7597,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="28" t="s">
-        <x:v>182</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G61" s="28" t="s">
-        <x:v>183</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H61" s="30">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I61" s="30">
-        <x:v>46122.244317963</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J61" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="K61" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M61" s="28" t="s">
         <x:v>20</x:v>
@@ -7482,25 +7635,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="28" t="s">
-        <x:v>184</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G62" s="28" t="s">
-        <x:v>185</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H62" s="30">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I62" s="30">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J62" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K62" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="32">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M62" s="28" t="s">
         <x:v>20</x:v>
@@ -7508,10 +7661,10 @@
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
       <x:c r="B63" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C63" s="28" t="s">
-        <x:v>188</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D63" s="29" t="s">
         <x:v>15</x:v>
@@ -7520,25 +7673,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="28" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G63" s="28" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H63" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I63" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J63" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K63" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M63" s="28" t="s">
         <x:v>20</x:v>
@@ -7546,10 +7699,10 @@
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
       <x:c r="B64" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C64" s="28" t="s">
-        <x:v>192</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D64" s="29" t="s">
         <x:v>15</x:v>
@@ -7558,25 +7711,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="28" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G64" s="28" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H64" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I64" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J64" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K64" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M64" s="28" t="s">
         <x:v>20</x:v>
@@ -7584,10 +7737,10 @@
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
       <x:c r="B65" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C65" s="28" t="s">
-        <x:v>195</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D65" s="29" t="s">
         <x:v>15</x:v>
@@ -7602,19 +7755,19 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="H65" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I65" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J65" s="29" t="s">
-        <x:v>198</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K65" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M65" s="28" t="s">
         <x:v>20</x:v>
@@ -7622,10 +7775,10 @@
     </x:row>
     <x:row r="66" spans="1:28" ht="30" customHeight="1">
       <x:c r="B66" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C66" s="28" t="s">
-        <x:v>199</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D66" s="29" t="s">
         <x:v>15</x:v>
@@ -7634,25 +7787,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="28" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G66" s="28" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H66" s="30">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I66" s="30">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J66" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G66" s="28" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H66" s="30">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I66" s="30">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J66" s="29" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="K66" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M66" s="28" t="s">
         <x:v>20</x:v>
@@ -7660,10 +7813,10 @@
     </x:row>
     <x:row r="67" spans="1:28" ht="30" customHeight="1">
       <x:c r="B67" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C67" s="28" t="s">
-        <x:v>203</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D67" s="29" t="s">
         <x:v>15</x:v>
@@ -7672,25 +7825,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="28" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G67" s="28" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H67" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I67" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J67" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K67" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M67" s="28" t="s">
         <x:v>20</x:v>
@@ -7698,10 +7851,10 @@
     </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
       <x:c r="B68" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C68" s="28" t="s">
-        <x:v>206</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D68" s="29" t="s">
         <x:v>15</x:v>
@@ -7710,25 +7863,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="28" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G68" s="28" t="s">
-        <x:v>208</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H68" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I68" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J68" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K68" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M68" s="28" t="s">
         <x:v>20</x:v>
@@ -7736,10 +7889,10 @@
     </x:row>
     <x:row r="69" spans="1:28" ht="30" customHeight="1">
       <x:c r="B69" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C69" s="28" t="s">
-        <x:v>206</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D69" s="29" t="s">
         <x:v>15</x:v>
@@ -7748,25 +7901,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="28" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G69" s="28" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H69" s="30">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I69" s="30">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J69" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="K69" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H69" s="30">
-        <x:v>46118.439490081</x:v>
-      </x:c>
-      <x:c r="I69" s="30">
-        <x:v>46118.4395309375</x:v>
-      </x:c>
-      <x:c r="J69" s="29" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="K69" s="31" t="n">
-        <x:v>3530</x:v>
-      </x:c>
       <x:c r="L69" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M69" s="28" t="s">
         <x:v>20</x:v>
@@ -7774,10 +7927,10 @@
     </x:row>
     <x:row r="70" spans="1:28" ht="30" customHeight="1">
       <x:c r="B70" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C70" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D70" s="29" t="s">
         <x:v>15</x:v>
@@ -7786,125 +7939,735 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="28" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G70" s="28" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H70" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I70" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J70" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K70" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M70" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B71" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C71" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D71" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E71" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F71" s="28" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G71" s="28" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H71" s="30">
+        <x:v>46122.5945434491</x:v>
+      </x:c>
+      <x:c r="I71" s="30">
+        <x:v>46122.5999534606</x:v>
+      </x:c>
+      <x:c r="J71" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K71" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L71" s="32">
+        <x:v>46122.6007489699</x:v>
+      </x:c>
+      <x:c r="M71" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B72" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C72" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D72" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E72" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F72" s="28" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G72" s="28" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H72" s="30">
+        <x:v>46122.6182774306</x:v>
+      </x:c>
+      <x:c r="I72" s="30">
+        <x:v>46122.6193276968</x:v>
+      </x:c>
+      <x:c r="J72" s="29" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K72" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L72" s="32">
+        <x:v>46122.6199813426</x:v>
+      </x:c>
+      <x:c r="M72" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="73" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B73" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C73" s="17" t="s"/>
-      <x:c r="D73" s="17" t="s"/>
-      <x:c r="E73" s="18" t="s"/>
-      <x:c r="F73" s="18" t="s"/>
-    </x:row>
-    <x:row r="74" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B74" s="19" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C74" s="20" t="s"/>
-      <x:c r="D74" s="20" t="s"/>
-      <x:c r="E74" s="20" t="s"/>
-      <x:c r="F74" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B75" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C75" s="23" t="s"/>
-      <x:c r="D75" s="23" t="s"/>
-      <x:c r="E75" s="23" t="s"/>
-      <x:c r="F75" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B76" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C76" s="23" t="s"/>
-      <x:c r="D76" s="23" t="s"/>
-      <x:c r="E76" s="23" t="s"/>
-      <x:c r="F76" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B77" s="22" t="s">
+      <x:c r="B73" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C77" s="23" t="s"/>
-      <x:c r="D77" s="23" t="s"/>
-      <x:c r="E77" s="23" t="s"/>
-      <x:c r="F77" s="24" t="n">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B78" s="22" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="C78" s="23" t="s"/>
-      <x:c r="D78" s="23" t="s"/>
-      <x:c r="E78" s="23" t="s"/>
-      <x:c r="F78" s="24" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B79" s="25" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C79" s="26" t="s"/>
-      <x:c r="D79" s="26" t="s"/>
-      <x:c r="E79" s="26" t="s"/>
-      <x:c r="F79" s="27" t="n">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C73" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D73" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E73" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F73" s="28" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G73" s="28" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H73" s="30">
+        <x:v>46122.6795081481</x:v>
+      </x:c>
+      <x:c r="I73" s="30">
+        <x:v>46122.6802186921</x:v>
+      </x:c>
+      <x:c r="J73" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K73" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L73" s="32">
+        <x:v>46122.6809879398</x:v>
+      </x:c>
+      <x:c r="M73" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B74" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C74" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D74" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E74" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F74" s="28" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G74" s="28" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H74" s="30">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I74" s="30">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J74" s="29" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="K74" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L74" s="32">
+        <x:v>46122.6831438079</x:v>
+      </x:c>
+      <x:c r="M74" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B75" s="28" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C75" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D75" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E75" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F75" s="28" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G75" s="28" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H75" s="30">
+        <x:v>46122.7261372338</x:v>
+      </x:c>
+      <x:c r="I75" s="30">
+        <x:v>46122.727234375</x:v>
+      </x:c>
+      <x:c r="J75" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K75" s="31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L75" s="32">
+        <x:v>46122.7277720023</x:v>
+      </x:c>
+      <x:c r="M75" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B76" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C76" s="28" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D76" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E76" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F76" s="28" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G76" s="28" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H76" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I76" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J76" s="29" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="K76" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L76" s="32">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M76" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B77" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C77" s="28" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D77" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E77" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F77" s="28" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G77" s="28" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H77" s="30">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I77" s="30">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J77" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K77" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L77" s="32">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M77" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B78" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C78" s="28" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D78" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E78" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F78" s="28" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G78" s="28" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H78" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I78" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J78" s="29" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="K78" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L78" s="32">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M78" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B79" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C79" s="28" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D79" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E79" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F79" s="28" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G79" s="28" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H79" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I79" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J79" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="K79" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L79" s="32">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M79" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B80" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C80" s="28" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D80" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E80" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F80" s="28" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G80" s="28" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H80" s="30">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I80" s="30">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J80" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K80" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L80" s="32">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M80" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B81" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C81" s="28" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D81" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E81" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F81" s="28" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G81" s="28" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H81" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I81" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J81" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K81" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L81" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M81" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B82" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C82" s="28" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D82" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E82" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F82" s="28" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G82" s="28" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H82" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I82" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J82" s="29" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="K82" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L82" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M82" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B83" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C83" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D83" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E83" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F83" s="28" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G83" s="28" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H83" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I83" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J83" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K83" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L83" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M83" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B84" s="28" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C84" s="28" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D84" s="29" t="s"/>
+      <x:c r="E84" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F84" s="28" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G84" s="28" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H84" s="30">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I84" s="30">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J84" s="29" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="K84" s="31" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L84" s="32">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M84" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B85" s="28" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C85" s="28" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D85" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E85" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F85" s="28" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G85" s="28" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H85" s="30">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I85" s="30">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J85" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="K85" s="31" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L85" s="32">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M85" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B86" s="28" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C86" s="28" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D86" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E86" s="28" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F86" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G86" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H86" s="30">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I86" s="30">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J86" s="29" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="K86" s="31" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L86" s="32">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M86" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B89" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C89" s="17" t="s"/>
+      <x:c r="D89" s="17" t="s"/>
+      <x:c r="E89" s="18" t="s"/>
+      <x:c r="F89" s="18" t="s"/>
+    </x:row>
+    <x:row r="90" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B90" s="19" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C90" s="20" t="s"/>
+      <x:c r="D90" s="20" t="s"/>
+      <x:c r="E90" s="20" t="s"/>
+      <x:c r="F90" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B91" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C91" s="23" t="s"/>
+      <x:c r="D91" s="23" t="s"/>
+      <x:c r="E91" s="23" t="s"/>
+      <x:c r="F91" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B92" s="22" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C92" s="23" t="s"/>
+      <x:c r="D92" s="23" t="s"/>
+      <x:c r="E92" s="23" t="s"/>
+      <x:c r="F92" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B93" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C93" s="23" t="s"/>
+      <x:c r="D93" s="23" t="s"/>
+      <x:c r="E93" s="23" t="s"/>
+      <x:c r="F93" s="24" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B94" s="22" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C94" s="23" t="s"/>
+      <x:c r="D94" s="23" t="s"/>
+      <x:c r="E94" s="23" t="s"/>
+      <x:c r="F94" s="24" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B95" s="22" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C95" s="23" t="s"/>
+      <x:c r="D95" s="23" t="s"/>
+      <x:c r="E95" s="23" t="s"/>
+      <x:c r="F95" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B96" s="22" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C96" s="23" t="s"/>
+      <x:c r="D96" s="23" t="s"/>
+      <x:c r="E96" s="23" t="s"/>
+      <x:c r="F96" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B97" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C97" s="26" t="s"/>
+      <x:c r="D97" s="26" t="s"/>
+      <x:c r="E97" s="26" t="s"/>
+      <x:c r="F97" s="27" t="n">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
     <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8802,17 +9565,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B73:F73"/>
-    <x:mergeCell ref="B74:E74"/>
-    <x:mergeCell ref="B75:E75"/>
-    <x:mergeCell ref="B76:E76"/>
-    <x:mergeCell ref="B77:E77"/>
-    <x:mergeCell ref="B78:E78"/>
-    <x:mergeCell ref="B79:E79"/>
+    <x:mergeCell ref="B89:F89"/>
+    <x:mergeCell ref="B90:E90"/>
+    <x:mergeCell ref="B91:E91"/>
+    <x:mergeCell ref="B92:E92"/>
+    <x:mergeCell ref="B93:E93"/>
+    <x:mergeCell ref="B94:E94"/>
+    <x:mergeCell ref="B95:E95"/>
+    <x:mergeCell ref="B96:E96"/>
+    <x:mergeCell ref="B97:E97"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="280">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -162,6 +162,18 @@
     <x:t>Amateur Radio Station Permit to PURCHASE</x:t>
   </x:si>
   <x:si>
+    <x:t>CHING'S COLLECTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-ROXIV-08261-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1320-150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdadasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZXCASD</x:t>
   </x:si>
   <x:si>
@@ -174,6 +186,48 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
   </x:si>
   <x:si>
@@ -204,16 +258,64 @@
     <x:t>test123</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08134</x:t>
@@ -225,31 +327,136 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -261,103 +468,256 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -369,300 +729,6 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08176</x:t>
   </x:si>
   <x:si>
@@ -673,27 +739,6 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5618,7 +5663,7 @@
       </x:c>
       <x:c r="D9" s="29" t="s"/>
       <x:c r="E9" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F9" s="28" t="s">
         <x:v>46</x:v>
@@ -5627,10 +5672,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="30">
-        <x:v>46119.5290592824</x:v>
+        <x:v>46126.0027495833</x:v>
       </x:c>
       <x:c r="I9" s="30">
-        <x:v>46119.5300361458</x:v>
+        <x:v>46126.1631260764</x:v>
       </x:c>
       <x:c r="J9" s="29" t="s">
         <x:v>48</x:v>
@@ -5639,7 +5684,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46119.5304719792</x:v>
+        <x:v>46126.177127963</x:v>
       </x:c>
       <x:c r="M9" s="28" t="s">
         <x:v>20</x:v>
@@ -5647,37 +5692,35 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="28" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C10" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="s"/>
       <x:c r="E10" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="28" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="28" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="30">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46119.5290592824</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46119.5300361458</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46119.5304719792</x:v>
       </x:c>
       <x:c r="M10" s="28" t="s">
         <x:v>20</x:v>
@@ -5688,34 +5731,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5726,34 +5769,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F12" s="28" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G12" s="28" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5764,34 +5807,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G13" s="28" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5802,34 +5845,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F14" s="28" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G14" s="28" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5849,10 +5892,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G15" s="28" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="30">
         <x:v>46119.8023724884</x:v>
@@ -5861,7 +5904,7 @@
         <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
@@ -5887,25 +5930,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G16" s="28" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5925,25 +5968,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G17" s="28" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5963,16 +6006,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G18" s="28" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
         <x:v>71</x:v>
@@ -5981,7 +6024,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -6001,25 +6044,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G19" s="28" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -6039,25 +6082,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G20" s="28" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -6077,25 +6120,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -6121,19 +6164,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -6159,19 +6202,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -6191,25 +6234,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G24" s="28" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -6229,25 +6272,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G25" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6267,25 +6310,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G26" s="28" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6305,25 +6348,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G27" s="28" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
-        <x:v>95</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6343,25 +6386,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G28" s="28" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6381,25 +6424,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G29" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>101</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6425,10 +6468,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
         <x:v>104</x:v>
@@ -6437,7 +6480,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6463,19 +6506,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6495,25 +6538,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G32" s="28" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G32" s="28" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="H32" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6533,25 +6576,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G33" s="28" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H33" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I33" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J33" s="29" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="G33" s="28" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H33" s="30">
-        <x:v>46122.1996025926</x:v>
-      </x:c>
-      <x:c r="I33" s="30">
-        <x:v>46122.2050823032</x:v>
-      </x:c>
-      <x:c r="J33" s="29" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6571,25 +6614,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G34" s="28" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H34" s="30">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I34" s="30">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J34" s="29" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="G34" s="28" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H34" s="30">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I34" s="30">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J34" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6609,25 +6652,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G35" s="28" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G35" s="28" t="s">
+      <x:c r="H35" s="30">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I35" s="30">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J35" s="29" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="H35" s="30">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I35" s="30">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J35" s="29" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6647,25 +6690,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G36" s="28" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G36" s="28" t="s">
+      <x:c r="H36" s="30">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I36" s="30">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J36" s="29" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="H36" s="30">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I36" s="30">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J36" s="29" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6685,25 +6728,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G37" s="28" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G37" s="28" t="s">
+      <x:c r="H37" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I37" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J37" s="29" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="H37" s="30">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I37" s="30">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J37" s="29" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6723,25 +6766,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G38" s="28" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G38" s="28" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="H38" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6761,25 +6804,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G39" s="28" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H39" s="30">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I39" s="30">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J39" s="29" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="G39" s="28" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H39" s="30">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I39" s="30">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J39" s="29" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6799,25 +6842,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G40" s="28" t="s">
+      <x:c r="H40" s="30">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I40" s="30">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J40" s="29" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="H40" s="30">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I40" s="30">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J40" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6843,10 +6886,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
         <x:v>134</x:v>
@@ -6855,7 +6898,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6881,19 +6924,19 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46122.244317963</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6913,25 +6956,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G43" s="28" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6951,25 +6994,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="28" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G44" s="28" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -6989,25 +7032,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G45" s="28" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H45" s="30">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46124.704475463</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -7027,25 +7070,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="28" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G46" s="28" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H46" s="30">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
-        <x:v>147</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -7065,25 +7108,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="28" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G47" s="28" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H47" s="30">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -7103,25 +7146,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="28" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G48" s="28" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H48" s="30">
-        <x:v>46124.701771875</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I48" s="30">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -7141,25 +7184,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="28" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G49" s="28" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H49" s="30">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I49" s="30">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J49" s="29" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -7179,25 +7222,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="28" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G50" s="28" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H50" s="30">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I50" s="30">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -7217,25 +7260,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="28" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G51" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H51" s="30">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I51" s="30">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J51" s="29" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
@@ -7255,25 +7298,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="28" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G52" s="28" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H52" s="30">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I52" s="30">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J52" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="32">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M52" s="28" t="s">
         <x:v>20</x:v>
@@ -7299,10 +7342,10 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="H53" s="30">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I53" s="30">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J53" s="29" t="s">
         <x:v>167</x:v>
@@ -7311,7 +7354,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="32">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M53" s="28" t="s">
         <x:v>20</x:v>
@@ -7337,19 +7380,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7369,25 +7412,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G55" s="28" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H55" s="30">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I55" s="30">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J55" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7407,25 +7450,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G56" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H56" s="30">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7445,25 +7488,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G57" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H57" s="30">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I57" s="30">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J57" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7483,25 +7526,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="28" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G58" s="28" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H58" s="30">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I58" s="30">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J58" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K58" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7521,25 +7564,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="28" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G59" s="28" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H59" s="30">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I59" s="30">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J59" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K59" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
@@ -7565,19 +7608,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H60" s="30">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I60" s="30">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J60" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K60" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="32">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M60" s="28" t="s">
         <x:v>20</x:v>
@@ -7603,10 +7646,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H61" s="30">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I61" s="30">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J61" s="29" t="s">
         <x:v>188</x:v>
@@ -7615,7 +7658,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="32">
-        <x:v>46123.049084375</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M61" s="28" t="s">
         <x:v>20</x:v>
@@ -7641,10 +7684,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H62" s="30">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I62" s="30">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J62" s="29" t="s">
         <x:v>191</x:v>
@@ -7653,7 +7696,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M62" s="28" t="s">
         <x:v>20</x:v>
@@ -7679,19 +7722,19 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H63" s="30">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I63" s="30">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J63" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K63" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="32">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M63" s="28" t="s">
         <x:v>20</x:v>
@@ -7711,25 +7754,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="28" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G64" s="28" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H64" s="30">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I64" s="30">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J64" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="K64" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="32">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M64" s="28" t="s">
         <x:v>20</x:v>
@@ -7749,25 +7792,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="28" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G65" s="28" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H65" s="30">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I65" s="30">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J65" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K65" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="32">
-        <x:v>46122.398526713</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M65" s="28" t="s">
         <x:v>20</x:v>
@@ -7787,25 +7830,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="28" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G66" s="28" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H66" s="30">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I66" s="30">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J66" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K66" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="32">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M66" s="28" t="s">
         <x:v>20</x:v>
@@ -7825,25 +7868,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="28" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G67" s="28" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H67" s="30">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I67" s="30">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J67" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K67" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="32">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M67" s="28" t="s">
         <x:v>20</x:v>
@@ -7863,25 +7906,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="28" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G68" s="28" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H68" s="30">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I68" s="30">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J68" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K68" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="32">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M68" s="28" t="s">
         <x:v>20</x:v>
@@ -7901,25 +7944,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="28" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G69" s="28" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H69" s="30">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I69" s="30">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J69" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K69" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M69" s="28" t="s">
         <x:v>20</x:v>
@@ -7939,25 +7982,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="28" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G70" s="28" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H70" s="30">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I70" s="30">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J70" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K70" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="32">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M70" s="28" t="s">
         <x:v>20</x:v>
@@ -7977,25 +8020,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="28" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G71" s="28" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H71" s="30">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I71" s="30">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J71" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K71" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="32">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M71" s="28" t="s">
         <x:v>20</x:v>
@@ -8015,25 +8058,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="28" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G72" s="28" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H72" s="30">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I72" s="30">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J72" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K72" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="32">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M72" s="28" t="s">
         <x:v>20</x:v>
@@ -8053,16 +8096,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="28" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G73" s="28" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H73" s="30">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I73" s="30">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J73" s="29" t="s">
         <x:v>29</x:v>
@@ -8071,7 +8114,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="32">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M73" s="28" t="s">
         <x:v>20</x:v>
@@ -8091,25 +8134,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="28" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G74" s="28" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H74" s="30">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I74" s="30">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J74" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="K74" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="32">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M74" s="28" t="s">
         <x:v>20</x:v>
@@ -8129,25 +8172,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="28" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G75" s="28" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H75" s="30">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I75" s="30">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J75" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K75" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="32">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M75" s="28" t="s">
         <x:v>20</x:v>
@@ -8155,10 +8198,10 @@
     </x:row>
     <x:row r="76" spans="1:28" ht="30" customHeight="1">
       <x:c r="B76" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C76" s="28" t="s">
-        <x:v>224</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D76" s="29" t="s">
         <x:v>15</x:v>
@@ -8167,25 +8210,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="28" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G76" s="28" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H76" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I76" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J76" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="K76" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M76" s="28" t="s">
         <x:v>20</x:v>
@@ -8193,10 +8236,10 @@
     </x:row>
     <x:row r="77" spans="1:28" ht="30" customHeight="1">
       <x:c r="B77" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C77" s="28" t="s">
-        <x:v>228</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D77" s="29" t="s">
         <x:v>15</x:v>
@@ -8211,19 +8254,19 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="H77" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I77" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J77" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="K77" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M77" s="28" t="s">
         <x:v>20</x:v>
@@ -8231,10 +8274,10 @@
     </x:row>
     <x:row r="78" spans="1:28" ht="30" customHeight="1">
       <x:c r="B78" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C78" s="28" t="s">
-        <x:v>231</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D78" s="29" t="s">
         <x:v>15</x:v>
@@ -8243,25 +8286,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="28" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G78" s="28" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G78" s="28" t="s">
+      <x:c r="H78" s="30">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I78" s="30">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J78" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="H78" s="30">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I78" s="30">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J78" s="29" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="K78" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M78" s="28" t="s">
         <x:v>20</x:v>
@@ -8269,10 +8312,10 @@
     </x:row>
     <x:row r="79" spans="1:28" ht="30" customHeight="1">
       <x:c r="B79" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C79" s="28" t="s">
-        <x:v>235</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D79" s="29" t="s">
         <x:v>15</x:v>
@@ -8281,25 +8324,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="28" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G79" s="28" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H79" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I79" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J79" s="29" t="s">
-        <x:v>238</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K79" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M79" s="28" t="s">
         <x:v>20</x:v>
@@ -8307,10 +8350,10 @@
     </x:row>
     <x:row r="80" spans="1:28" ht="30" customHeight="1">
       <x:c r="B80" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C80" s="28" t="s">
-        <x:v>239</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D80" s="29" t="s">
         <x:v>15</x:v>
@@ -8319,25 +8362,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="28" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G80" s="28" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H80" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I80" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J80" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K80" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M80" s="28" t="s">
         <x:v>20</x:v>
@@ -8345,10 +8388,10 @@
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
       <x:c r="B81" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C81" s="28" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D81" s="29" t="s">
         <x:v>15</x:v>
@@ -8357,25 +8400,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="28" t="s">
-        <x:v>243</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G81" s="28" t="s">
-        <x:v>244</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H81" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I81" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J81" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K81" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L81" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M81" s="28" t="s">
         <x:v>20</x:v>
@@ -8383,10 +8426,10 @@
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
       <x:c r="B82" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C82" s="28" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D82" s="29" t="s">
         <x:v>15</x:v>
@@ -8395,25 +8438,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="28" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G82" s="28" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G82" s="28" t="s">
-        <x:v>246</x:v>
-      </x:c>
       <x:c r="H82" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I82" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J82" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K82" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L82" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M82" s="28" t="s">
         <x:v>20</x:v>
@@ -8421,10 +8464,10 @@
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
       <x:c r="B83" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C83" s="28" t="s">
-        <x:v>45</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D83" s="29" t="s">
         <x:v>15</x:v>
@@ -8433,25 +8476,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="28" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G83" s="28" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="G83" s="28" t="s">
+      <x:c r="H83" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I83" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J83" s="29" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="H83" s="30">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I83" s="30">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J83" s="29" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K83" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L83" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M83" s="28" t="s">
         <x:v>20</x:v>
@@ -8459,35 +8502,37 @@
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
       <x:c r="B84" s="28" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C84" s="28" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C84" s="28" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="D84" s="29" t="s"/>
+      <x:c r="D84" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E84" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="28" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G84" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G84" s="28" t="s">
+      <x:c r="H84" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I84" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J84" s="29" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="H84" s="30">
-        <x:v>46124.1588481829</x:v>
-      </x:c>
-      <x:c r="I84" s="30">
-        <x:v>46124.1588689236</x:v>
-      </x:c>
-      <x:c r="J84" s="29" t="s">
-        <x:v>254</x:v>
-      </x:c>
       <x:c r="K84" s="31" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L84" s="32">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M84" s="28" t="s">
         <x:v>20</x:v>
@@ -8495,37 +8540,37 @@
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
       <x:c r="B85" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C85" s="28" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D85" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E85" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G85" s="28" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="H85" s="30">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I85" s="30">
-        <x:v>46023</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J85" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K85" s="31" t="n">
-        <x:v>3100</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L85" s="32">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M85" s="28" t="s">
         <x:v>20</x:v>
@@ -8533,146 +8578,329 @@
     </x:row>
     <x:row r="86" spans="1:28" ht="30" customHeight="1">
       <x:c r="B86" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C86" s="28" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D86" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E86" s="28" t="s">
-        <x:v>261</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="28" t="s">
-        <x:v>262</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G86" s="28" t="s">
-        <x:v>263</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H86" s="30">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I86" s="30">
-        <x:v>46215</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J86" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K86" s="31" t="n">
-        <x:v>3006</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L86" s="32">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M86" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B87" s="28" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C87" s="28" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D87" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E87" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F87" s="28" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G87" s="28" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H87" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I87" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J87" s="29" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="K87" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L87" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M87" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B88" s="28" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C88" s="28" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D88" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E88" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F88" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G88" s="28" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H88" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I88" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J88" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K88" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L88" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M88" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B89" s="16" t="s">
+      <x:c r="B89" s="28" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C89" s="28" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D89" s="29" t="s"/>
+      <x:c r="E89" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F89" s="28" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G89" s="28" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H89" s="30">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I89" s="30">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J89" s="29" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="K89" s="31" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L89" s="32">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M89" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B90" s="28" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="C90" s="28" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D90" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E90" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F90" s="28" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G90" s="28" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H90" s="30">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I90" s="30">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J90" s="29" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="K90" s="31" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L90" s="32">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M90" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B91" s="28" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="C91" s="28" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D91" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E91" s="28" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F91" s="28" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G91" s="28" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H91" s="30">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I91" s="30">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J91" s="29" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="K91" s="31" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L91" s="32">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M91" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B94" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C89" s="17" t="s"/>
-      <x:c r="D89" s="17" t="s"/>
-      <x:c r="E89" s="18" t="s"/>
-      <x:c r="F89" s="18" t="s"/>
-    </x:row>
-    <x:row r="90" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B90" s="19" t="s">
+      <x:c r="C94" s="17" t="s"/>
+      <x:c r="D94" s="17" t="s"/>
+      <x:c r="E94" s="18" t="s"/>
+      <x:c r="F94" s="18" t="s"/>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B95" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C90" s="20" t="s"/>
-      <x:c r="D90" s="20" t="s"/>
-      <x:c r="E90" s="20" t="s"/>
-      <x:c r="F90" s="21" t="s">
+      <x:c r="C95" s="20" t="s"/>
+      <x:c r="D95" s="20" t="s"/>
+      <x:c r="E95" s="20" t="s"/>
+      <x:c r="F95" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B91" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C91" s="23" t="s"/>
-      <x:c r="D91" s="23" t="s"/>
-      <x:c r="E91" s="23" t="s"/>
-      <x:c r="F91" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B92" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C92" s="23" t="s"/>
-      <x:c r="D92" s="23" t="s"/>
-      <x:c r="E92" s="23" t="s"/>
-      <x:c r="F92" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B93" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C93" s="23" t="s"/>
-      <x:c r="D93" s="23" t="s"/>
-      <x:c r="E93" s="23" t="s"/>
-      <x:c r="F93" s="24" t="n">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B94" s="22" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="C94" s="23" t="s"/>
-      <x:c r="D94" s="23" t="s"/>
-      <x:c r="E94" s="23" t="s"/>
-      <x:c r="F94" s="24" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B95" s="22" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="C95" s="23" t="s"/>
-      <x:c r="D95" s="23" t="s"/>
-      <x:c r="E95" s="23" t="s"/>
-      <x:c r="F95" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:28" ht="18" customHeight="1">
       <x:c r="B96" s="22" t="s">
-        <x:v>255</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C96" s="23" t="s"/>
       <x:c r="D96" s="23" t="s"/>
       <x:c r="E96" s="23" t="s"/>
       <x:c r="F96" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B97" s="22" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C97" s="23" t="s"/>
+      <x:c r="D97" s="23" t="s"/>
+      <x:c r="E97" s="23" t="s"/>
+      <x:c r="F97" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B97" s="25" t="s">
+    <x:row r="98" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B98" s="22" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C98" s="23" t="s"/>
+      <x:c r="D98" s="23" t="s"/>
+      <x:c r="E98" s="23" t="s"/>
+      <x:c r="F98" s="24" t="n">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B99" s="22" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C99" s="23" t="s"/>
+      <x:c r="D99" s="23" t="s"/>
+      <x:c r="E99" s="23" t="s"/>
+      <x:c r="F99" s="24" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B100" s="22" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C100" s="23" t="s"/>
+      <x:c r="D100" s="23" t="s"/>
+      <x:c r="E100" s="23" t="s"/>
+      <x:c r="F100" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B101" s="22" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="C101" s="23" t="s"/>
+      <x:c r="D101" s="23" t="s"/>
+      <x:c r="E101" s="23" t="s"/>
+      <x:c r="F101" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B102" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C97" s="26" t="s"/>
-      <x:c r="D97" s="26" t="s"/>
-      <x:c r="E97" s="26" t="s"/>
-      <x:c r="F97" s="27" t="n">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C102" s="26" t="s"/>
+      <x:c r="D102" s="26" t="s"/>
+      <x:c r="E102" s="26" t="s"/>
+      <x:c r="F102" s="27" t="n">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
@@ -9569,15 +9797,15 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B89:F89"/>
-    <x:mergeCell ref="B90:E90"/>
-    <x:mergeCell ref="B91:E91"/>
-    <x:mergeCell ref="B92:E92"/>
-    <x:mergeCell ref="B93:E93"/>
-    <x:mergeCell ref="B94:E94"/>
+    <x:mergeCell ref="B94:F94"/>
     <x:mergeCell ref="B95:E95"/>
     <x:mergeCell ref="B96:E96"/>
     <x:mergeCell ref="B97:E97"/>
+    <x:mergeCell ref="B98:E98"/>
+    <x:mergeCell ref="B99:E99"/>
+    <x:mergeCell ref="B100:E100"/>
+    <x:mergeCell ref="B101:E101"/>
+    <x:mergeCell ref="B102:E102"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="280">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -195,6 +195,15 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08296</x:t>
   </x:si>
   <x:si>
@@ -213,13 +222,130 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
@@ -228,34 +354,25 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -264,67 +381,76 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
@@ -333,13 +459,52 @@
     <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08096</x:t>
@@ -348,48 +513,6 @@
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -399,64 +522,16 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -468,27 +543,6 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08215</x:t>
   </x:si>
   <x:si>
@@ -567,60 +621,60 @@
     <x:t>scawdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08190</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1301-555</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
   </x:si>
   <x:si>
@@ -675,36 +729,36 @@
     <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08180</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08179</x:t>
   </x:si>
   <x:si>
@@ -720,13 +774,10 @@
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08176</x:t>
@@ -5784,10 +5835,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>58</x:v>
@@ -5796,7 +5847,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5822,10 +5873,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>61</x:v>
@@ -5834,7 +5885,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5860,10 +5911,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>64</x:v>
@@ -5872,7 +5923,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5883,13 +5934,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="28" t="s">
         <x:v>65</x:v>
@@ -5898,19 +5949,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5921,34 +5972,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F16" s="28" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G16" s="28" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -5959,34 +6010,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F17" s="28" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G17" s="28" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -5997,34 +6048,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F18" s="28" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G18" s="28" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H18" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I18" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J18" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M18" s="28" t="s">
         <x:v>20</x:v>
@@ -6035,34 +6086,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="28" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="28" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F19" s="28" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G19" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -6082,25 +6133,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="28" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="28" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -6120,25 +6171,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -6158,25 +6209,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="28" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G22" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -6196,25 +6247,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G23" s="28" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="30">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I23" s="30">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J23" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46121.498248206</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -6234,25 +6285,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="28" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G24" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -6272,25 +6323,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G25" s="28" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6310,25 +6361,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="28" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G26" s="28" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6348,25 +6399,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="28" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G27" s="28" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I27" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J27" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M27" s="28" t="s">
         <x:v>20</x:v>
@@ -6386,25 +6437,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="28" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G28" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I28" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J28" s="29" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M28" s="28" t="s">
         <x:v>20</x:v>
@@ -6424,25 +6475,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G29" s="28" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H29" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I29" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J29" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M29" s="28" t="s">
         <x:v>20</x:v>
@@ -6462,25 +6513,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G30" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>104</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6500,25 +6551,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G31" s="28" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6538,25 +6589,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G32" s="28" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6576,25 +6627,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6614,25 +6665,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6652,25 +6703,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6690,25 +6741,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G36" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6728,25 +6779,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G37" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6766,25 +6817,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="28" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G38" s="28" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6804,25 +6855,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="28" t="s">
-        <x:v>126</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G39" s="28" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6842,25 +6893,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="28" t="s">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G40" s="28" t="s">
-        <x:v>130</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6880,25 +6931,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="28" t="s">
-        <x:v>132</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G41" s="28" t="s">
-        <x:v>133</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6918,25 +6969,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="28" t="s">
-        <x:v>135</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G42" s="28" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -6956,25 +7007,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="28" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G43" s="28" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -6994,25 +7045,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="28" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G44" s="28" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -7032,25 +7083,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G45" s="28" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H45" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -7070,25 +7121,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="28" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G46" s="28" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H46" s="30">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -7108,25 +7159,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="28" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G47" s="28" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H47" s="30">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -7146,25 +7197,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="28" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G48" s="28" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H48" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I48" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -7184,25 +7235,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="28" t="s">
-        <x:v>154</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G49" s="28" t="s">
-        <x:v>155</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H49" s="30">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I49" s="30">
-        <x:v>46124.704475463</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J49" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -7222,25 +7273,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="28" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G50" s="28" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H50" s="30">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I50" s="30">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -7260,25 +7311,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G51" s="28" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H51" s="30">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I51" s="30">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J51" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
@@ -7298,25 +7349,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="28" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G52" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H52" s="30">
-        <x:v>46124.701771875</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I52" s="30">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J52" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="32">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M52" s="28" t="s">
         <x:v>20</x:v>
@@ -7336,25 +7387,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="28" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G53" s="28" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H53" s="30">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I53" s="30">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J53" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="32">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M53" s="28" t="s">
         <x:v>20</x:v>
@@ -7374,25 +7425,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="28" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G54" s="28" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7412,25 +7463,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G55" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H55" s="30">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I55" s="30">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J55" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7450,25 +7501,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G56" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="30">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7488,25 +7539,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G57" s="28" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H57" s="30">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I57" s="30">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J57" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7526,25 +7577,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="28" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G58" s="28" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H58" s="30">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I58" s="30">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J58" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K58" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7564,25 +7615,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="28" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G59" s="28" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H59" s="30">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I59" s="30">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J59" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="K59" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
@@ -7602,25 +7653,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="28" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G60" s="28" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H60" s="30">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I60" s="30">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J60" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="K60" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="32">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M60" s="28" t="s">
         <x:v>20</x:v>
@@ -7640,25 +7691,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="28" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G61" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H61" s="30">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I61" s="30">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J61" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K61" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="32">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M61" s="28" t="s">
         <x:v>20</x:v>
@@ -7678,25 +7729,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="28" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G62" s="28" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H62" s="30">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I62" s="30">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J62" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K62" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="32">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M62" s="28" t="s">
         <x:v>20</x:v>
@@ -7716,25 +7767,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="28" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G63" s="28" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H63" s="30">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I63" s="30">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J63" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="K63" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="32">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M63" s="28" t="s">
         <x:v>20</x:v>
@@ -7754,25 +7805,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="28" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G64" s="28" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H64" s="30">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I64" s="30">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J64" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K64" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="32">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M64" s="28" t="s">
         <x:v>20</x:v>
@@ -7792,25 +7843,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="28" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G65" s="28" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H65" s="30">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I65" s="30">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J65" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K65" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="32">
-        <x:v>46123.049084375</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M65" s="28" t="s">
         <x:v>20</x:v>
@@ -7830,25 +7881,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="28" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G66" s="28" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H66" s="30">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I66" s="30">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J66" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K66" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M66" s="28" t="s">
         <x:v>20</x:v>
@@ -7868,25 +7919,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="28" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G67" s="28" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H67" s="30">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I67" s="30">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J67" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K67" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="32">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M67" s="28" t="s">
         <x:v>20</x:v>
@@ -7906,25 +7957,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="28" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G68" s="28" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H68" s="30">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I68" s="30">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J68" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K68" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="32">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M68" s="28" t="s">
         <x:v>20</x:v>
@@ -7944,25 +7995,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="28" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G69" s="28" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H69" s="30">
-        <x:v>46123.061368912</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I69" s="30">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J69" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K69" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="32">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M69" s="28" t="s">
         <x:v>20</x:v>
@@ -7982,25 +8033,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="28" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G70" s="28" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H70" s="30">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I70" s="30">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J70" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K70" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M70" s="28" t="s">
         <x:v>20</x:v>
@@ -8020,25 +8071,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="28" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G71" s="28" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H71" s="30">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I71" s="30">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J71" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K71" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="32">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M71" s="28" t="s">
         <x:v>20</x:v>
@@ -8058,25 +8109,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="28" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G72" s="28" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H72" s="30">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I72" s="30">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J72" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="K72" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="32">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M72" s="28" t="s">
         <x:v>20</x:v>
@@ -8096,25 +8147,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="28" t="s">
-        <x:v>218</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G73" s="28" t="s">
-        <x:v>219</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H73" s="30">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I73" s="30">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J73" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K73" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="32">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M73" s="28" t="s">
         <x:v>20</x:v>
@@ -8134,25 +8185,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="28" t="s">
-        <x:v>220</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G74" s="28" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H74" s="30">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I74" s="30">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J74" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K74" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="32">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M74" s="28" t="s">
         <x:v>20</x:v>
@@ -8172,25 +8223,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="28" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G75" s="28" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H75" s="30">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I75" s="30">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J75" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="K75" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="32">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M75" s="28" t="s">
         <x:v>20</x:v>
@@ -8210,25 +8261,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="28" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G76" s="28" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H76" s="30">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I76" s="30">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J76" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K76" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="32">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M76" s="28" t="s">
         <x:v>20</x:v>
@@ -8248,25 +8299,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="28" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G77" s="28" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H77" s="30">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I77" s="30">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J77" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K77" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="32">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M77" s="28" t="s">
         <x:v>20</x:v>
@@ -8286,25 +8337,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="28" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G78" s="28" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H78" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I78" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J78" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K78" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M78" s="28" t="s">
         <x:v>20</x:v>
@@ -8324,25 +8375,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="28" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G79" s="28" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H79" s="30">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I79" s="30">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J79" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K79" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="32">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M79" s="28" t="s">
         <x:v>20</x:v>
@@ -8362,25 +8413,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="28" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G80" s="28" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H80" s="30">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I80" s="30">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J80" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="K80" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="32">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M80" s="28" t="s">
         <x:v>20</x:v>
@@ -8388,10 +8439,10 @@
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
       <x:c r="B81" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C81" s="28" t="s">
-        <x:v>239</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D81" s="29" t="s">
         <x:v>15</x:v>
@@ -8400,25 +8451,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="28" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G81" s="28" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H81" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I81" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J81" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K81" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M81" s="28" t="s">
         <x:v>20</x:v>
@@ -8426,10 +8477,10 @@
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
       <x:c r="B82" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C82" s="28" t="s">
-        <x:v>243</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D82" s="29" t="s">
         <x:v>15</x:v>
@@ -8444,19 +8495,19 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="H82" s="30">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I82" s="30">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J82" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="K82" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M82" s="28" t="s">
         <x:v>20</x:v>
@@ -8464,10 +8515,10 @@
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
       <x:c r="B83" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C83" s="28" t="s">
-        <x:v>246</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D83" s="29" t="s">
         <x:v>15</x:v>
@@ -8482,19 +8533,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="H83" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I83" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J83" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K83" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M83" s="28" t="s">
         <x:v>20</x:v>
@@ -8502,10 +8553,10 @@
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
       <x:c r="B84" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C84" s="28" t="s">
-        <x:v>250</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D84" s="29" t="s">
         <x:v>15</x:v>
@@ -8514,25 +8565,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="28" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G84" s="28" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H84" s="30">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I84" s="30">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J84" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K84" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M84" s="28" t="s">
         <x:v>20</x:v>
@@ -8540,10 +8591,10 @@
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
       <x:c r="B85" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C85" s="28" t="s">
-        <x:v>254</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D85" s="29" t="s">
         <x:v>15</x:v>
@@ -8552,25 +8603,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G85" s="28" t="s">
-        <x:v>256</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H85" s="30">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I85" s="30">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J85" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K85" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M85" s="28" t="s">
         <x:v>20</x:v>
@@ -8578,10 +8629,10 @@
     </x:row>
     <x:row r="86" spans="1:28" ht="30" customHeight="1">
       <x:c r="B86" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C86" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D86" s="29" t="s">
         <x:v>15</x:v>
@@ -8590,25 +8641,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="28" t="s">
-        <x:v>258</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G86" s="28" t="s">
-        <x:v>259</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H86" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I86" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J86" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K86" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M86" s="28" t="s">
         <x:v>20</x:v>
@@ -8616,10 +8667,10 @@
     </x:row>
     <x:row r="87" spans="1:28" ht="30" customHeight="1">
       <x:c r="B87" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C87" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D87" s="29" t="s">
         <x:v>15</x:v>
@@ -8628,25 +8679,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="28" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G87" s="28" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H87" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I87" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J87" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="K87" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L87" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M87" s="28" t="s">
         <x:v>20</x:v>
@@ -8654,10 +8705,10 @@
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
       <x:c r="B88" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C88" s="28" t="s">
-        <x:v>49</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="D88" s="29" t="s">
         <x:v>15</x:v>
@@ -8666,25 +8717,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="28" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G88" s="28" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H88" s="30">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I88" s="30">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J88" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K88" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L88" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M88" s="28" t="s">
         <x:v>20</x:v>
@@ -8692,35 +8743,37 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="28" t="s">
-        <x:v>265</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C89" s="28" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="D89" s="29" t="s"/>
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="D89" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E89" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="28" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G89" s="28" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H89" s="30">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I89" s="30">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J89" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="K89" s="31" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L89" s="32">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M89" s="28" t="s">
         <x:v>20</x:v>
@@ -8728,37 +8781,37 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="28" t="s">
-        <x:v>270</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C90" s="28" t="s">
-        <x:v>271</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D90" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E90" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="28" t="s">
-        <x:v>272</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G90" s="28" t="s">
-        <x:v>273</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="H90" s="30">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46118.7372774306</x:v>
       </x:c>
       <x:c r="I90" s="30">
-        <x:v>46023</x:v>
+        <x:v>46118.7373236806</x:v>
       </x:c>
       <x:c r="J90" s="29" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="K90" s="31" t="n">
-        <x:v>3100</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="32">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M90" s="28" t="s">
         <x:v>20</x:v>
@@ -8766,147 +8819,367 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="28" t="s">
-        <x:v>270</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C91" s="28" t="s">
-        <x:v>275</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D91" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E91" s="28" t="s">
-        <x:v>276</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F91" s="28" t="s">
-        <x:v>277</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G91" s="28" t="s">
-        <x:v>278</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H91" s="30">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I91" s="30">
-        <x:v>46215</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J91" s="29" t="s">
-        <x:v>279</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K91" s="31" t="n">
-        <x:v>3006</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="32">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M91" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B92" s="28" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C92" s="28" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D92" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E92" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F92" s="28" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G92" s="28" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H92" s="30">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I92" s="30">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J92" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K92" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L92" s="32">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M92" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B93" s="28" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C93" s="28" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="D93" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E93" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F93" s="28" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G93" s="28" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H93" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I93" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J93" s="29" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="K93" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L93" s="32">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M93" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B94" s="16" t="s">
+      <x:c r="B94" s="28" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C94" s="28" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D94" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E94" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F94" s="28" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G94" s="28" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H94" s="30">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I94" s="30">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J94" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K94" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L94" s="32">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M94" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B95" s="28" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C95" s="28" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D95" s="29" t="s"/>
+      <x:c r="E95" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F95" s="28" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G95" s="28" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H95" s="30">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I95" s="30">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J95" s="29" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="K95" s="31" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L95" s="32">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M95" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B96" s="28" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C96" s="28" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D96" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E96" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F96" s="28" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G96" s="28" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H96" s="30">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I96" s="30">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J96" s="29" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="K96" s="31" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L96" s="32">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M96" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B97" s="28" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C97" s="28" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D97" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E97" s="28" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F97" s="28" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G97" s="28" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H97" s="30">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I97" s="30">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J97" s="29" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K97" s="31" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L97" s="32">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M97" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B100" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C94" s="17" t="s"/>
-      <x:c r="D94" s="17" t="s"/>
-      <x:c r="E94" s="18" t="s"/>
-      <x:c r="F94" s="18" t="s"/>
-    </x:row>
-    <x:row r="95" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B95" s="19" t="s">
+      <x:c r="C100" s="17" t="s"/>
+      <x:c r="D100" s="17" t="s"/>
+      <x:c r="E100" s="18" t="s"/>
+      <x:c r="F100" s="18" t="s"/>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B101" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C95" s="20" t="s"/>
-      <x:c r="D95" s="20" t="s"/>
-      <x:c r="E95" s="20" t="s"/>
-      <x:c r="F95" s="21" t="s">
+      <x:c r="C101" s="20" t="s"/>
+      <x:c r="D101" s="20" t="s"/>
+      <x:c r="E101" s="20" t="s"/>
+      <x:c r="F101" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B96" s="22" t="s">
+    <x:row r="102" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B102" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C96" s="23" t="s"/>
-      <x:c r="D96" s="23" t="s"/>
-      <x:c r="E96" s="23" t="s"/>
-      <x:c r="F96" s="24" t="n">
+      <x:c r="C102" s="23" t="s"/>
+      <x:c r="D102" s="23" t="s"/>
+      <x:c r="E102" s="23" t="s"/>
+      <x:c r="F102" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B97" s="22" t="s">
+    <x:row r="103" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B103" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C97" s="23" t="s"/>
-      <x:c r="D97" s="23" t="s"/>
-      <x:c r="E97" s="23" t="s"/>
-      <x:c r="F97" s="24" t="n">
+      <x:c r="C103" s="23" t="s"/>
+      <x:c r="D103" s="23" t="s"/>
+      <x:c r="E103" s="23" t="s"/>
+      <x:c r="F103" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B98" s="22" t="s">
+    <x:row r="104" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B104" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C98" s="23" t="s"/>
-      <x:c r="D98" s="23" t="s"/>
-      <x:c r="E98" s="23" t="s"/>
-      <x:c r="F98" s="24" t="n">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B99" s="22" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="C99" s="23" t="s"/>
-      <x:c r="D99" s="23" t="s"/>
-      <x:c r="E99" s="23" t="s"/>
-      <x:c r="F99" s="24" t="n">
+      <x:c r="C104" s="23" t="s"/>
+      <x:c r="D104" s="23" t="s"/>
+      <x:c r="E104" s="23" t="s"/>
+      <x:c r="F104" s="24" t="n">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B105" s="22" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C105" s="23" t="s"/>
+      <x:c r="D105" s="23" t="s"/>
+      <x:c r="E105" s="23" t="s"/>
+      <x:c r="F105" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B100" s="22" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="C100" s="23" t="s"/>
-      <x:c r="D100" s="23" t="s"/>
-      <x:c r="E100" s="23" t="s"/>
-      <x:c r="F100" s="24" t="n">
+    <x:row r="106" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B106" s="22" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C106" s="23" t="s"/>
+      <x:c r="D106" s="23" t="s"/>
+      <x:c r="E106" s="23" t="s"/>
+      <x:c r="F106" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B101" s="22" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="C101" s="23" t="s"/>
-      <x:c r="D101" s="23" t="s"/>
-      <x:c r="E101" s="23" t="s"/>
-      <x:c r="F101" s="24" t="n">
+    <x:row r="107" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B107" s="22" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C107" s="23" t="s"/>
+      <x:c r="D107" s="23" t="s"/>
+      <x:c r="E107" s="23" t="s"/>
+      <x:c r="F107" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B102" s="25" t="s">
+    <x:row r="108" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B108" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C102" s="26" t="s"/>
-      <x:c r="D102" s="26" t="s"/>
-      <x:c r="E102" s="26" t="s"/>
-      <x:c r="F102" s="27" t="n">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C108" s="26" t="s"/>
+      <x:c r="D108" s="26" t="s"/>
+      <x:c r="E108" s="26" t="s"/>
+      <x:c r="F108" s="27" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
     <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
@@ -9797,15 +10070,15 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B94:F94"/>
-    <x:mergeCell ref="B95:E95"/>
-    <x:mergeCell ref="B96:E96"/>
-    <x:mergeCell ref="B97:E97"/>
-    <x:mergeCell ref="B98:E98"/>
-    <x:mergeCell ref="B99:E99"/>
-    <x:mergeCell ref="B100:E100"/>
+    <x:mergeCell ref="B100:F100"/>
     <x:mergeCell ref="B101:E101"/>
     <x:mergeCell ref="B102:E102"/>
+    <x:mergeCell ref="B103:E103"/>
+    <x:mergeCell ref="B104:E104"/>
+    <x:mergeCell ref="B105:E105"/>
+    <x:mergeCell ref="B106:E106"/>
+    <x:mergeCell ref="B107:E107"/>
+    <x:mergeCell ref="B108:E108"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -186,6 +186,60 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08219</x:t>
   </x:si>
   <x:si>
@@ -195,6 +249,15 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08292</x:t>
   </x:si>
   <x:si>
@@ -204,67 +267,13 @@
     <x:t>sczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1325-890</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdxzcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -303,13 +312,40 @@
     <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08147</x:t>
@@ -321,54 +357,27 @@
     <x:t>zxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
@@ -483,13 +492,10 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
@@ -522,10 +528,10 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
@@ -534,6 +540,90 @@
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -543,73 +633,43 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08191</x:t>
@@ -621,43 +681,31 @@
     <x:t>scawdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -669,10 +717,76 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
@@ -682,114 +796,6 @@
   </x:si>
   <x:si>
     <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5797,19 +5803,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5835,10 +5841,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>58</x:v>
@@ -5847,7 +5853,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5873,10 +5879,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>61</x:v>
@@ -5885,7 +5891,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5911,10 +5917,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="30">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
         <x:v>64</x:v>
@@ -5923,7 +5929,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M14" s="28" t="s">
         <x:v>20</x:v>
@@ -5949,10 +5955,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
         <x:v>67</x:v>
@@ -5961,7 +5967,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5987,10 +5993,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
         <x:v>70</x:v>
@@ -5999,7 +6005,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -6025,19 +6031,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -6101,10 +6107,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>79</x:v>
@@ -6113,7 +6119,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -6139,19 +6145,19 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -6171,25 +6177,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H21" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I21" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J21" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -6215,19 +6221,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -6247,25 +6253,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H23" s="30">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I23" s="30">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -6291,19 +6297,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -6323,25 +6329,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="28" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I25" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J25" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6367,10 +6373,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
         <x:v>97</x:v>
@@ -6379,7 +6385,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6519,19 +6525,19 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H30" s="30">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I30" s="30">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J30" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="32">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="28" t="s">
         <x:v>20</x:v>
@@ -6551,25 +6557,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="28" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G31" s="28" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H31" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I31" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J31" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M31" s="28" t="s">
         <x:v>20</x:v>
@@ -6633,19 +6639,19 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6665,25 +6671,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G34" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="30">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I34" s="30">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J34" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="32">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M34" s="28" t="s">
         <x:v>20</x:v>
@@ -6703,25 +6709,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="28" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G35" s="28" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="30">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I35" s="30">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="32">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M35" s="28" t="s">
         <x:v>20</x:v>
@@ -6747,10 +6753,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H36" s="30">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I36" s="30">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J36" s="29" t="s">
         <x:v>123</x:v>
@@ -6759,7 +6765,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="32">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M36" s="28" t="s">
         <x:v>20</x:v>
@@ -6785,10 +6791,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="H37" s="30">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I37" s="30">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J37" s="29" t="s">
         <x:v>126</x:v>
@@ -6797,7 +6803,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="32">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M37" s="28" t="s">
         <x:v>20</x:v>
@@ -6823,10 +6829,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="30">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I38" s="30">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J38" s="29" t="s">
         <x:v>129</x:v>
@@ -6835,7 +6841,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="32">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M38" s="28" t="s">
         <x:v>20</x:v>
@@ -6861,10 +6867,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H39" s="30">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I39" s="30">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J39" s="29" t="s">
         <x:v>132</x:v>
@@ -6873,7 +6879,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="32">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M39" s="28" t="s">
         <x:v>20</x:v>
@@ -6899,10 +6905,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="H40" s="30">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I40" s="30">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J40" s="29" t="s">
         <x:v>135</x:v>
@@ -6911,7 +6917,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="32">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M40" s="28" t="s">
         <x:v>20</x:v>
@@ -6937,10 +6943,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H41" s="30">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I41" s="30">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="29" t="s">
         <x:v>138</x:v>
@@ -6949,7 +6955,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="32">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M41" s="28" t="s">
         <x:v>20</x:v>
@@ -6975,10 +6981,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H42" s="30">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I42" s="30">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J42" s="29" t="s">
         <x:v>141</x:v>
@@ -6987,7 +6993,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="32">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M42" s="28" t="s">
         <x:v>20</x:v>
@@ -7013,19 +7019,19 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H43" s="30">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I43" s="30">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J43" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="32">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M43" s="28" t="s">
         <x:v>20</x:v>
@@ -7045,25 +7051,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G44" s="28" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H44" s="30">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I44" s="30">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="32">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M44" s="28" t="s">
         <x:v>20</x:v>
@@ -7083,25 +7089,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="28" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G45" s="28" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H45" s="30">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I45" s="30">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J45" s="29" t="s">
-        <x:v>148</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="32">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M45" s="28" t="s">
         <x:v>20</x:v>
@@ -7127,10 +7133,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H46" s="30">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I46" s="30">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J46" s="29" t="s">
         <x:v>151</x:v>
@@ -7139,7 +7145,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="32">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M46" s="28" t="s">
         <x:v>20</x:v>
@@ -7165,10 +7171,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="H47" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I47" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J47" s="29" t="s">
         <x:v>154</x:v>
@@ -7177,7 +7183,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M47" s="28" t="s">
         <x:v>20</x:v>
@@ -7203,19 +7209,19 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H48" s="30">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I48" s="30">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="32">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M48" s="28" t="s">
         <x:v>20</x:v>
@@ -7235,25 +7241,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="28" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G49" s="28" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G49" s="28" t="s">
+      <x:c r="H49" s="30">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I49" s="30">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J49" s="29" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="H49" s="30">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I49" s="30">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J49" s="29" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="32">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M49" s="28" t="s">
         <x:v>20</x:v>
@@ -7279,19 +7285,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H50" s="30">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I50" s="30">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="32">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M50" s="28" t="s">
         <x:v>20</x:v>
@@ -7317,19 +7323,19 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H51" s="30">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I51" s="30">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J51" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="32">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M51" s="28" t="s">
         <x:v>20</x:v>
@@ -7349,25 +7355,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="28" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G52" s="28" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G52" s="28" t="s">
+      <x:c r="H52" s="30">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I52" s="30">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J52" s="29" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="H52" s="30">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I52" s="30">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J52" s="29" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="32">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M52" s="28" t="s">
         <x:v>20</x:v>
@@ -7393,19 +7399,19 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="H53" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I53" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J53" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M53" s="28" t="s">
         <x:v>20</x:v>
@@ -7431,19 +7437,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7463,25 +7469,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G55" s="28" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G55" s="28" t="s">
+      <x:c r="H55" s="30">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I55" s="30">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J55" s="29" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="H55" s="30">
-        <x:v>46124.7035032407</x:v>
-      </x:c>
-      <x:c r="I55" s="30">
-        <x:v>46124.704475463</x:v>
-      </x:c>
-      <x:c r="J55" s="29" t="s">
-        <x:v>174</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7501,25 +7507,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G56" s="28" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G56" s="28" t="s">
-        <x:v>176</x:v>
-      </x:c>
       <x:c r="H56" s="30">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7539,25 +7545,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G57" s="28" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H57" s="30">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I57" s="30">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J57" s="29" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="G57" s="28" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H57" s="30">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I57" s="30">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J57" s="29" t="s">
-        <x:v>180</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7577,25 +7583,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="28" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G58" s="28" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H58" s="30">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I58" s="30">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J58" s="29" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="G58" s="28" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H58" s="30">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I58" s="30">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J58" s="29" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K58" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7615,25 +7621,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="28" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G59" s="28" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="G59" s="28" t="s">
+      <x:c r="H59" s="30">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I59" s="30">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J59" s="29" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="H59" s="30">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I59" s="30">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J59" s="29" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="K59" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
@@ -7653,25 +7659,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="28" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G60" s="28" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="G60" s="28" t="s">
-        <x:v>187</x:v>
-      </x:c>
       <x:c r="H60" s="30">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I60" s="30">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J60" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K60" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="32">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M60" s="28" t="s">
         <x:v>20</x:v>
@@ -7691,25 +7697,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="28" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G61" s="28" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H61" s="30">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I61" s="30">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J61" s="29" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="G61" s="28" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H61" s="30">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I61" s="30">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J61" s="29" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="K61" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="32">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M61" s="28" t="s">
         <x:v>20</x:v>
@@ -7729,25 +7735,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="28" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G62" s="28" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H62" s="30">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I62" s="30">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J62" s="29" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G62" s="28" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H62" s="30">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I62" s="30">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J62" s="29" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="K62" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="32">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M62" s="28" t="s">
         <x:v>20</x:v>
@@ -7767,25 +7773,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="28" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G63" s="28" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H63" s="30">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I63" s="30">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J63" s="29" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="G63" s="28" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H63" s="30">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I63" s="30">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J63" s="29" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="K63" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="32">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M63" s="28" t="s">
         <x:v>20</x:v>
@@ -7805,25 +7811,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="28" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G64" s="28" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H64" s="30">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I64" s="30">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J64" s="29" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="G64" s="28" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H64" s="30">
-        <x:v>46122.3569147569</x:v>
-      </x:c>
-      <x:c r="I64" s="30">
-        <x:v>46122.3577305324</x:v>
-      </x:c>
-      <x:c r="J64" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K64" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="32">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M64" s="28" t="s">
         <x:v>20</x:v>
@@ -7843,25 +7849,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="28" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G65" s="28" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G65" s="28" t="s">
+      <x:c r="H65" s="30">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I65" s="30">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J65" s="29" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="H65" s="30">
-        <x:v>46124.1487218981</x:v>
-      </x:c>
-      <x:c r="I65" s="30">
-        <x:v>46124.1494313773</x:v>
-      </x:c>
-      <x:c r="J65" s="29" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="K65" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="32">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M65" s="28" t="s">
         <x:v>20</x:v>
@@ -7881,25 +7887,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="28" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G66" s="28" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G66" s="28" t="s">
-        <x:v>204</x:v>
-      </x:c>
       <x:c r="H66" s="30">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I66" s="30">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J66" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K66" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="32">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M66" s="28" t="s">
         <x:v>20</x:v>
@@ -7919,25 +7925,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="28" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G67" s="28" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G67" s="28" t="s">
+      <x:c r="H67" s="30">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I67" s="30">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J67" s="29" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="H67" s="30">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I67" s="30">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J67" s="29" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="K67" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="32">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M67" s="28" t="s">
         <x:v>20</x:v>
@@ -7957,25 +7963,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="28" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G68" s="28" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G68" s="28" t="s">
-        <x:v>209</x:v>
-      </x:c>
       <x:c r="H68" s="30">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I68" s="30">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J68" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K68" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="32">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M68" s="28" t="s">
         <x:v>20</x:v>
@@ -7995,25 +8001,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="28" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G69" s="28" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H69" s="30">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I69" s="30">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J69" s="29" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="G69" s="28" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H69" s="30">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I69" s="30">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J69" s="29" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="K69" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="32">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M69" s="28" t="s">
         <x:v>20</x:v>
@@ -8033,25 +8039,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="28" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G70" s="28" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H70" s="30">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I70" s="30">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J70" s="29" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="G70" s="28" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H70" s="30">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I70" s="30">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J70" s="29" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K70" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="32">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M70" s="28" t="s">
         <x:v>20</x:v>
@@ -8071,25 +8077,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="28" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G71" s="28" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="G71" s="28" t="s">
+      <x:c r="H71" s="30">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I71" s="30">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J71" s="29" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="H71" s="30">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I71" s="30">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J71" s="29" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="K71" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="32">
-        <x:v>46123.049084375</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M71" s="28" t="s">
         <x:v>20</x:v>
@@ -8109,25 +8115,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="28" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G72" s="28" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G72" s="28" t="s">
+      <x:c r="H72" s="30">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I72" s="30">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J72" s="29" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="H72" s="30">
-        <x:v>46122.3767795718</x:v>
-      </x:c>
-      <x:c r="I72" s="30">
-        <x:v>46122.3776183449</x:v>
-      </x:c>
-      <x:c r="J72" s="29" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="K72" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M72" s="28" t="s">
         <x:v>20</x:v>
@@ -8147,10 +8153,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="28" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G73" s="28" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="G73" s="28" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="H73" s="30">
         <x:v>46122.3879258681</x:v>
@@ -8159,7 +8165,7 @@
         <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J73" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K73" s="31" t="n">
         <x:v>210</x:v>
@@ -8185,10 +8191,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="28" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G74" s="28" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="G74" s="28" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="H74" s="30">
         <x:v>46122.3885020718</x:v>
@@ -8223,25 +8229,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="28" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G75" s="28" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G75" s="28" t="s">
-        <x:v>227</x:v>
-      </x:c>
       <x:c r="H75" s="30">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I75" s="30">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J75" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K75" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="32">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M75" s="28" t="s">
         <x:v>20</x:v>
@@ -8261,25 +8267,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="28" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G76" s="28" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H76" s="30">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I76" s="30">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J76" s="29" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="G76" s="28" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H76" s="30">
-        <x:v>46122.5587807523</x:v>
-      </x:c>
-      <x:c r="I76" s="30">
-        <x:v>46122.5602428125</x:v>
-      </x:c>
-      <x:c r="J76" s="29" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="K76" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M76" s="28" t="s">
         <x:v>20</x:v>
@@ -8299,10 +8305,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="28" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G77" s="28" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H77" s="30">
         <x:v>46122.5623107755</x:v>
@@ -8311,7 +8317,7 @@
         <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J77" s="29" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K77" s="31" t="n">
         <x:v>210</x:v>
@@ -8337,10 +8343,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="28" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G78" s="28" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H78" s="30">
         <x:v>46122.5911383796</x:v>
@@ -8349,7 +8355,7 @@
         <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J78" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="K78" s="31" t="n">
         <x:v>210</x:v>
@@ -8375,25 +8381,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="28" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G79" s="28" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H79" s="30">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I79" s="30">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J79" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K79" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="32">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M79" s="28" t="s">
         <x:v>20</x:v>
@@ -8413,25 +8419,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="28" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G80" s="28" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H80" s="30">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I80" s="30">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J80" s="29" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="G80" s="28" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H80" s="30">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I80" s="30">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J80" s="29" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="K80" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="32">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M80" s="28" t="s">
         <x:v>20</x:v>
@@ -8451,16 +8457,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="28" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G81" s="28" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H81" s="30">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I81" s="30">
-        <x:v>46122.727234375</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J81" s="29" t="s">
         <x:v>29</x:v>
@@ -8469,7 +8475,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="32">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M81" s="28" t="s">
         <x:v>20</x:v>
@@ -8489,25 +8495,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="28" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G82" s="28" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H82" s="30">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I82" s="30">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J82" s="29" t="s">
-        <x:v>246</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K82" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="32">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M82" s="28" t="s">
         <x:v>20</x:v>
@@ -8527,25 +8533,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="28" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G83" s="28" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H83" s="30">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I83" s="30">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J83" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="K83" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="32">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M83" s="28" t="s">
         <x:v>20</x:v>
@@ -8565,16 +8571,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="28" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G84" s="28" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H84" s="30">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I84" s="30">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J84" s="29" t="s">
         <x:v>29</x:v>
@@ -8583,7 +8589,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="32">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M84" s="28" t="s">
         <x:v>20</x:v>
@@ -8603,25 +8609,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="28" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G85" s="28" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H85" s="30">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I85" s="30">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J85" s="29" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="G85" s="28" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H85" s="30">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I85" s="30">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J85" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K85" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="32">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M85" s="28" t="s">
         <x:v>20</x:v>
@@ -8641,10 +8647,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="28" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G86" s="28" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="G86" s="28" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="H86" s="30">
         <x:v>46122.6182774306</x:v>
@@ -8653,7 +8659,7 @@
         <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J86" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K86" s="31" t="n">
         <x:v>210</x:v>
@@ -8667,10 +8673,10 @@
     </x:row>
     <x:row r="87" spans="1:28" ht="30" customHeight="1">
       <x:c r="B87" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C87" s="28" t="s">
-        <x:v>256</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D87" s="29" t="s">
         <x:v>15</x:v>
@@ -8679,25 +8685,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G87" s="28" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H87" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I87" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J87" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K87" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M87" s="28" t="s">
         <x:v>20</x:v>
@@ -8705,10 +8711,10 @@
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
       <x:c r="B88" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C88" s="28" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D88" s="29" t="s">
         <x:v>15</x:v>
@@ -8717,25 +8723,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="28" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G88" s="28" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H88" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I88" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J88" s="29" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="G88" s="28" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H88" s="30">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I88" s="30">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J88" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K88" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L88" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M88" s="28" t="s">
         <x:v>20</x:v>
@@ -8743,10 +8749,10 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C89" s="28" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D89" s="29" t="s">
         <x:v>15</x:v>
@@ -8755,25 +8761,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="28" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G89" s="28" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="G89" s="28" t="s">
-        <x:v>265</x:v>
-      </x:c>
       <x:c r="H89" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I89" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J89" s="29" t="s">
-        <x:v>266</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K89" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L89" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M89" s="28" t="s">
         <x:v>20</x:v>
@@ -8781,10 +8787,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C90" s="28" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D90" s="29" t="s">
         <x:v>15</x:v>
@@ -8793,25 +8799,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="28" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G90" s="28" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H90" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I90" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J90" s="29" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="G90" s="28" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H90" s="30">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I90" s="30">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J90" s="29" t="s">
-        <x:v>270</x:v>
       </x:c>
       <x:c r="K90" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M90" s="28" t="s">
         <x:v>20</x:v>
@@ -8819,10 +8825,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C91" s="28" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D91" s="29" t="s">
         <x:v>15</x:v>
@@ -8831,25 +8837,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F91" s="28" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G91" s="28" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H91" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I91" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J91" s="29" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="G91" s="28" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H91" s="30">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I91" s="30">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J91" s="29" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K91" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M91" s="28" t="s">
         <x:v>20</x:v>
@@ -8857,10 +8863,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C92" s="28" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D92" s="29" t="s">
         <x:v>15</x:v>
@@ -8869,25 +8875,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F92" s="28" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G92" s="28" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G92" s="28" t="s">
-        <x:v>276</x:v>
-      </x:c>
       <x:c r="H92" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I92" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J92" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K92" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M92" s="28" t="s">
         <x:v>20</x:v>
@@ -8895,10 +8901,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C93" s="28" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D93" s="29" t="s">
         <x:v>15</x:v>
@@ -8913,19 +8919,19 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="H93" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I93" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J93" s="29" t="s">
-        <x:v>279</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K93" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M93" s="28" t="s">
         <x:v>20</x:v>
@@ -8933,10 +8939,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="28" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C94" s="28" t="s">
-        <x:v>49</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D94" s="29" t="s">
         <x:v>15</x:v>
@@ -8945,25 +8951,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F94" s="28" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="G94" s="28" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G94" s="28" t="s">
+      <x:c r="H94" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I94" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J94" s="29" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="H94" s="30">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I94" s="30">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J94" s="29" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K94" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M94" s="28" t="s">
         <x:v>20</x:v>
@@ -8971,35 +8977,37 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="28" t="s">
-        <x:v>282</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C95" s="28" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="D95" s="29" t="s"/>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D95" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E95" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F95" s="28" t="s">
-        <x:v>284</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="G95" s="28" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="H95" s="30">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I95" s="30">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J95" s="29" t="s">
-        <x:v>286</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K95" s="31" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="32">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M95" s="28" t="s">
         <x:v>20</x:v>
@@ -9007,37 +9015,35 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="28" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C96" s="28" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D96" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D96" s="29" t="s"/>
       <x:c r="E96" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F96" s="28" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G96" s="28" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="H96" s="30">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I96" s="30">
-        <x:v>46023</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J96" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="K96" s="31" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L96" s="32">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M96" s="28" t="s">
         <x:v>20</x:v>
@@ -9045,142 +9051,179 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="28" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C97" s="28" t="s">
-        <x:v>292</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D97" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E97" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F97" s="28" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G97" s="28" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H97" s="30">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I97" s="30">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J97" s="29" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="F97" s="28" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G97" s="28" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H97" s="30">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I97" s="30">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J97" s="29" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="K97" s="31" t="n">
-        <x:v>3006</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="L97" s="32">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1624131829</x:v>
       </x:c>
       <x:c r="M97" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B98" s="28" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C98" s="28" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D98" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E98" s="28" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F98" s="28" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G98" s="28" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H98" s="30">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I98" s="30">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J98" s="29" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="K98" s="31" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L98" s="32">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M98" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B100" s="16" t="s">
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B101" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C100" s="17" t="s"/>
-      <x:c r="D100" s="17" t="s"/>
-      <x:c r="E100" s="18" t="s"/>
-      <x:c r="F100" s="18" t="s"/>
-    </x:row>
-    <x:row r="101" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B101" s="19" t="s">
+      <x:c r="C101" s="17" t="s"/>
+      <x:c r="D101" s="17" t="s"/>
+      <x:c r="E101" s="18" t="s"/>
+      <x:c r="F101" s="18" t="s"/>
+    </x:row>
+    <x:row r="102" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B102" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C101" s="20" t="s"/>
-      <x:c r="D101" s="20" t="s"/>
-      <x:c r="E101" s="20" t="s"/>
-      <x:c r="F101" s="21" t="s">
+      <x:c r="C102" s="20" t="s"/>
+      <x:c r="D102" s="20" t="s"/>
+      <x:c r="E102" s="20" t="s"/>
+      <x:c r="F102" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B102" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C102" s="23" t="s"/>
-      <x:c r="D102" s="23" t="s"/>
-      <x:c r="E102" s="23" t="s"/>
-      <x:c r="F102" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:28" ht="18" customHeight="1">
       <x:c r="B103" s="22" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C103" s="23" t="s"/>
       <x:c r="D103" s="23" t="s"/>
       <x:c r="E103" s="23" t="s"/>
       <x:c r="F103" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:28" ht="18" customHeight="1">
       <x:c r="B104" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C104" s="23" t="s"/>
       <x:c r="D104" s="23" t="s"/>
       <x:c r="E104" s="23" t="s"/>
       <x:c r="F104" s="24" t="n">
-        <x:v>76</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
       <x:c r="B105" s="22" t="s">
-        <x:v>255</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C105" s="23" t="s"/>
       <x:c r="D105" s="23" t="s"/>
       <x:c r="E105" s="23" t="s"/>
       <x:c r="F105" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="22" t="s">
-        <x:v>282</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C106" s="23" t="s"/>
       <x:c r="D106" s="23" t="s"/>
       <x:c r="E106" s="23" t="s"/>
       <x:c r="F106" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="22" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C107" s="23" t="s"/>
       <x:c r="D107" s="23" t="s"/>
       <x:c r="E107" s="23" t="s"/>
       <x:c r="F107" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B108" s="22" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C108" s="23" t="s"/>
+      <x:c r="D108" s="23" t="s"/>
+      <x:c r="E108" s="23" t="s"/>
+      <x:c r="F108" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B108" s="25" t="s">
+    <x:row r="109" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B109" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C108" s="26" t="s"/>
-      <x:c r="D108" s="26" t="s"/>
-      <x:c r="E108" s="26" t="s"/>
-      <x:c r="F108" s="27" t="n">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C109" s="26" t="s"/>
+      <x:c r="D109" s="26" t="s"/>
+      <x:c r="E109" s="26" t="s"/>
+      <x:c r="F109" s="27" t="n">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
     <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10070,8 +10113,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B100:F100"/>
-    <x:mergeCell ref="B101:E101"/>
+    <x:mergeCell ref="B101:F101"/>
     <x:mergeCell ref="B102:E102"/>
     <x:mergeCell ref="B103:E103"/>
     <x:mergeCell ref="B104:E104"/>
@@ -10079,6 +10121,7 @@
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
+    <x:mergeCell ref="B109:E109"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -186,6 +186,60 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08339</x:t>
   </x:si>
   <x:si>
@@ -195,13 +249,13 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08337</x:t>
@@ -213,58 +267,40 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1316-566</x:t>
-  </x:si>
-  <x:si>
-    <x:t>szdasdqweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08134</x:t>
@@ -276,40 +312,55 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08148</x:t>
@@ -321,63 +372,12 @@
     <x:t>df</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
@@ -534,85 +534,139 @@
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08192</x:t>
@@ -624,43 +678,40 @@
     <x:t>asdweq</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -672,13 +723,40 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
@@ -690,75 +768,27 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08178</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08179</x:t>
   </x:si>
   <x:si>
@@ -772,30 +802,6 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5803,10 +5809,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="30">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J11" s="29" t="s">
         <x:v>55</x:v>
@@ -5815,7 +5821,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
         <x:v>20</x:v>
@@ -5841,10 +5847,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="30">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J12" s="29" t="s">
         <x:v>58</x:v>
@@ -5853,7 +5859,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M12" s="28" t="s">
         <x:v>20</x:v>
@@ -5879,10 +5885,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J13" s="29" t="s">
         <x:v>61</x:v>
@@ -5891,7 +5897,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M13" s="28" t="s">
         <x:v>20</x:v>
@@ -5955,19 +5961,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="30">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I15" s="30">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J15" s="29" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M15" s="28" t="s">
         <x:v>20</x:v>
@@ -5993,10 +5999,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="30">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I16" s="30">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J16" s="29" t="s">
         <x:v>70</x:v>
@@ -6005,7 +6011,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M16" s="28" t="s">
         <x:v>20</x:v>
@@ -6031,19 +6037,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="30">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I17" s="30">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J17" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M17" s="28" t="s">
         <x:v>20</x:v>
@@ -6107,10 +6113,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="30">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I19" s="30">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J19" s="29" t="s">
         <x:v>79</x:v>
@@ -6119,7 +6125,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="32">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M19" s="28" t="s">
         <x:v>20</x:v>
@@ -6145,19 +6151,19 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="30">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I20" s="30">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J20" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="32">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M20" s="28" t="s">
         <x:v>20</x:v>
@@ -6177,25 +6183,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="28" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G21" s="28" t="s">
+      <x:c r="H21" s="30">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I21" s="30">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J21" s="29" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K21" s="31" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="32">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M21" s="28" t="s">
         <x:v>20</x:v>
@@ -6221,19 +6227,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="30">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I22" s="30">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="32">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M22" s="28" t="s">
         <x:v>20</x:v>
@@ -6253,25 +6259,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G23" s="28" t="s">
+      <x:c r="H23" s="30">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I23" s="30">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J23" s="29" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I23" s="30">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="32">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M23" s="28" t="s">
         <x:v>20</x:v>
@@ -6297,19 +6303,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="30">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I24" s="30">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J24" s="29" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="32">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M24" s="28" t="s">
         <x:v>20</x:v>
@@ -6329,25 +6335,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="28" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G25" s="28" t="s">
+      <x:c r="H25" s="30">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I25" s="30">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J25" s="29" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="H25" s="30">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I25" s="30">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J25" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="32">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M25" s="28" t="s">
         <x:v>20</x:v>
@@ -6373,10 +6379,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="30">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I26" s="30">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J26" s="29" t="s">
         <x:v>97</x:v>
@@ -6385,7 +6391,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="32">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M26" s="28" t="s">
         <x:v>20</x:v>
@@ -6601,19 +6607,19 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="30">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I32" s="30">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J32" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="32">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M32" s="28" t="s">
         <x:v>20</x:v>
@@ -6633,25 +6639,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="28" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G33" s="28" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="30">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I33" s="30">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J33" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="32">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M33" s="28" t="s">
         <x:v>20</x:v>
@@ -6721,7 +6727,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J35" s="29" t="s">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
         <x:v>210</x:v>
@@ -7063,7 +7069,7 @@
         <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J44" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
         <x:v>210</x:v>
@@ -7215,7 +7221,7 @@
         <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J48" s="29" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
         <x:v>210</x:v>
@@ -7291,7 +7297,7 @@
         <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J50" s="29" t="s">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
         <x:v>210</x:v>
@@ -7437,19 +7443,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="30">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I54" s="30">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J54" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="32">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M54" s="28" t="s">
         <x:v>20</x:v>
@@ -7469,25 +7475,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="28" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G55" s="28" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H55" s="30">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I55" s="30">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J55" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="32">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M55" s="28" t="s">
         <x:v>20</x:v>
@@ -7507,16 +7513,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G56" s="28" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="30">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I56" s="30">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J56" s="29" t="s">
         <x:v>29</x:v>
@@ -7525,7 +7531,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="32">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M56" s="28" t="s">
         <x:v>20</x:v>
@@ -7545,25 +7551,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="28" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G57" s="28" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H57" s="30">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I57" s="30">
-        <x:v>46124.704475463</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J57" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="32">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M57" s="28" t="s">
         <x:v>20</x:v>
@@ -7589,10 +7595,10 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H58" s="30">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I58" s="30">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J58" s="29" t="s">
         <x:v>181</x:v>
@@ -7601,7 +7607,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="32">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M58" s="28" t="s">
         <x:v>20</x:v>
@@ -7627,10 +7633,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H59" s="30">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I59" s="30">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J59" s="29" t="s">
         <x:v>184</x:v>
@@ -7639,7 +7645,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="32">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M59" s="28" t="s">
         <x:v>20</x:v>
@@ -7665,19 +7671,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H60" s="30">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I60" s="30">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J60" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K60" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="32">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M60" s="28" t="s">
         <x:v>20</x:v>
@@ -7697,25 +7703,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="28" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G61" s="28" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H61" s="30">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I61" s="30">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J61" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K61" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="32">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M61" s="28" t="s">
         <x:v>20</x:v>
@@ -7741,10 +7747,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H62" s="30">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I62" s="30">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J62" s="29" t="s">
         <x:v>192</x:v>
@@ -7753,7 +7759,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="32">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M62" s="28" t="s">
         <x:v>20</x:v>
@@ -7779,10 +7785,10 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H63" s="30">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I63" s="30">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J63" s="29" t="s">
         <x:v>195</x:v>
@@ -7791,7 +7797,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="32">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M63" s="28" t="s">
         <x:v>20</x:v>
@@ -7817,10 +7823,10 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="H64" s="30">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I64" s="30">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J64" s="29" t="s">
         <x:v>198</x:v>
@@ -7829,7 +7835,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="32">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M64" s="28" t="s">
         <x:v>20</x:v>
@@ -7855,19 +7861,19 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H65" s="30">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I65" s="30">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J65" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K65" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="32">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M65" s="28" t="s">
         <x:v>20</x:v>
@@ -7887,25 +7893,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="28" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G66" s="28" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G66" s="28" t="s">
+      <x:c r="H66" s="30">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I66" s="30">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J66" s="29" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="H66" s="30">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I66" s="30">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J66" s="29" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K66" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="32">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M66" s="28" t="s">
         <x:v>20</x:v>
@@ -7931,19 +7937,19 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="H67" s="30">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I67" s="30">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J67" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K67" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="32">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M67" s="28" t="s">
         <x:v>20</x:v>
@@ -7963,25 +7969,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="28" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G68" s="28" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G68" s="28" t="s">
+      <x:c r="H68" s="30">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I68" s="30">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J68" s="29" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="H68" s="30">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I68" s="30">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J68" s="29" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K68" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="32">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M68" s="28" t="s">
         <x:v>20</x:v>
@@ -8007,19 +8013,19 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="H69" s="30">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I69" s="30">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J69" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K69" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="32">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M69" s="28" t="s">
         <x:v>20</x:v>
@@ -8039,25 +8045,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="28" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G70" s="28" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G70" s="28" t="s">
+      <x:c r="H70" s="30">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I70" s="30">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J70" s="29" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="H70" s="30">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I70" s="30">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J70" s="29" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="K70" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="32">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M70" s="28" t="s">
         <x:v>20</x:v>
@@ -8077,25 +8083,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="28" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G71" s="28" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G71" s="28" t="s">
+      <x:c r="H71" s="30">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I71" s="30">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J71" s="29" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="H71" s="30">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I71" s="30">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J71" s="29" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="K71" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="32">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M71" s="28" t="s">
         <x:v>20</x:v>
@@ -8115,25 +8121,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="28" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G72" s="28" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G72" s="28" t="s">
+      <x:c r="H72" s="30">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I72" s="30">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J72" s="29" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="H72" s="30">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I72" s="30">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J72" s="29" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="K72" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="32">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M72" s="28" t="s">
         <x:v>20</x:v>
@@ -8153,10 +8159,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="28" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G73" s="28" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="G73" s="28" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="H73" s="30">
         <x:v>46122.3879258681</x:v>
@@ -8165,7 +8171,7 @@
         <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J73" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K73" s="31" t="n">
         <x:v>210</x:v>
@@ -8191,10 +8197,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="28" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G74" s="28" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="G74" s="28" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="H74" s="30">
         <x:v>46122.3885020718</x:v>
@@ -8229,10 +8235,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="28" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G75" s="28" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="G75" s="28" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="H75" s="30">
         <x:v>46122.3974322338</x:v>
@@ -8241,7 +8247,7 @@
         <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J75" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K75" s="31" t="n">
         <x:v>210</x:v>
@@ -8267,25 +8273,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="28" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G76" s="28" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G76" s="28" t="s">
+      <x:c r="H76" s="30">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I76" s="30">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J76" s="29" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="H76" s="30">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I76" s="30">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J76" s="29" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="K76" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="32">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M76" s="28" t="s">
         <x:v>20</x:v>
@@ -8305,25 +8311,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="28" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G77" s="28" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G77" s="28" t="s">
+      <x:c r="H77" s="30">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I77" s="30">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J77" s="29" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="H77" s="30">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I77" s="30">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J77" s="29" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="K77" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="32">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M77" s="28" t="s">
         <x:v>20</x:v>
@@ -8425,19 +8431,19 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="H80" s="30">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I80" s="30">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J80" s="29" t="s">
-        <x:v>239</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K80" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="32">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M80" s="28" t="s">
         <x:v>20</x:v>
@@ -8457,25 +8463,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="28" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G81" s="28" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G81" s="28" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="H81" s="30">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I81" s="30">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J81" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K81" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="32">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M81" s="28" t="s">
         <x:v>20</x:v>
@@ -8495,25 +8501,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="28" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G82" s="28" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G82" s="28" t="s">
+      <x:c r="H82" s="30">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I82" s="30">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J82" s="29" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="H82" s="30">
-        <x:v>46122.6795081481</x:v>
-      </x:c>
-      <x:c r="I82" s="30">
-        <x:v>46122.6802186921</x:v>
-      </x:c>
-      <x:c r="J82" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K82" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="32">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M82" s="28" t="s">
         <x:v>20</x:v>
@@ -8539,10 +8545,10 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="H83" s="30">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I83" s="30">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J83" s="29" t="s">
         <x:v>246</x:v>
@@ -8551,7 +8557,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="32">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M83" s="28" t="s">
         <x:v>20</x:v>
@@ -8577,10 +8583,10 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="H84" s="30">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I84" s="30">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J84" s="29" t="s">
         <x:v>29</x:v>
@@ -8589,7 +8595,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="32">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M84" s="28" t="s">
         <x:v>20</x:v>
@@ -8653,19 +8659,19 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="H86" s="30">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I86" s="30">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J86" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K86" s="31" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="32">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M86" s="28" t="s">
         <x:v>20</x:v>
@@ -8691,10 +8697,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="H87" s="30">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I87" s="30">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J87" s="29" t="s">
         <x:v>256</x:v>
@@ -8703,7 +8709,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="32">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M87" s="28" t="s">
         <x:v>20</x:v>
@@ -8711,10 +8717,10 @@
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
       <x:c r="B88" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C88" s="28" t="s">
-        <x:v>258</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D88" s="29" t="s">
         <x:v>15</x:v>
@@ -8723,25 +8729,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="28" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G88" s="28" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H88" s="30">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I88" s="30">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J88" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K88" s="31" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="32">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M88" s="28" t="s">
         <x:v>20</x:v>
@@ -8749,10 +8755,10 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C89" s="28" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="D89" s="29" t="s">
         <x:v>15</x:v>
@@ -8761,25 +8767,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="28" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G89" s="28" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H89" s="30">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I89" s="30">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J89" s="29" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="G89" s="28" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H89" s="30">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I89" s="30">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J89" s="29" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K89" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L89" s="32">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M89" s="28" t="s">
         <x:v>20</x:v>
@@ -8787,10 +8793,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C90" s="28" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D90" s="29" t="s">
         <x:v>15</x:v>
@@ -8799,25 +8805,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="28" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G90" s="28" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="G90" s="28" t="s">
-        <x:v>267</x:v>
-      </x:c>
       <x:c r="H90" s="30">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I90" s="30">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J90" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K90" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="32">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M90" s="28" t="s">
         <x:v>20</x:v>
@@ -8825,10 +8831,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C91" s="28" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D91" s="29" t="s">
         <x:v>15</x:v>
@@ -8837,25 +8843,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F91" s="28" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G91" s="28" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H91" s="30">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I91" s="30">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J91" s="29" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="G91" s="28" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H91" s="30">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I91" s="30">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J91" s="29" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="K91" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="32">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M91" s="28" t="s">
         <x:v>20</x:v>
@@ -8863,10 +8869,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C92" s="28" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D92" s="29" t="s">
         <x:v>15</x:v>
@@ -8875,25 +8881,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F92" s="28" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G92" s="28" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H92" s="30">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I92" s="30">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J92" s="29" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="G92" s="28" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H92" s="30">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I92" s="30">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J92" s="29" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K92" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="32">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M92" s="28" t="s">
         <x:v>20</x:v>
@@ -8901,10 +8907,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C93" s="28" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D93" s="29" t="s">
         <x:v>15</x:v>
@@ -8913,25 +8919,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F93" s="28" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G93" s="28" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="G93" s="28" t="s">
-        <x:v>278</x:v>
-      </x:c>
       <x:c r="H93" s="30">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I93" s="30">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J93" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K93" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="32">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M93" s="28" t="s">
         <x:v>20</x:v>
@@ -8939,10 +8945,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C94" s="28" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="D94" s="29" t="s">
         <x:v>15</x:v>
@@ -8957,19 +8963,19 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="H94" s="30">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I94" s="30">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J94" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K94" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="32">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M94" s="28" t="s">
         <x:v>20</x:v>
@@ -8977,10 +8983,10 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="28" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C95" s="28" t="s">
-        <x:v>49</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="D95" s="29" t="s">
         <x:v>15</x:v>
@@ -8989,25 +8995,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F95" s="28" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G95" s="28" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G95" s="28" t="s">
+      <x:c r="H95" s="30">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I95" s="30">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J95" s="29" t="s">
         <x:v>283</x:v>
-      </x:c>
-      <x:c r="H95" s="30">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I95" s="30">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J95" s="29" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K95" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="32">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M95" s="28" t="s">
         <x:v>20</x:v>
@@ -9015,35 +9021,37 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="28" t="s">
-        <x:v>284</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C96" s="28" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="D96" s="29" t="s"/>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D96" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E96" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F96" s="28" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G96" s="28" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H96" s="30">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I96" s="30">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J96" s="29" t="s">
-        <x:v>288</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K96" s="31" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="32">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M96" s="28" t="s">
         <x:v>20</x:v>
@@ -9051,37 +9059,35 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="28" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C97" s="28" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="D97" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D97" s="29" t="s"/>
       <x:c r="E97" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F97" s="28" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="G97" s="28" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="H97" s="30">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I97" s="30">
-        <x:v>46023</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J97" s="29" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="K97" s="31" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L97" s="32">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M97" s="28" t="s">
         <x:v>20</x:v>
@@ -9089,142 +9095,179 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="28" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C98" s="28" t="s">
-        <x:v>294</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D98" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E98" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F98" s="28" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G98" s="28" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H98" s="30">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I98" s="30">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J98" s="29" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="F98" s="28" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="G98" s="28" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H98" s="30">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I98" s="30">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J98" s="29" t="s">
-        <x:v>298</x:v>
-      </x:c>
       <x:c r="K98" s="31" t="n">
-        <x:v>3006</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="L98" s="32">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1624131829</x:v>
       </x:c>
       <x:c r="M98" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B99" s="28" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C99" s="28" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D99" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E99" s="28" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F99" s="28" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G99" s="28" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H99" s="30">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I99" s="30">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J99" s="29" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="K99" s="31" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L99" s="32">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M99" s="28" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B101" s="16" t="s">
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B102" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C101" s="17" t="s"/>
-      <x:c r="D101" s="17" t="s"/>
-      <x:c r="E101" s="18" t="s"/>
-      <x:c r="F101" s="18" t="s"/>
-    </x:row>
-    <x:row r="102" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B102" s="19" t="s">
+      <x:c r="C102" s="17" t="s"/>
+      <x:c r="D102" s="17" t="s"/>
+      <x:c r="E102" s="18" t="s"/>
+      <x:c r="F102" s="18" t="s"/>
+    </x:row>
+    <x:row r="103" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B103" s="19" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C102" s="20" t="s"/>
-      <x:c r="D102" s="20" t="s"/>
-      <x:c r="E102" s="20" t="s"/>
-      <x:c r="F102" s="21" t="s">
+      <x:c r="C103" s="20" t="s"/>
+      <x:c r="D103" s="20" t="s"/>
+      <x:c r="E103" s="20" t="s"/>
+      <x:c r="F103" s="21" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B103" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C103" s="23" t="s"/>
-      <x:c r="D103" s="23" t="s"/>
-      <x:c r="E103" s="23" t="s"/>
-      <x:c r="F103" s="24" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:28" ht="18" customHeight="1">
       <x:c r="B104" s="22" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C104" s="23" t="s"/>
       <x:c r="D104" s="23" t="s"/>
       <x:c r="E104" s="23" t="s"/>
       <x:c r="F104" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
       <x:c r="B105" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C105" s="23" t="s"/>
       <x:c r="D105" s="23" t="s"/>
       <x:c r="E105" s="23" t="s"/>
       <x:c r="F105" s="24" t="n">
-        <x:v>77</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="22" t="s">
-        <x:v>257</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C106" s="23" t="s"/>
       <x:c r="D106" s="23" t="s"/>
       <x:c r="E106" s="23" t="s"/>
       <x:c r="F106" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="22" t="s">
-        <x:v>284</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C107" s="23" t="s"/>
       <x:c r="D107" s="23" t="s"/>
       <x:c r="E107" s="23" t="s"/>
       <x:c r="F107" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="22" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C108" s="23" t="s"/>
       <x:c r="D108" s="23" t="s"/>
       <x:c r="E108" s="23" t="s"/>
       <x:c r="F108" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B109" s="22" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C109" s="23" t="s"/>
+      <x:c r="D109" s="23" t="s"/>
+      <x:c r="E109" s="23" t="s"/>
+      <x:c r="F109" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B109" s="25" t="s">
+    <x:row r="110" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B110" s="25" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C109" s="26" t="s"/>
-      <x:c r="D109" s="26" t="s"/>
-      <x:c r="E109" s="26" t="s"/>
-      <x:c r="F109" s="27" t="n">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C110" s="26" t="s"/>
+      <x:c r="D110" s="26" t="s"/>
+      <x:c r="E110" s="26" t="s"/>
+      <x:c r="F110" s="27" t="n">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
     <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10113,8 +10156,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B101:F101"/>
-    <x:mergeCell ref="B102:E102"/>
+    <x:mergeCell ref="B102:F102"/>
     <x:mergeCell ref="B103:E103"/>
     <x:mergeCell ref="B104:E104"/>
     <x:mergeCell ref="B105:E105"/>
@@ -10122,6 +10164,7 @@
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
     <x:mergeCell ref="B109:E109"/>
+    <x:mergeCell ref="B110:E110"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -985,7 +985,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1258,7 +1258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1269,7 +1269,10 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1342,7 +1345,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1377,7 +1380,11 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1745,17 +1752,17 @@
       <x:c r="B4" s="11">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -1782,80 +1789,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="H8" s="15">
         <x:v>46049.5726010069</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="15">
         <x:v>46049.5726341898</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L8" s="15">
         <x:v>46049.5962660532</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -1875,44 +1882,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2999,17 +3006,17 @@
       <x:c r="B4" s="11">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -3036,78 +3043,78 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s"/>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="H8" s="15">
         <x:v>46066.6004589236</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="15">
         <x:v>46066.6024709375</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L8" s="15">
         <x:v>46066.6040195139</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3127,44 +3134,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="16" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s"/>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="18" t="s"/>
-      <x:c r="F11" s="18" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="21" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="25" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4251,17 +4258,17 @@
       <x:c r="B4" s="11">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -4288,238 +4295,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="28" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="29" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="28" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="28" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="28" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H8" s="30">
+      <x:c r="H8" s="31">
         <x:v>46106.5066742245</x:v>
       </x:c>
-      <x:c r="I8" s="30">
+      <x:c r="I8" s="31">
         <x:v>46106.5082381134</x:v>
       </x:c>
-      <x:c r="J8" s="29" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="33">
         <x:v>46106.5099302546</x:v>
       </x:c>
-      <x:c r="M8" s="28" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="28" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="29" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F9" s="28" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G9" s="28" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H9" s="30">
+      <x:c r="H9" s="31">
         <x:v>46105.676846794</x:v>
       </x:c>
-      <x:c r="I9" s="30">
+      <x:c r="I9" s="31">
         <x:v>46106.5084437037</x:v>
       </x:c>
-      <x:c r="J9" s="29" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="32">
+      <x:c r="L9" s="33">
         <x:v>46106.5101144792</x:v>
       </x:c>
-      <x:c r="M9" s="28" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="28" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F10" s="28" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G10" s="28" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H10" s="30">
+      <x:c r="H10" s="31">
         <x:v>46105.6741278125</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>46106.5086548727</x:v>
       </x:c>
-      <x:c r="J10" s="29" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46106.5103567593</x:v>
       </x:c>
-      <x:c r="M10" s="28" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="28" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F11" s="28" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G11" s="28" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H11" s="30">
+      <x:c r="H11" s="31">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J11" s="29" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M11" s="28" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="16" t="s">
+      <x:c r="B14" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="s"/>
-      <x:c r="D14" s="17" t="s"/>
-      <x:c r="E14" s="18" t="s"/>
-      <x:c r="F14" s="18" t="s"/>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="19" t="s">
+      <x:c r="B15" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="21" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="B16" s="23" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="n">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="25" t="s">
+      <x:c r="B17" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -5603,17 +5610,17 @@
       <x:c r="B4" s="11">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -5640,3631 +5647,3631 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="28" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="29" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E8" s="28" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F8" s="28" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G8" s="28" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H8" s="30">
+      <x:c r="H8" s="31">
         <x:v>46118.3222074537</x:v>
       </x:c>
-      <x:c r="I8" s="30">
+      <x:c r="I8" s="31">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="29" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="33">
         <x:v>46118.3241166898</x:v>
       </x:c>
-      <x:c r="M8" s="28" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="28" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D9" s="29" t="s"/>
-      <x:c r="E9" s="28" t="s">
+      <x:c r="D9" s="30" t="s"/>
+      <x:c r="E9" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F9" s="28" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G9" s="28" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H9" s="30">
+      <x:c r="H9" s="31">
         <x:v>46126.0027495833</x:v>
       </x:c>
-      <x:c r="I9" s="30">
+      <x:c r="I9" s="31">
         <x:v>46126.1631260764</x:v>
       </x:c>
-      <x:c r="J9" s="29" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L9" s="32">
+      <x:c r="L9" s="33">
         <x:v>46126.177127963</x:v>
       </x:c>
-      <x:c r="M9" s="28" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="28" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D10" s="29" t="s"/>
-      <x:c r="E10" s="28" t="s">
+      <x:c r="D10" s="30" t="s"/>
+      <x:c r="E10" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F10" s="28" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G10" s="28" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H10" s="30">
+      <x:c r="H10" s="31">
         <x:v>46119.5290592824</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>46119.5300361458</x:v>
       </x:c>
-      <x:c r="J10" s="29" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46119.5304719792</x:v>
       </x:c>
-      <x:c r="M10" s="28" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="28" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F11" s="28" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G11" s="28" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H11" s="30">
+      <x:c r="H11" s="31">
         <x:v>46126.1388059144</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>46126.1498425347</x:v>
       </x:c>
-      <x:c r="J11" s="29" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46126.176386169</x:v>
       </x:c>
-      <x:c r="M11" s="28" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="28" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="28" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D12" s="29" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="28" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F12" s="28" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G12" s="28" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H12" s="30">
+      <x:c r="H12" s="31">
         <x:v>46126.1914900926</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>46126.2594011574</x:v>
       </x:c>
-      <x:c r="J12" s="29" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>46126.2601296875</x:v>
       </x:c>
-      <x:c r="M12" s="28" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="28" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D13" s="29" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="28" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F13" s="28" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G13" s="28" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H13" s="30">
+      <x:c r="H13" s="31">
         <x:v>46126.2608066551</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>46126.2618529282</x:v>
       </x:c>
-      <x:c r="J13" s="29" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>46126.2624254167</x:v>
       </x:c>
-      <x:c r="M13" s="28" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="28" t="s">
+      <x:c r="B14" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s">
+      <x:c r="C14" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D14" s="29" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="28" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F14" s="28" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G14" s="28" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H14" s="30">
+      <x:c r="H14" s="31">
         <x:v>46126.4381590509</x:v>
       </x:c>
-      <x:c r="I14" s="30">
+      <x:c r="I14" s="31">
         <x:v>46126.4434486343</x:v>
       </x:c>
-      <x:c r="J14" s="29" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L14" s="32">
+      <x:c r="L14" s="33">
         <x:v>46126.444417662</x:v>
       </x:c>
-      <x:c r="M14" s="28" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="28" t="s">
+      <x:c r="B15" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="s">
+      <x:c r="C15" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D15" s="29" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="28" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F15" s="28" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G15" s="28" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H15" s="30">
+      <x:c r="H15" s="31">
         <x:v>46124.9835281713</x:v>
       </x:c>
-      <x:c r="I15" s="30">
+      <x:c r="I15" s="31">
         <x:v>46125.0608962963</x:v>
       </x:c>
-      <x:c r="J15" s="29" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="K15" s="31" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L15" s="32">
+      <x:c r="L15" s="33">
         <x:v>46126.1641622569</x:v>
       </x:c>
-      <x:c r="M15" s="28" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+      <x:c r="B16" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s">
+      <x:c r="C16" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D16" s="29" t="s">
+      <x:c r="D16" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="28" t="s">
+      <x:c r="E16" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F16" s="28" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G16" s="28" t="s">
+      <x:c r="G16" s="29" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H16" s="30">
+      <x:c r="H16" s="31">
         <x:v>46126.455832662</x:v>
       </x:c>
-      <x:c r="I16" s="30">
+      <x:c r="I16" s="31">
         <x:v>46126.4740829051</x:v>
       </x:c>
-      <x:c r="J16" s="29" t="s">
+      <x:c r="J16" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L16" s="32">
+      <x:c r="L16" s="33">
         <x:v>46126.4751368866</x:v>
       </x:c>
-      <x:c r="M16" s="28" t="s">
+      <x:c r="M16" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="s">
+      <x:c r="C17" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D17" s="29" t="s">
+      <x:c r="D17" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="28" t="s">
+      <x:c r="E17" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F17" s="28" t="s">
+      <x:c r="F17" s="29" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G17" s="28" t="s">
+      <x:c r="G17" s="29" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H17" s="30">
+      <x:c r="H17" s="31">
         <x:v>46126.4716621296</x:v>
       </x:c>
-      <x:c r="I17" s="30">
+      <x:c r="I17" s="31">
         <x:v>46126.4737503704</x:v>
       </x:c>
-      <x:c r="J17" s="29" t="s">
+      <x:c r="J17" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K17" s="31" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L17" s="32">
+      <x:c r="L17" s="33">
         <x:v>46126.4748429977</x:v>
       </x:c>
-      <x:c r="M17" s="28" t="s">
+      <x:c r="M17" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+      <x:c r="B18" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="s">
+      <x:c r="C18" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D18" s="29" t="s">
+      <x:c r="D18" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="28" t="s">
+      <x:c r="E18" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F18" s="28" t="s">
+      <x:c r="F18" s="29" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G18" s="28" t="s">
+      <x:c r="G18" s="29" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H18" s="30">
+      <x:c r="H18" s="31">
         <x:v>46126.4798427199</x:v>
       </x:c>
-      <x:c r="I18" s="30">
+      <x:c r="I18" s="31">
         <x:v>46126.4809562153</x:v>
       </x:c>
-      <x:c r="J18" s="29" t="s">
+      <x:c r="J18" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="K18" s="31" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L18" s="32">
+      <x:c r="L18" s="33">
         <x:v>46126.4814216667</x:v>
       </x:c>
-      <x:c r="M18" s="28" t="s">
+      <x:c r="M18" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="28" t="s">
+      <x:c r="B19" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="28" t="s">
+      <x:c r="C19" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D19" s="29" t="s">
+      <x:c r="D19" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E19" s="28" t="s">
+      <x:c r="E19" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F19" s="28" t="s">
+      <x:c r="F19" s="29" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G19" s="28" t="s">
+      <x:c r="G19" s="29" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H19" s="30">
+      <x:c r="H19" s="31">
         <x:v>46126.4485157523</x:v>
       </x:c>
-      <x:c r="I19" s="30">
+      <x:c r="I19" s="31">
         <x:v>46126.4527227431</x:v>
       </x:c>
-      <x:c r="J19" s="29" t="s">
+      <x:c r="J19" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K19" s="31" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L19" s="32">
+      <x:c r="L19" s="33">
         <x:v>46126.4533495949</x:v>
       </x:c>
-      <x:c r="M19" s="28" t="s">
+      <x:c r="M19" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+      <x:c r="B20" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="s">
+      <x:c r="C20" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D20" s="29" t="s">
+      <x:c r="D20" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E20" s="28" t="s">
+      <x:c r="E20" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F20" s="28" t="s">
+      <x:c r="F20" s="29" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G20" s="28" t="s">
+      <x:c r="G20" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="H20" s="30">
+      <x:c r="H20" s="31">
         <x:v>46119.8029380671</x:v>
       </x:c>
-      <x:c r="I20" s="30">
+      <x:c r="I20" s="31">
         <x:v>46120.5237086343</x:v>
       </x:c>
-      <x:c r="J20" s="29" t="s">
+      <x:c r="J20" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K20" s="31" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L20" s="32">
+      <x:c r="L20" s="33">
         <x:v>46120.5257164468</x:v>
       </x:c>
-      <x:c r="M20" s="28" t="s">
+      <x:c r="M20" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="28" t="s">
+      <x:c r="B21" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="s">
+      <x:c r="C21" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D21" s="29" t="s">
+      <x:c r="D21" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E21" s="28" t="s">
+      <x:c r="E21" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F21" s="28" t="s">
+      <x:c r="F21" s="29" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G21" s="28" t="s">
+      <x:c r="G21" s="29" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H21" s="30">
+      <x:c r="H21" s="31">
         <x:v>46120.2349196412</x:v>
       </x:c>
-      <x:c r="I21" s="30">
+      <x:c r="I21" s="31">
         <x:v>46120.5229746296</x:v>
       </x:c>
-      <x:c r="J21" s="29" t="s">
+      <x:c r="J21" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K21" s="31" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="32">
+      <x:c r="L21" s="33">
         <x:v>46120.5255047106</x:v>
       </x:c>
-      <x:c r="M21" s="28" t="s">
+      <x:c r="M21" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="28" t="s">
+      <x:c r="B22" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="28" t="s">
+      <x:c r="C22" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D22" s="29" t="s">
+      <x:c r="D22" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E22" s="28" t="s">
+      <x:c r="E22" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F22" s="28" t="s">
+      <x:c r="F22" s="29" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G22" s="28" t="s">
+      <x:c r="G22" s="29" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="H22" s="30">
+      <x:c r="H22" s="31">
         <x:v>46120.2362105324</x:v>
       </x:c>
-      <x:c r="I22" s="30">
+      <x:c r="I22" s="31">
         <x:v>46120.5226826273</x:v>
       </x:c>
-      <x:c r="J22" s="29" t="s">
+      <x:c r="J22" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K22" s="31" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L22" s="32">
+      <x:c r="L22" s="33">
         <x:v>46120.5252627315</x:v>
       </x:c>
-      <x:c r="M22" s="28" t="s">
+      <x:c r="M22" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="28" t="s">
+      <x:c r="B23" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="28" t="s">
+      <x:c r="C23" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D23" s="29" t="s">
+      <x:c r="D23" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E23" s="28" t="s">
+      <x:c r="E23" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F23" s="28" t="s">
+      <x:c r="F23" s="29" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G23" s="28" t="s">
+      <x:c r="G23" s="29" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H23" s="30">
+      <x:c r="H23" s="31">
         <x:v>46120.2374046412</x:v>
       </x:c>
-      <x:c r="I23" s="30">
+      <x:c r="I23" s="31">
         <x:v>46120.5224942245</x:v>
       </x:c>
-      <x:c r="J23" s="29" t="s">
+      <x:c r="J23" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K23" s="31" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L23" s="32">
+      <x:c r="L23" s="33">
         <x:v>46120.5250032292</x:v>
       </x:c>
-      <x:c r="M23" s="28" t="s">
+      <x:c r="M23" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="28" t="s">
+      <x:c r="B24" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="s">
+      <x:c r="C24" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D24" s="29" t="s">
+      <x:c r="D24" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E24" s="28" t="s">
+      <x:c r="E24" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F24" s="28" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G24" s="28" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H24" s="30">
+      <x:c r="H24" s="31">
         <x:v>46120.7129542245</x:v>
       </x:c>
-      <x:c r="I24" s="30">
+      <x:c r="I24" s="31">
         <x:v>46121.100944213</x:v>
       </x:c>
-      <x:c r="J24" s="29" t="s">
+      <x:c r="J24" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K24" s="31" t="n">
+      <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L24" s="32">
+      <x:c r="L24" s="33">
         <x:v>46121.1029720949</x:v>
       </x:c>
-      <x:c r="M24" s="28" t="s">
+      <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="28" t="s">
+      <x:c r="B25" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C25" s="28" t="s">
+      <x:c r="C25" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D25" s="29" t="s">
+      <x:c r="D25" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E25" s="28" t="s">
+      <x:c r="E25" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F25" s="28" t="s">
+      <x:c r="F25" s="29" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G25" s="28" t="s">
+      <x:c r="G25" s="29" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H25" s="30">
+      <x:c r="H25" s="31">
         <x:v>46121.0999663542</x:v>
       </x:c>
-      <x:c r="I25" s="30">
+      <x:c r="I25" s="31">
         <x:v>46121.1007466204</x:v>
       </x:c>
-      <x:c r="J25" s="29" t="s">
+      <x:c r="J25" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="K25" s="31" t="n">
+      <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L25" s="32">
+      <x:c r="L25" s="33">
         <x:v>46121.1027298958</x:v>
       </x:c>
-      <x:c r="M25" s="28" t="s">
+      <x:c r="M25" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="28" t="s">
+      <x:c r="B26" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C26" s="28" t="s">
+      <x:c r="C26" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D26" s="29" t="s">
+      <x:c r="D26" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E26" s="28" t="s">
+      <x:c r="E26" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F26" s="28" t="s">
+      <x:c r="F26" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G26" s="28" t="s">
+      <x:c r="G26" s="29" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H26" s="30">
+      <x:c r="H26" s="31">
         <x:v>46122.1996025926</x:v>
       </x:c>
-      <x:c r="I26" s="30">
+      <x:c r="I26" s="31">
         <x:v>46122.2050823032</x:v>
       </x:c>
-      <x:c r="J26" s="29" t="s">
+      <x:c r="J26" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="K26" s="31" t="n">
+      <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L26" s="32">
+      <x:c r="L26" s="33">
         <x:v>46122.2083635185</x:v>
       </x:c>
-      <x:c r="M26" s="28" t="s">
+      <x:c r="M26" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="28" t="s">
+      <x:c r="B27" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C27" s="28" t="s">
+      <x:c r="C27" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D27" s="29" t="s">
+      <x:c r="D27" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E27" s="28" t="s">
+      <x:c r="E27" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F27" s="28" t="s">
+      <x:c r="F27" s="29" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G27" s="28" t="s">
+      <x:c r="G27" s="29" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H27" s="30">
+      <x:c r="H27" s="31">
         <x:v>46121.2464636111</x:v>
       </x:c>
-      <x:c r="I27" s="30">
+      <x:c r="I27" s="31">
         <x:v>46121.3217277662</x:v>
       </x:c>
-      <x:c r="J27" s="29" t="s">
+      <x:c r="J27" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K27" s="31" t="n">
+      <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="33">
         <x:v>46121.498248206</x:v>
       </x:c>
-      <x:c r="M27" s="28" t="s">
+      <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="28" t="s">
+      <x:c r="B28" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C28" s="28" t="s">
+      <x:c r="C28" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D28" s="29" t="s">
+      <x:c r="D28" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E28" s="28" t="s">
+      <x:c r="E28" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F28" s="28" t="s">
+      <x:c r="F28" s="29" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="28" t="s">
+      <x:c r="G28" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H28" s="30">
+      <x:c r="H28" s="31">
         <x:v>46121.4966047917</x:v>
       </x:c>
-      <x:c r="I28" s="30">
+      <x:c r="I28" s="31">
         <x:v>46121.4974146412</x:v>
       </x:c>
-      <x:c r="J28" s="29" t="s">
+      <x:c r="J28" s="30" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="K28" s="31" t="n">
+      <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L28" s="32">
+      <x:c r="L28" s="33">
         <x:v>46121.4980146875</x:v>
       </x:c>
-      <x:c r="M28" s="28" t="s">
+      <x:c r="M28" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="28" t="s">
+      <x:c r="B29" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C29" s="28" t="s">
+      <x:c r="C29" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D29" s="29" t="s">
+      <x:c r="D29" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E29" s="28" t="s">
+      <x:c r="E29" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F29" s="28" t="s">
+      <x:c r="F29" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G29" s="28" t="s">
+      <x:c r="G29" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H29" s="30">
+      <x:c r="H29" s="31">
         <x:v>46121.5149441551</x:v>
       </x:c>
-      <x:c r="I29" s="30">
+      <x:c r="I29" s="31">
         <x:v>46122.2067431944</x:v>
       </x:c>
-      <x:c r="J29" s="29" t="s">
+      <x:c r="J29" s="30" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="K29" s="31" t="n">
+      <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L29" s="32">
+      <x:c r="L29" s="33">
         <x:v>46122.2310990278</x:v>
       </x:c>
-      <x:c r="M29" s="28" t="s">
+      <x:c r="M29" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="28" t="s">
+      <x:c r="B30" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C30" s="28" t="s">
+      <x:c r="C30" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D30" s="29" t="s">
+      <x:c r="D30" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E30" s="28" t="s">
+      <x:c r="E30" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F30" s="28" t="s">
+      <x:c r="F30" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G30" s="28" t="s">
+      <x:c r="G30" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H30" s="30">
+      <x:c r="H30" s="31">
         <x:v>46121.5178724884</x:v>
       </x:c>
-      <x:c r="I30" s="30">
+      <x:c r="I30" s="31">
         <x:v>46122.2064690394</x:v>
       </x:c>
-      <x:c r="J30" s="29" t="s">
+      <x:c r="J30" s="30" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K30" s="31" t="n">
+      <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L30" s="32">
+      <x:c r="L30" s="33">
         <x:v>46122.230922581</x:v>
       </x:c>
-      <x:c r="M30" s="28" t="s">
+      <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="28" t="s">
+      <x:c r="B31" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C31" s="28" t="s">
+      <x:c r="C31" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D31" s="29" t="s">
+      <x:c r="D31" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E31" s="28" t="s">
+      <x:c r="E31" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F31" s="28" t="s">
+      <x:c r="F31" s="29" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G31" s="28" t="s">
+      <x:c r="G31" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="H31" s="30">
+      <x:c r="H31" s="31">
         <x:v>46119.8023724884</x:v>
       </x:c>
-      <x:c r="I31" s="30">
+      <x:c r="I31" s="31">
         <x:v>46119.8046602662</x:v>
       </x:c>
-      <x:c r="J31" s="29" t="s">
+      <x:c r="J31" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K31" s="31" t="n">
+      <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L31" s="32">
+      <x:c r="L31" s="33">
         <x:v>46119.8055532407</x:v>
       </x:c>
-      <x:c r="M31" s="28" t="s">
+      <x:c r="M31" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="28" t="s">
+      <x:c r="B32" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C32" s="28" t="s">
+      <x:c r="C32" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D32" s="29" t="s">
+      <x:c r="D32" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E32" s="28" t="s">
+      <x:c r="E32" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F32" s="28" t="s">
+      <x:c r="F32" s="29" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G32" s="28" t="s">
+      <x:c r="G32" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H32" s="30">
+      <x:c r="H32" s="31">
         <x:v>46121.5183984954</x:v>
       </x:c>
-      <x:c r="I32" s="30">
+      <x:c r="I32" s="31">
         <x:v>46122.2061737153</x:v>
       </x:c>
-      <x:c r="J32" s="29" t="s">
+      <x:c r="J32" s="30" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="K32" s="31" t="n">
+      <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L32" s="32">
+      <x:c r="L32" s="33">
         <x:v>46122.2307100926</x:v>
       </x:c>
-      <x:c r="M32" s="28" t="s">
+      <x:c r="M32" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="28" t="s">
+      <x:c r="B33" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C33" s="28" t="s">
+      <x:c r="C33" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D33" s="29" t="s">
+      <x:c r="D33" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E33" s="28" t="s">
+      <x:c r="E33" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F33" s="28" t="s">
+      <x:c r="F33" s="29" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G33" s="28" t="s">
+      <x:c r="G33" s="29" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="H33" s="30">
+      <x:c r="H33" s="31">
         <x:v>46122.1299166204</x:v>
       </x:c>
-      <x:c r="I33" s="30">
+      <x:c r="I33" s="31">
         <x:v>46122.2059087963</x:v>
       </x:c>
-      <x:c r="J33" s="29" t="s">
+      <x:c r="J33" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K33" s="31" t="n">
+      <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L33" s="32">
+      <x:c r="L33" s="33">
         <x:v>46122.2086237847</x:v>
       </x:c>
-      <x:c r="M33" s="28" t="s">
+      <x:c r="M33" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="28" t="s">
+      <x:c r="B34" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C34" s="28" t="s">
+      <x:c r="C34" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D34" s="29" t="s">
+      <x:c r="D34" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E34" s="28" t="s">
+      <x:c r="E34" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F34" s="28" t="s">
+      <x:c r="F34" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G34" s="28" t="s">
+      <x:c r="G34" s="29" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H34" s="30">
+      <x:c r="H34" s="31">
         <x:v>46121.2273626852</x:v>
       </x:c>
-      <x:c r="I34" s="30">
+      <x:c r="I34" s="31">
         <x:v>46121.228379213</x:v>
       </x:c>
-      <x:c r="J34" s="29" t="s">
+      <x:c r="J34" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K34" s="31" t="n">
+      <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L34" s="32">
+      <x:c r="L34" s="33">
         <x:v>46121.2291153125</x:v>
       </x:c>
-      <x:c r="M34" s="28" t="s">
+      <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="28" t="s">
+      <x:c r="B35" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C35" s="28" t="s">
+      <x:c r="C35" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D35" s="29" t="s">
+      <x:c r="D35" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E35" s="28" t="s">
+      <x:c r="E35" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F35" s="28" t="s">
+      <x:c r="F35" s="29" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G35" s="28" t="s">
+      <x:c r="G35" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H35" s="30">
+      <x:c r="H35" s="31">
         <x:v>46119.8017436343</x:v>
       </x:c>
-      <x:c r="I35" s="30">
+      <x:c r="I35" s="31">
         <x:v>46119.8048384144</x:v>
       </x:c>
-      <x:c r="J35" s="29" t="s">
+      <x:c r="J35" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K35" s="31" t="n">
+      <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L35" s="32">
+      <x:c r="L35" s="33">
         <x:v>46119.8080510417</x:v>
       </x:c>
-      <x:c r="M35" s="28" t="s">
+      <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="28" t="s">
+      <x:c r="B36" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C36" s="28" t="s">
+      <x:c r="C36" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D36" s="29" t="s">
+      <x:c r="D36" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E36" s="28" t="s">
+      <x:c r="E36" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F36" s="28" t="s">
+      <x:c r="F36" s="29" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G36" s="28" t="s">
+      <x:c r="G36" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H36" s="30">
+      <x:c r="H36" s="31">
         <x:v>46119.5434206134</x:v>
       </x:c>
-      <x:c r="I36" s="30">
+      <x:c r="I36" s="31">
         <x:v>46119.545474919</x:v>
       </x:c>
-      <x:c r="J36" s="29" t="s">
+      <x:c r="J36" s="30" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="K36" s="31" t="n">
+      <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L36" s="32">
+      <x:c r="L36" s="33">
         <x:v>46119.5469447569</x:v>
       </x:c>
-      <x:c r="M36" s="28" t="s">
+      <x:c r="M36" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="28" t="s">
+      <x:c r="B37" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C37" s="28" t="s">
+      <x:c r="C37" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D37" s="29" t="s">
+      <x:c r="D37" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E37" s="28" t="s">
+      <x:c r="E37" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F37" s="28" t="s">
+      <x:c r="F37" s="29" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G37" s="28" t="s">
+      <x:c r="G37" s="29" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H37" s="30">
+      <x:c r="H37" s="31">
         <x:v>46119.729231331</x:v>
       </x:c>
-      <x:c r="I37" s="30">
+      <x:c r="I37" s="31">
         <x:v>46119.7316308565</x:v>
       </x:c>
-      <x:c r="J37" s="29" t="s">
+      <x:c r="J37" s="30" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="K37" s="31" t="n">
+      <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L37" s="32">
+      <x:c r="L37" s="33">
         <x:v>46119.7327704398</x:v>
       </x:c>
-      <x:c r="M37" s="28" t="s">
+      <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="28" t="s">
+      <x:c r="B38" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C38" s="28" t="s">
+      <x:c r="C38" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D38" s="29" t="s">
+      <x:c r="D38" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E38" s="28" t="s">
+      <x:c r="E38" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F38" s="28" t="s">
+      <x:c r="F38" s="29" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G38" s="28" t="s">
+      <x:c r="G38" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="H38" s="30">
+      <x:c r="H38" s="31">
         <x:v>46118.4219285995</x:v>
       </x:c>
-      <x:c r="I38" s="30">
+      <x:c r="I38" s="31">
         <x:v>46118.4229350116</x:v>
       </x:c>
-      <x:c r="J38" s="29" t="s">
+      <x:c r="J38" s="30" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="K38" s="31" t="n">
+      <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L38" s="32">
+      <x:c r="L38" s="33">
         <x:v>46118.4241364815</x:v>
       </x:c>
-      <x:c r="M38" s="28" t="s">
+      <x:c r="M38" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="28" t="s">
+      <x:c r="B39" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C39" s="28" t="s">
+      <x:c r="C39" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D39" s="29" t="s">
+      <x:c r="D39" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E39" s="28" t="s">
+      <x:c r="E39" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F39" s="28" t="s">
+      <x:c r="F39" s="29" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G39" s="28" t="s">
+      <x:c r="G39" s="29" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="H39" s="30">
+      <x:c r="H39" s="31">
         <x:v>46118.7424944097</x:v>
       </x:c>
-      <x:c r="I39" s="30">
+      <x:c r="I39" s="31">
         <x:v>46118.7432728009</x:v>
       </x:c>
-      <x:c r="J39" s="29" t="s">
+      <x:c r="J39" s="30" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="K39" s="31" t="n">
+      <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L39" s="32">
+      <x:c r="L39" s="33">
         <x:v>46118.743899213</x:v>
       </x:c>
-      <x:c r="M39" s="28" t="s">
+      <x:c r="M39" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="28" t="s">
+      <x:c r="B40" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C40" s="28" t="s">
+      <x:c r="C40" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D40" s="29" t="s">
+      <x:c r="D40" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E40" s="28" t="s">
+      <x:c r="E40" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F40" s="28" t="s">
+      <x:c r="F40" s="29" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G40" s="28" t="s">
+      <x:c r="G40" s="29" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H40" s="30">
+      <x:c r="H40" s="31">
         <x:v>46118.7562945255</x:v>
       </x:c>
-      <x:c r="I40" s="30">
+      <x:c r="I40" s="31">
         <x:v>46118.7571720255</x:v>
       </x:c>
-      <x:c r="J40" s="29" t="s">
+      <x:c r="J40" s="30" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="K40" s="31" t="n">
+      <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L40" s="32">
+      <x:c r="L40" s="33">
         <x:v>46118.7577859143</x:v>
       </x:c>
-      <x:c r="M40" s="28" t="s">
+      <x:c r="M40" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="28" t="s">
+      <x:c r="B41" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C41" s="28" t="s">
+      <x:c r="C41" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D41" s="29" t="s">
+      <x:c r="D41" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E41" s="28" t="s">
+      <x:c r="E41" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F41" s="28" t="s">
+      <x:c r="F41" s="29" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G41" s="28" t="s">
+      <x:c r="G41" s="29" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H41" s="30">
+      <x:c r="H41" s="31">
         <x:v>46119.0668949653</x:v>
       </x:c>
-      <x:c r="I41" s="30">
+      <x:c r="I41" s="31">
         <x:v>46119.0755180324</x:v>
       </x:c>
-      <x:c r="J41" s="29" t="s">
+      <x:c r="J41" s="30" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="K41" s="31" t="n">
+      <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L41" s="32">
+      <x:c r="L41" s="33">
         <x:v>46119.076169375</x:v>
       </x:c>
-      <x:c r="M41" s="28" t="s">
+      <x:c r="M41" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="28" t="s">
+      <x:c r="B42" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C42" s="28" t="s">
+      <x:c r="C42" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D42" s="29" t="s">
+      <x:c r="D42" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E42" s="28" t="s">
+      <x:c r="E42" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F42" s="28" t="s">
+      <x:c r="F42" s="29" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G42" s="28" t="s">
+      <x:c r="G42" s="29" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="H42" s="30">
+      <x:c r="H42" s="31">
         <x:v>46119.0739296412</x:v>
       </x:c>
-      <x:c r="I42" s="30">
+      <x:c r="I42" s="31">
         <x:v>46119.0753097685</x:v>
       </x:c>
-      <x:c r="J42" s="29" t="s">
+      <x:c r="J42" s="30" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="K42" s="31" t="n">
+      <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L42" s="32">
+      <x:c r="L42" s="33">
         <x:v>46119.0764109954</x:v>
       </x:c>
-      <x:c r="M42" s="28" t="s">
+      <x:c r="M42" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="28" t="s">
+      <x:c r="B43" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C43" s="28" t="s">
+      <x:c r="C43" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D43" s="29" t="s">
+      <x:c r="D43" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E43" s="28" t="s">
+      <x:c r="E43" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F43" s="28" t="s">
+      <x:c r="F43" s="29" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G43" s="28" t="s">
+      <x:c r="G43" s="29" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H43" s="30">
+      <x:c r="H43" s="31">
         <x:v>46119.1921340856</x:v>
       </x:c>
-      <x:c r="I43" s="30">
+      <x:c r="I43" s="31">
         <x:v>46119.1932160417</x:v>
       </x:c>
-      <x:c r="J43" s="29" t="s">
+      <x:c r="J43" s="30" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="K43" s="31" t="n">
+      <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L43" s="32">
+      <x:c r="L43" s="33">
         <x:v>46119.193627581</x:v>
       </x:c>
-      <x:c r="M43" s="28" t="s">
+      <x:c r="M43" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="28" t="s">
+      <x:c r="B44" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C44" s="28" t="s">
+      <x:c r="C44" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D44" s="29" t="s">
+      <x:c r="D44" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E44" s="28" t="s">
+      <x:c r="E44" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F44" s="28" t="s">
+      <x:c r="F44" s="29" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G44" s="28" t="s">
+      <x:c r="G44" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H44" s="30">
+      <x:c r="H44" s="31">
         <x:v>46119.7297941435</x:v>
       </x:c>
-      <x:c r="I44" s="30">
+      <x:c r="I44" s="31">
         <x:v>46119.731450544</x:v>
       </x:c>
-      <x:c r="J44" s="29" t="s">
+      <x:c r="J44" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K44" s="31" t="n">
+      <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L44" s="32">
+      <x:c r="L44" s="33">
         <x:v>46119.7324832755</x:v>
       </x:c>
-      <x:c r="M44" s="28" t="s">
+      <x:c r="M44" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="28" t="s">
+      <x:c r="B45" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C45" s="28" t="s">
+      <x:c r="C45" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D45" s="29" t="s">
+      <x:c r="D45" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E45" s="28" t="s">
+      <x:c r="E45" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F45" s="28" t="s">
+      <x:c r="F45" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G45" s="28" t="s">
+      <x:c r="G45" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="H45" s="30">
+      <x:c r="H45" s="31">
         <x:v>46119.4681336458</x:v>
       </x:c>
-      <x:c r="I45" s="30">
+      <x:c r="I45" s="31">
         <x:v>46119.4697068056</x:v>
       </x:c>
-      <x:c r="J45" s="29" t="s">
+      <x:c r="J45" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K45" s="31" t="n">
+      <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L45" s="32">
+      <x:c r="L45" s="33">
         <x:v>46119.470392037</x:v>
       </x:c>
-      <x:c r="M45" s="28" t="s">
+      <x:c r="M45" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="28" t="s">
+      <x:c r="B46" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C46" s="28" t="s">
+      <x:c r="C46" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D46" s="29" t="s">
+      <x:c r="D46" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E46" s="28" t="s">
+      <x:c r="E46" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F46" s="28" t="s">
+      <x:c r="F46" s="29" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G46" s="28" t="s">
+      <x:c r="G46" s="29" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H46" s="30">
+      <x:c r="H46" s="31">
         <x:v>46119.5424612384</x:v>
       </x:c>
-      <x:c r="I46" s="30">
+      <x:c r="I46" s="31">
         <x:v>46119.5457934491</x:v>
       </x:c>
-      <x:c r="J46" s="29" t="s">
+      <x:c r="J46" s="30" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="K46" s="31" t="n">
+      <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L46" s="32">
+      <x:c r="L46" s="33">
         <x:v>46119.5465567708</x:v>
       </x:c>
-      <x:c r="M46" s="28" t="s">
+      <x:c r="M46" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="28" t="s">
+      <x:c r="B47" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C47" s="28" t="s">
+      <x:c r="C47" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D47" s="29" t="s">
+      <x:c r="D47" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E47" s="28" t="s">
+      <x:c r="E47" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F47" s="28" t="s">
+      <x:c r="F47" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G47" s="28" t="s">
+      <x:c r="G47" s="29" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="H47" s="30">
+      <x:c r="H47" s="31">
         <x:v>46119.542956794</x:v>
       </x:c>
-      <x:c r="I47" s="30">
+      <x:c r="I47" s="31">
         <x:v>46119.5456356481</x:v>
       </x:c>
-      <x:c r="J47" s="29" t="s">
+      <x:c r="J47" s="30" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="K47" s="31" t="n">
+      <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L47" s="32">
+      <x:c r="L47" s="33">
         <x:v>46119.5477968982</x:v>
       </x:c>
-      <x:c r="M47" s="28" t="s">
+      <x:c r="M47" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="28" t="s">
+      <x:c r="B48" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C48" s="28" t="s">
+      <x:c r="C48" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D48" s="29" t="s">
+      <x:c r="D48" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E48" s="28" t="s">
+      <x:c r="E48" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F48" s="28" t="s">
+      <x:c r="F48" s="29" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="G48" s="28" t="s">
+      <x:c r="G48" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="H48" s="30">
+      <x:c r="H48" s="31">
         <x:v>46122.2429836343</x:v>
       </x:c>
-      <x:c r="I48" s="30">
+      <x:c r="I48" s="31">
         <x:v>46122.244317963</x:v>
       </x:c>
-      <x:c r="J48" s="29" t="s">
+      <x:c r="J48" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K48" s="31" t="n">
+      <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L48" s="32">
+      <x:c r="L48" s="33">
         <x:v>46122.2448800694</x:v>
       </x:c>
-      <x:c r="M48" s="28" t="s">
+      <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B49" s="28" t="s">
+      <x:c r="B49" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C49" s="28" t="s">
+      <x:c r="C49" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D49" s="29" t="s">
+      <x:c r="D49" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E49" s="28" t="s">
+      <x:c r="E49" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F49" s="28" t="s">
+      <x:c r="F49" s="29" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G49" s="28" t="s">
+      <x:c r="G49" s="29" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H49" s="30">
+      <x:c r="H49" s="31">
         <x:v>46119.5439653357</x:v>
       </x:c>
-      <x:c r="I49" s="30">
+      <x:c r="I49" s="31">
         <x:v>46119.5452984143</x:v>
       </x:c>
-      <x:c r="J49" s="29" t="s">
+      <x:c r="J49" s="30" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="K49" s="31" t="n">
+      <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L49" s="32">
+      <x:c r="L49" s="33">
         <x:v>46119.5467543982</x:v>
       </x:c>
-      <x:c r="M49" s="28" t="s">
+      <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="28" t="s">
+      <x:c r="B50" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C50" s="28" t="s">
+      <x:c r="C50" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D50" s="29" t="s">
+      <x:c r="D50" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E50" s="28" t="s">
+      <x:c r="E50" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F50" s="28" t="s">
+      <x:c r="F50" s="29" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="G50" s="28" t="s">
+      <x:c r="G50" s="29" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="H50" s="30">
+      <x:c r="H50" s="31">
         <x:v>46119.7254171991</x:v>
       </x:c>
-      <x:c r="I50" s="30">
+      <x:c r="I50" s="31">
         <x:v>46119.7262936574</x:v>
       </x:c>
-      <x:c r="J50" s="29" t="s">
+      <x:c r="J50" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K50" s="31" t="n">
+      <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L50" s="32">
+      <x:c r="L50" s="33">
         <x:v>46119.7267657407</x:v>
       </x:c>
-      <x:c r="M50" s="28" t="s">
+      <x:c r="M50" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="28" t="s">
+      <x:c r="B51" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C51" s="28" t="s">
+      <x:c r="C51" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D51" s="29" t="s">
+      <x:c r="D51" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E51" s="28" t="s">
+      <x:c r="E51" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F51" s="28" t="s">
+      <x:c r="F51" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G51" s="28" t="s">
+      <x:c r="G51" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H51" s="30">
+      <x:c r="H51" s="31">
         <x:v>46119.7285584838</x:v>
       </x:c>
-      <x:c r="I51" s="30">
+      <x:c r="I51" s="31">
         <x:v>46119.7318005208</x:v>
       </x:c>
-      <x:c r="J51" s="29" t="s">
+      <x:c r="J51" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K51" s="31" t="n">
+      <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L51" s="32">
+      <x:c r="L51" s="33">
         <x:v>46119.7339888773</x:v>
       </x:c>
-      <x:c r="M51" s="28" t="s">
+      <x:c r="M51" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="28" t="s">
+      <x:c r="B52" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C52" s="28" t="s">
+      <x:c r="C52" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D52" s="29" t="s">
+      <x:c r="D52" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E52" s="28" t="s">
+      <x:c r="E52" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F52" s="28" t="s">
+      <x:c r="F52" s="29" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="G52" s="28" t="s">
+      <x:c r="G52" s="29" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="H52" s="30">
+      <x:c r="H52" s="31">
         <x:v>46119.5267212153</x:v>
       </x:c>
-      <x:c r="I52" s="30">
+      <x:c r="I52" s="31">
         <x:v>46119.5274664236</x:v>
       </x:c>
-      <x:c r="J52" s="29" t="s">
+      <x:c r="J52" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="K52" s="31" t="n">
+      <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L52" s="32">
+      <x:c r="L52" s="33">
         <x:v>46119.5279398495</x:v>
       </x:c>
-      <x:c r="M52" s="28" t="s">
+      <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="28" t="s">
+      <x:c r="B53" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C53" s="28" t="s">
+      <x:c r="C53" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D53" s="29" t="s">
+      <x:c r="D53" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E53" s="28" t="s">
+      <x:c r="E53" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F53" s="28" t="s">
+      <x:c r="F53" s="29" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G53" s="28" t="s">
+      <x:c r="G53" s="29" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="H53" s="30">
+      <x:c r="H53" s="31">
         <x:v>46122.3569147569</x:v>
       </x:c>
-      <x:c r="I53" s="30">
+      <x:c r="I53" s="31">
         <x:v>46122.3577305324</x:v>
       </x:c>
-      <x:c r="J53" s="29" t="s">
+      <x:c r="J53" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K53" s="31" t="n">
+      <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L53" s="32">
+      <x:c r="L53" s="33">
         <x:v>46122.3582679861</x:v>
       </x:c>
-      <x:c r="M53" s="28" t="s">
+      <x:c r="M53" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="28" t="s">
+      <x:c r="B54" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C54" s="28" t="s">
+      <x:c r="C54" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D54" s="29" t="s">
+      <x:c r="D54" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E54" s="28" t="s">
+      <x:c r="E54" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F54" s="28" t="s">
+      <x:c r="F54" s="29" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G54" s="28" t="s">
+      <x:c r="G54" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H54" s="30">
+      <x:c r="H54" s="31">
         <x:v>46122.3767795718</x:v>
       </x:c>
-      <x:c r="I54" s="30">
+      <x:c r="I54" s="31">
         <x:v>46122.3776183449</x:v>
       </x:c>
-      <x:c r="J54" s="29" t="s">
+      <x:c r="J54" s="30" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="K54" s="31" t="n">
+      <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L54" s="32">
+      <x:c r="L54" s="33">
         <x:v>46122.3780755324</x:v>
       </x:c>
-      <x:c r="M54" s="28" t="s">
+      <x:c r="M54" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B55" s="28" t="s">
+      <x:c r="B55" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C55" s="28" t="s">
+      <x:c r="C55" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D55" s="29" t="s">
+      <x:c r="D55" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E55" s="28" t="s">
+      <x:c r="E55" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F55" s="28" t="s">
+      <x:c r="F55" s="29" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G55" s="28" t="s">
+      <x:c r="G55" s="29" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="H55" s="30">
+      <x:c r="H55" s="31">
         <x:v>46118.3446055671</x:v>
       </x:c>
-      <x:c r="I55" s="30">
+      <x:c r="I55" s="31">
         <x:v>46118.476906412</x:v>
       </x:c>
-      <x:c r="J55" s="29" t="s">
+      <x:c r="J55" s="30" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="K55" s="31" t="n">
+      <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L55" s="32">
+      <x:c r="L55" s="33">
         <x:v>46118.3476865394</x:v>
       </x:c>
-      <x:c r="M55" s="28" t="s">
+      <x:c r="M55" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="28" t="s">
+      <x:c r="B56" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C56" s="28" t="s">
+      <x:c r="C56" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D56" s="29" t="s">
+      <x:c r="D56" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E56" s="28" t="s">
+      <x:c r="E56" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F56" s="28" t="s">
+      <x:c r="F56" s="29" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G56" s="28" t="s">
+      <x:c r="G56" s="29" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="H56" s="30">
+      <x:c r="H56" s="31">
         <x:v>46127.1221474769</x:v>
       </x:c>
-      <x:c r="I56" s="30">
+      <x:c r="I56" s="31">
         <x:v>46127.1231965625</x:v>
       </x:c>
-      <x:c r="J56" s="29" t="s">
+      <x:c r="J56" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K56" s="31" t="n">
+      <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L56" s="32">
+      <x:c r="L56" s="33">
         <x:v>46128.1095700579</x:v>
       </x:c>
-      <x:c r="M56" s="28" t="s">
+      <x:c r="M56" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B57" s="28" t="s">
+      <x:c r="B57" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C57" s="28" t="s">
+      <x:c r="C57" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D57" s="29" t="s">
+      <x:c r="D57" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E57" s="28" t="s">
+      <x:c r="E57" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F57" s="28" t="s">
+      <x:c r="F57" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G57" s="28" t="s">
+      <x:c r="G57" s="29" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H57" s="30">
+      <x:c r="H57" s="31">
         <x:v>46126.5341923727</x:v>
       </x:c>
-      <x:c r="I57" s="30">
+      <x:c r="I57" s="31">
         <x:v>46126.5348242708</x:v>
       </x:c>
-      <x:c r="J57" s="29" t="s">
+      <x:c r="J57" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K57" s="31" t="n">
+      <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L57" s="32">
+      <x:c r="L57" s="33">
         <x:v>46126.5353594213</x:v>
       </x:c>
-      <x:c r="M57" s="28" t="s">
+      <x:c r="M57" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B58" s="28" t="s">
+      <x:c r="B58" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C58" s="28" t="s">
+      <x:c r="C58" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D58" s="29" t="s">
+      <x:c r="D58" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E58" s="28" t="s">
+      <x:c r="E58" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F58" s="28" t="s">
+      <x:c r="F58" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G58" s="28" t="s">
+      <x:c r="G58" s="29" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H58" s="30">
+      <x:c r="H58" s="31">
         <x:v>46124.7035032407</x:v>
       </x:c>
-      <x:c r="I58" s="30">
+      <x:c r="I58" s="31">
         <x:v>46124.704475463</x:v>
       </x:c>
-      <x:c r="J58" s="29" t="s">
+      <x:c r="J58" s="30" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K58" s="31" t="n">
+      <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L58" s="32">
+      <x:c r="L58" s="33">
         <x:v>46124.7056197917</x:v>
       </x:c>
-      <x:c r="M58" s="28" t="s">
+      <x:c r="M58" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B59" s="28" t="s">
+      <x:c r="B59" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C59" s="28" t="s">
+      <x:c r="C59" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D59" s="29" t="s">
+      <x:c r="D59" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E59" s="28" t="s">
+      <x:c r="E59" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F59" s="28" t="s">
+      <x:c r="F59" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G59" s="28" t="s">
+      <x:c r="G59" s="29" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H59" s="30">
+      <x:c r="H59" s="31">
         <x:v>46124.7029179398</x:v>
       </x:c>
-      <x:c r="I59" s="30">
+      <x:c r="I59" s="31">
         <x:v>46124.7046092014</x:v>
       </x:c>
-      <x:c r="J59" s="29" t="s">
+      <x:c r="J59" s="30" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="K59" s="31" t="n">
+      <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L59" s="32">
+      <x:c r="L59" s="33">
         <x:v>46124.7058091204</x:v>
       </x:c>
-      <x:c r="M59" s="28" t="s">
+      <x:c r="M59" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B60" s="28" t="s">
+      <x:c r="B60" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C60" s="28" t="s">
+      <x:c r="C60" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D60" s="29" t="s">
+      <x:c r="D60" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E60" s="28" t="s">
+      <x:c r="E60" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F60" s="28" t="s">
+      <x:c r="F60" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G60" s="28" t="s">
+      <x:c r="G60" s="29" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H60" s="30">
+      <x:c r="H60" s="31">
         <x:v>46124.7023532986</x:v>
       </x:c>
-      <x:c r="I60" s="30">
+      <x:c r="I60" s="31">
         <x:v>46124.7048005093</x:v>
       </x:c>
-      <x:c r="J60" s="29" t="s">
+      <x:c r="J60" s="30" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="K60" s="31" t="n">
+      <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L60" s="32">
+      <x:c r="L60" s="33">
         <x:v>46124.7059938426</x:v>
       </x:c>
-      <x:c r="M60" s="28" t="s">
+      <x:c r="M60" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B61" s="28" t="s">
+      <x:c r="B61" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C61" s="28" t="s">
+      <x:c r="C61" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D61" s="29" t="s">
+      <x:c r="D61" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E61" s="28" t="s">
+      <x:c r="E61" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F61" s="28" t="s">
+      <x:c r="F61" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G61" s="28" t="s">
+      <x:c r="G61" s="29" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H61" s="30">
+      <x:c r="H61" s="31">
         <x:v>46124.701771875</x:v>
       </x:c>
-      <x:c r="I61" s="30">
+      <x:c r="I61" s="31">
         <x:v>46124.7049218519</x:v>
       </x:c>
-      <x:c r="J61" s="29" t="s">
+      <x:c r="J61" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K61" s="31" t="n">
+      <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L61" s="32">
+      <x:c r="L61" s="33">
         <x:v>46124.7061899306</x:v>
       </x:c>
-      <x:c r="M61" s="28" t="s">
+      <x:c r="M61" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="28" t="s">
+      <x:c r="B62" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C62" s="28" t="s">
+      <x:c r="C62" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D62" s="29" t="s">
+      <x:c r="D62" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E62" s="28" t="s">
+      <x:c r="E62" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F62" s="28" t="s">
+      <x:c r="F62" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G62" s="28" t="s">
+      <x:c r="G62" s="29" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="H62" s="30">
+      <x:c r="H62" s="31">
         <x:v>46124.6975491551</x:v>
       </x:c>
-      <x:c r="I62" s="30">
+      <x:c r="I62" s="31">
         <x:v>46124.6983328357</x:v>
       </x:c>
-      <x:c r="J62" s="29" t="s">
+      <x:c r="J62" s="30" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="K62" s="31" t="n">
+      <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L62" s="32">
+      <x:c r="L62" s="33">
         <x:v>46124.6990752199</x:v>
       </x:c>
-      <x:c r="M62" s="28" t="s">
+      <x:c r="M62" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B63" s="28" t="s">
+      <x:c r="B63" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C63" s="28" t="s">
+      <x:c r="C63" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D63" s="29" t="s">
+      <x:c r="D63" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E63" s="28" t="s">
+      <x:c r="E63" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F63" s="28" t="s">
+      <x:c r="F63" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G63" s="28" t="s">
+      <x:c r="G63" s="29" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="H63" s="30">
+      <x:c r="H63" s="31">
         <x:v>46124.6761778356</x:v>
       </x:c>
-      <x:c r="I63" s="30">
+      <x:c r="I63" s="31">
         <x:v>46124.6772295602</x:v>
       </x:c>
-      <x:c r="J63" s="29" t="s">
+      <x:c r="J63" s="30" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="K63" s="31" t="n">
+      <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L63" s="32">
+      <x:c r="L63" s="33">
         <x:v>46124.6777516435</x:v>
       </x:c>
-      <x:c r="M63" s="28" t="s">
+      <x:c r="M63" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="28" t="s">
+      <x:c r="B64" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C64" s="28" t="s">
+      <x:c r="C64" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D64" s="29" t="s">
+      <x:c r="D64" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E64" s="28" t="s">
+      <x:c r="E64" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F64" s="28" t="s">
+      <x:c r="F64" s="29" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G64" s="28" t="s">
+      <x:c r="G64" s="29" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="H64" s="30">
+      <x:c r="H64" s="31">
         <x:v>46124.5490358102</x:v>
       </x:c>
-      <x:c r="I64" s="30">
+      <x:c r="I64" s="31">
         <x:v>46124.6984689583</x:v>
       </x:c>
-      <x:c r="J64" s="29" t="s">
+      <x:c r="J64" s="30" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="K64" s="31" t="n">
+      <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L64" s="32">
+      <x:c r="L64" s="33">
         <x:v>46124.6992754861</x:v>
       </x:c>
-      <x:c r="M64" s="28" t="s">
+      <x:c r="M64" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B65" s="28" t="s">
+      <x:c r="B65" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C65" s="28" t="s">
+      <x:c r="C65" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D65" s="29" t="s">
+      <x:c r="D65" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E65" s="28" t="s">
+      <x:c r="E65" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F65" s="28" t="s">
+      <x:c r="F65" s="29" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G65" s="28" t="s">
+      <x:c r="G65" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H65" s="30">
+      <x:c r="H65" s="31">
         <x:v>46122.36782125</x:v>
       </x:c>
-      <x:c r="I65" s="30">
+      <x:c r="I65" s="31">
         <x:v>46122.3686719907</x:v>
       </x:c>
-      <x:c r="J65" s="29" t="s">
+      <x:c r="J65" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K65" s="31" t="n">
+      <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L65" s="32">
+      <x:c r="L65" s="33">
         <x:v>46122.3692180787</x:v>
       </x:c>
-      <x:c r="M65" s="28" t="s">
+      <x:c r="M65" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B66" s="28" t="s">
+      <x:c r="B66" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C66" s="28" t="s">
+      <x:c r="C66" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D66" s="29" t="s">
+      <x:c r="D66" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E66" s="28" t="s">
+      <x:c r="E66" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F66" s="28" t="s">
+      <x:c r="F66" s="29" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G66" s="28" t="s">
+      <x:c r="G66" s="29" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="H66" s="30">
+      <x:c r="H66" s="31">
         <x:v>46124.1512647338</x:v>
       </x:c>
-      <x:c r="I66" s="30">
+      <x:c r="I66" s="31">
         <x:v>46124.1530803935</x:v>
       </x:c>
-      <x:c r="J66" s="29" t="s">
+      <x:c r="J66" s="30" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="K66" s="31" t="n">
+      <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L66" s="32">
+      <x:c r="L66" s="33">
         <x:v>46124.1540594444</x:v>
       </x:c>
-      <x:c r="M66" s="28" t="s">
+      <x:c r="M66" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B67" s="28" t="s">
+      <x:c r="B67" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C67" s="28" t="s">
+      <x:c r="C67" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D67" s="29" t="s">
+      <x:c r="D67" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E67" s="28" t="s">
+      <x:c r="E67" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F67" s="28" t="s">
+      <x:c r="F67" s="29" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G67" s="28" t="s">
+      <x:c r="G67" s="29" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H67" s="30">
+      <x:c r="H67" s="31">
         <x:v>46124.150742662</x:v>
       </x:c>
-      <x:c r="I67" s="30">
+      <x:c r="I67" s="31">
         <x:v>46124.153253125</x:v>
       </x:c>
-      <x:c r="J67" s="29" t="s">
+      <x:c r="J67" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K67" s="31" t="n">
+      <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L67" s="32">
+      <x:c r="L67" s="33">
         <x:v>46124.1542643171</x:v>
       </x:c>
-      <x:c r="M67" s="28" t="s">
+      <x:c r="M67" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B68" s="28" t="s">
+      <x:c r="B68" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C68" s="28" t="s">
+      <x:c r="C68" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D68" s="29" t="s">
+      <x:c r="D68" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E68" s="28" t="s">
+      <x:c r="E68" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F68" s="28" t="s">
+      <x:c r="F68" s="29" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="G68" s="28" t="s">
+      <x:c r="G68" s="29" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="H68" s="30">
+      <x:c r="H68" s="31">
         <x:v>46124.1487218981</x:v>
       </x:c>
-      <x:c r="I68" s="30">
+      <x:c r="I68" s="31">
         <x:v>46124.1494313773</x:v>
       </x:c>
-      <x:c r="J68" s="29" t="s">
+      <x:c r="J68" s="30" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="K68" s="31" t="n">
+      <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L68" s="32">
+      <x:c r="L68" s="33">
         <x:v>46124.1498205093</x:v>
       </x:c>
-      <x:c r="M68" s="28" t="s">
+      <x:c r="M68" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B69" s="28" t="s">
+      <x:c r="B69" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C69" s="28" t="s">
+      <x:c r="C69" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D69" s="29" t="s">
+      <x:c r="D69" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E69" s="28" t="s">
+      <x:c r="E69" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F69" s="28" t="s">
+      <x:c r="F69" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G69" s="28" t="s">
+      <x:c r="G69" s="29" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H69" s="30">
+      <x:c r="H69" s="31">
         <x:v>46124.1449755903</x:v>
       </x:c>
-      <x:c r="I69" s="30">
+      <x:c r="I69" s="31">
         <x:v>46124.1465040046</x:v>
       </x:c>
-      <x:c r="J69" s="29" t="s">
+      <x:c r="J69" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K69" s="31" t="n">
+      <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L69" s="32">
+      <x:c r="L69" s="33">
         <x:v>46124.1471056481</x:v>
       </x:c>
-      <x:c r="M69" s="28" t="s">
+      <x:c r="M69" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B70" s="28" t="s">
+      <x:c r="B70" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C70" s="28" t="s">
+      <x:c r="C70" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D70" s="29" t="s">
+      <x:c r="D70" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E70" s="28" t="s">
+      <x:c r="E70" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F70" s="28" t="s">
+      <x:c r="F70" s="29" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G70" s="28" t="s">
+      <x:c r="G70" s="29" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H70" s="30">
+      <x:c r="H70" s="31">
         <x:v>46124.1410094907</x:v>
       </x:c>
-      <x:c r="I70" s="30">
+      <x:c r="I70" s="31">
         <x:v>46124.1426461806</x:v>
       </x:c>
-      <x:c r="J70" s="29" t="s">
+      <x:c r="J70" s="30" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="K70" s="31" t="n">
+      <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L70" s="32">
+      <x:c r="L70" s="33">
         <x:v>46124.1434541782</x:v>
       </x:c>
-      <x:c r="M70" s="28" t="s">
+      <x:c r="M70" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B71" s="28" t="s">
+      <x:c r="B71" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C71" s="28" t="s">
+      <x:c r="C71" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D71" s="29" t="s">
+      <x:c r="D71" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E71" s="28" t="s">
+      <x:c r="E71" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F71" s="28" t="s">
+      <x:c r="F71" s="29" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G71" s="28" t="s">
+      <x:c r="G71" s="29" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="H71" s="30">
+      <x:c r="H71" s="31">
         <x:v>46124.1518079282</x:v>
       </x:c>
-      <x:c r="I71" s="30">
+      <x:c r="I71" s="31">
         <x:v>46124.1529164583</x:v>
       </x:c>
-      <x:c r="J71" s="29" t="s">
+      <x:c r="J71" s="30" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="K71" s="31" t="n">
+      <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L71" s="32">
+      <x:c r="L71" s="33">
         <x:v>46124.1538595949</x:v>
       </x:c>
-      <x:c r="M71" s="28" t="s">
+      <x:c r="M71" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B72" s="28" t="s">
+      <x:c r="B72" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C72" s="28" t="s">
+      <x:c r="C72" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D72" s="29" t="s">
+      <x:c r="D72" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E72" s="28" t="s">
+      <x:c r="E72" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F72" s="28" t="s">
+      <x:c r="F72" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G72" s="28" t="s">
+      <x:c r="G72" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="H72" s="30">
+      <x:c r="H72" s="31">
         <x:v>46123.4162791088</x:v>
       </x:c>
-      <x:c r="I72" s="30">
+      <x:c r="I72" s="31">
         <x:v>46123.4173169792</x:v>
       </x:c>
-      <x:c r="J72" s="29" t="s">
+      <x:c r="J72" s="30" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="K72" s="31" t="n">
+      <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L72" s="32">
+      <x:c r="L72" s="33">
         <x:v>46123.417862662</x:v>
       </x:c>
-      <x:c r="M72" s="28" t="s">
+      <x:c r="M72" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B73" s="28" t="s">
+      <x:c r="B73" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C73" s="28" t="s">
+      <x:c r="C73" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D73" s="29" t="s">
+      <x:c r="D73" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E73" s="28" t="s">
+      <x:c r="E73" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F73" s="28" t="s">
+      <x:c r="F73" s="29" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="G73" s="28" t="s">
+      <x:c r="G73" s="29" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="H73" s="30">
+      <x:c r="H73" s="31">
         <x:v>46122.3879258681</x:v>
       </x:c>
-      <x:c r="I73" s="30">
+      <x:c r="I73" s="31">
         <x:v>46122.3894281713</x:v>
       </x:c>
-      <x:c r="J73" s="29" t="s">
+      <x:c r="J73" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K73" s="31" t="n">
+      <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L73" s="32">
+      <x:c r="L73" s="33">
         <x:v>46122.3900310185</x:v>
       </x:c>
-      <x:c r="M73" s="28" t="s">
+      <x:c r="M73" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B74" s="28" t="s">
+      <x:c r="B74" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C74" s="28" t="s">
+      <x:c r="C74" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D74" s="29" t="s">
+      <x:c r="D74" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E74" s="28" t="s">
+      <x:c r="E74" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F74" s="28" t="s">
+      <x:c r="F74" s="29" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G74" s="28" t="s">
+      <x:c r="G74" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="H74" s="30">
+      <x:c r="H74" s="31">
         <x:v>46122.3885020718</x:v>
       </x:c>
-      <x:c r="I74" s="30">
+      <x:c r="I74" s="31">
         <x:v>46122.3892655903</x:v>
       </x:c>
-      <x:c r="J74" s="29" t="s">
+      <x:c r="J74" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K74" s="31" t="n">
+      <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L74" s="32">
+      <x:c r="L74" s="33">
         <x:v>46122.3902404514</x:v>
       </x:c>
-      <x:c r="M74" s="28" t="s">
+      <x:c r="M74" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B75" s="28" t="s">
+      <x:c r="B75" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C75" s="28" t="s">
+      <x:c r="C75" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D75" s="29" t="s">
+      <x:c r="D75" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E75" s="28" t="s">
+      <x:c r="E75" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F75" s="28" t="s">
+      <x:c r="F75" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G75" s="28" t="s">
+      <x:c r="G75" s="29" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="H75" s="30">
+      <x:c r="H75" s="31">
         <x:v>46122.3974322338</x:v>
       </x:c>
-      <x:c r="I75" s="30">
+      <x:c r="I75" s="31">
         <x:v>46122.3980999421</x:v>
       </x:c>
-      <x:c r="J75" s="29" t="s">
+      <x:c r="J75" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K75" s="31" t="n">
+      <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L75" s="32">
+      <x:c r="L75" s="33">
         <x:v>46122.398526713</x:v>
       </x:c>
-      <x:c r="M75" s="28" t="s">
+      <x:c r="M75" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B76" s="28" t="s">
+      <x:c r="B76" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C76" s="28" t="s">
+      <x:c r="C76" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D76" s="29" t="s">
+      <x:c r="D76" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E76" s="28" t="s">
+      <x:c r="E76" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F76" s="28" t="s">
+      <x:c r="F76" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G76" s="28" t="s">
+      <x:c r="G76" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="H76" s="30">
+      <x:c r="H76" s="31">
         <x:v>46122.5587807523</x:v>
       </x:c>
-      <x:c r="I76" s="30">
+      <x:c r="I76" s="31">
         <x:v>46122.5602428125</x:v>
       </x:c>
-      <x:c r="J76" s="29" t="s">
+      <x:c r="J76" s="30" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="K76" s="31" t="n">
+      <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L76" s="32">
+      <x:c r="L76" s="33">
         <x:v>46122.5607516551</x:v>
       </x:c>
-      <x:c r="M76" s="28" t="s">
+      <x:c r="M76" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B77" s="28" t="s">
+      <x:c r="B77" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C77" s="28" t="s">
+      <x:c r="C77" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D77" s="29" t="s">
+      <x:c r="D77" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E77" s="28" t="s">
+      <x:c r="E77" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F77" s="28" t="s">
+      <x:c r="F77" s="29" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G77" s="28" t="s">
+      <x:c r="G77" s="29" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H77" s="30">
+      <x:c r="H77" s="31">
         <x:v>46123.4191184375</x:v>
       </x:c>
-      <x:c r="I77" s="30">
+      <x:c r="I77" s="31">
         <x:v>46123.4205974074</x:v>
       </x:c>
-      <x:c r="J77" s="29" t="s">
+      <x:c r="J77" s="30" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="K77" s="31" t="n">
+      <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L77" s="32">
+      <x:c r="L77" s="33">
         <x:v>46123.4214065278</x:v>
       </x:c>
-      <x:c r="M77" s="28" t="s">
+      <x:c r="M77" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B78" s="28" t="s">
+      <x:c r="B78" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C78" s="28" t="s">
+      <x:c r="C78" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D78" s="29" t="s">
+      <x:c r="D78" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E78" s="28" t="s">
+      <x:c r="E78" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F78" s="28" t="s">
+      <x:c r="F78" s="29" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G78" s="28" t="s">
+      <x:c r="G78" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="H78" s="30">
+      <x:c r="H78" s="31">
         <x:v>46122.5911383796</x:v>
       </x:c>
-      <x:c r="I78" s="30">
+      <x:c r="I78" s="31">
         <x:v>46122.5921380556</x:v>
       </x:c>
-      <x:c r="J78" s="29" t="s">
+      <x:c r="J78" s="30" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="K78" s="31" t="n">
+      <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L78" s="32">
+      <x:c r="L78" s="33">
         <x:v>46122.5928339699</x:v>
       </x:c>
-      <x:c r="M78" s="28" t="s">
+      <x:c r="M78" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B79" s="28" t="s">
+      <x:c r="B79" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C79" s="28" t="s">
+      <x:c r="C79" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D79" s="29" t="s">
+      <x:c r="D79" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E79" s="28" t="s">
+      <x:c r="E79" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F79" s="28" t="s">
+      <x:c r="F79" s="29" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G79" s="28" t="s">
+      <x:c r="G79" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="H79" s="30">
+      <x:c r="H79" s="31">
         <x:v>46122.5945434491</x:v>
       </x:c>
-      <x:c r="I79" s="30">
+      <x:c r="I79" s="31">
         <x:v>46122.5999534606</x:v>
       </x:c>
-      <x:c r="J79" s="29" t="s">
+      <x:c r="J79" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K79" s="31" t="n">
+      <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L79" s="32">
+      <x:c r="L79" s="33">
         <x:v>46122.6007489699</x:v>
       </x:c>
-      <x:c r="M79" s="28" t="s">
+      <x:c r="M79" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B80" s="28" t="s">
+      <x:c r="B80" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C80" s="28" t="s">
+      <x:c r="C80" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D80" s="29" t="s">
+      <x:c r="D80" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E80" s="28" t="s">
+      <x:c r="E80" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F80" s="28" t="s">
+      <x:c r="F80" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G80" s="28" t="s">
+      <x:c r="G80" s="29" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="H80" s="30">
+      <x:c r="H80" s="31">
         <x:v>46122.6182774306</x:v>
       </x:c>
-      <x:c r="I80" s="30">
+      <x:c r="I80" s="31">
         <x:v>46122.6193276968</x:v>
       </x:c>
-      <x:c r="J80" s="29" t="s">
+      <x:c r="J80" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K80" s="31" t="n">
+      <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L80" s="32">
+      <x:c r="L80" s="33">
         <x:v>46122.6199813426</x:v>
       </x:c>
-      <x:c r="M80" s="28" t="s">
+      <x:c r="M80" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B81" s="28" t="s">
+      <x:c r="B81" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C81" s="28" t="s">
+      <x:c r="C81" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D81" s="29" t="s">
+      <x:c r="D81" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E81" s="28" t="s">
+      <x:c r="E81" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F81" s="28" t="s">
+      <x:c r="F81" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G81" s="28" t="s">
+      <x:c r="G81" s="29" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H81" s="30">
+      <x:c r="H81" s="31">
         <x:v>46122.5623107755</x:v>
       </x:c>
-      <x:c r="I81" s="30">
+      <x:c r="I81" s="31">
         <x:v>46122.5630093981</x:v>
       </x:c>
-      <x:c r="J81" s="29" t="s">
+      <x:c r="J81" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="K81" s="31" t="n">
+      <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L81" s="32">
+      <x:c r="L81" s="33">
         <x:v>46122.5634620023</x:v>
       </x:c>
-      <x:c r="M81" s="28" t="s">
+      <x:c r="M81" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B82" s="28" t="s">
+      <x:c r="B82" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C82" s="28" t="s">
+      <x:c r="C82" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D82" s="29" t="s">
+      <x:c r="D82" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E82" s="28" t="s">
+      <x:c r="E82" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F82" s="28" t="s">
+      <x:c r="F82" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G82" s="28" t="s">
+      <x:c r="G82" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="H82" s="30">
+      <x:c r="H82" s="31">
         <x:v>46123.0476912847</x:v>
       </x:c>
-      <x:c r="I82" s="30">
+      <x:c r="I82" s="31">
         <x:v>46123.0484775694</x:v>
       </x:c>
-      <x:c r="J82" s="29" t="s">
+      <x:c r="J82" s="30" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="K82" s="31" t="n">
+      <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L82" s="32">
+      <x:c r="L82" s="33">
         <x:v>46123.049084375</x:v>
       </x:c>
-      <x:c r="M82" s="28" t="s">
+      <x:c r="M82" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B83" s="28" t="s">
+      <x:c r="B83" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C83" s="28" t="s">
+      <x:c r="C83" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D83" s="29" t="s">
+      <x:c r="D83" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E83" s="28" t="s">
+      <x:c r="E83" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F83" s="28" t="s">
+      <x:c r="F83" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G83" s="28" t="s">
+      <x:c r="G83" s="29" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H83" s="30">
+      <x:c r="H83" s="31">
         <x:v>46123.061368912</x:v>
       </x:c>
-      <x:c r="I83" s="30">
+      <x:c r="I83" s="31">
         <x:v>46123.0623472106</x:v>
       </x:c>
-      <x:c r="J83" s="29" t="s">
+      <x:c r="J83" s="30" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="K83" s="31" t="n">
+      <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L83" s="32">
+      <x:c r="L83" s="33">
         <x:v>46123.0628773958</x:v>
       </x:c>
-      <x:c r="M83" s="28" t="s">
+      <x:c r="M83" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B84" s="28" t="s">
+      <x:c r="B84" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C84" s="28" t="s">
+      <x:c r="C84" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D84" s="29" t="s">
+      <x:c r="D84" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E84" s="28" t="s">
+      <x:c r="E84" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F84" s="28" t="s">
+      <x:c r="F84" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G84" s="28" t="s">
+      <x:c r="G84" s="29" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="H84" s="30">
+      <x:c r="H84" s="31">
         <x:v>46122.6795081481</x:v>
       </x:c>
-      <x:c r="I84" s="30">
+      <x:c r="I84" s="31">
         <x:v>46122.6802186921</x:v>
       </x:c>
-      <x:c r="J84" s="29" t="s">
+      <x:c r="J84" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K84" s="31" t="n">
+      <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L84" s="32">
+      <x:c r="L84" s="33">
         <x:v>46122.6809879398</x:v>
       </x:c>
-      <x:c r="M84" s="28" t="s">
+      <x:c r="M84" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B85" s="28" t="s">
+      <x:c r="B85" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C85" s="28" t="s">
+      <x:c r="C85" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D85" s="29" t="s">
+      <x:c r="D85" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E85" s="28" t="s">
+      <x:c r="E85" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F85" s="28" t="s">
+      <x:c r="F85" s="29" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G85" s="28" t="s">
+      <x:c r="G85" s="29" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H85" s="30">
+      <x:c r="H85" s="31">
         <x:v>46122.9452935995</x:v>
       </x:c>
-      <x:c r="I85" s="30">
+      <x:c r="I85" s="31">
         <x:v>46123.0460683681</x:v>
       </x:c>
-      <x:c r="J85" s="29" t="s">
+      <x:c r="J85" s="30" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K85" s="31" t="n">
+      <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L85" s="32">
+      <x:c r="L85" s="33">
         <x:v>46123.0466478819</x:v>
       </x:c>
-      <x:c r="M85" s="28" t="s">
+      <x:c r="M85" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B86" s="28" t="s">
+      <x:c r="B86" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C86" s="28" t="s">
+      <x:c r="C86" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D86" s="29" t="s">
+      <x:c r="D86" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E86" s="28" t="s">
+      <x:c r="E86" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F86" s="28" t="s">
+      <x:c r="F86" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G86" s="28" t="s">
+      <x:c r="G86" s="29" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="H86" s="30">
+      <x:c r="H86" s="31">
         <x:v>46128.4605351157</x:v>
       </x:c>
-      <x:c r="I86" s="30">
+      <x:c r="I86" s="31">
         <x:v>46128.4612873727</x:v>
       </x:c>
-      <x:c r="J86" s="29" t="s">
+      <x:c r="J86" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K86" s="31" t="n">
+      <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L86" s="32">
+      <x:c r="L86" s="33">
         <x:v>46128.4617054051</x:v>
       </x:c>
-      <x:c r="M86" s="28" t="s">
+      <x:c r="M86" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B87" s="28" t="s">
+      <x:c r="B87" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C87" s="28" t="s">
+      <x:c r="C87" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D87" s="29" t="s">
+      <x:c r="D87" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E87" s="28" t="s">
+      <x:c r="E87" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F87" s="28" t="s">
+      <x:c r="F87" s="29" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G87" s="28" t="s">
+      <x:c r="G87" s="29" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="H87" s="30">
+      <x:c r="H87" s="31">
         <x:v>46122.6819179514</x:v>
       </x:c>
-      <x:c r="I87" s="30">
+      <x:c r="I87" s="31">
         <x:v>46122.6826717361</x:v>
       </x:c>
-      <x:c r="J87" s="29" t="s">
+      <x:c r="J87" s="30" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="K87" s="31" t="n">
+      <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L87" s="32">
+      <x:c r="L87" s="33">
         <x:v>46122.6831438079</x:v>
       </x:c>
-      <x:c r="M87" s="28" t="s">
+      <x:c r="M87" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B88" s="28" t="s">
+      <x:c r="B88" s="29" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C88" s="28" t="s">
+      <x:c r="C88" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D88" s="29" t="s">
+      <x:c r="D88" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E88" s="28" t="s">
+      <x:c r="E88" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F88" s="28" t="s">
+      <x:c r="F88" s="29" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="G88" s="28" t="s">
+      <x:c r="G88" s="29" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="H88" s="30">
+      <x:c r="H88" s="31">
         <x:v>46122.7261372338</x:v>
       </x:c>
-      <x:c r="I88" s="30">
+      <x:c r="I88" s="31">
         <x:v>46122.727234375</x:v>
       </x:c>
-      <x:c r="J88" s="29" t="s">
+      <x:c r="J88" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K88" s="31" t="n">
+      <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L88" s="32">
+      <x:c r="L88" s="33">
         <x:v>46122.7277720023</x:v>
       </x:c>
-      <x:c r="M88" s="28" t="s">
+      <x:c r="M88" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B89" s="28" t="s">
+      <x:c r="B89" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C89" s="28" t="s">
+      <x:c r="C89" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="D89" s="29" t="s">
+      <x:c r="D89" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E89" s="28" t="s">
+      <x:c r="E89" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F89" s="28" t="s">
+      <x:c r="F89" s="29" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="G89" s="28" t="s">
+      <x:c r="G89" s="29" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="H89" s="30">
+      <x:c r="H89" s="31">
         <x:v>46118.5788871875</x:v>
       </x:c>
-      <x:c r="I89" s="30">
+      <x:c r="I89" s="31">
         <x:v>46118.5789284722</x:v>
       </x:c>
-      <x:c r="J89" s="29" t="s">
+      <x:c r="J89" s="30" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="K89" s="31" t="n">
+      <x:c r="K89" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L89" s="32">
+      <x:c r="L89" s="33">
         <x:v>46118.5806122685</x:v>
       </x:c>
-      <x:c r="M89" s="28" t="s">
+      <x:c r="M89" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B90" s="28" t="s">
+      <x:c r="B90" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C90" s="28" t="s">
+      <x:c r="C90" s="29" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="D90" s="29" t="s">
+      <x:c r="D90" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E90" s="28" t="s">
+      <x:c r="E90" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F90" s="28" t="s">
+      <x:c r="F90" s="29" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="G90" s="28" t="s">
+      <x:c r="G90" s="29" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="H90" s="30">
+      <x:c r="H90" s="31">
         <x:v>46118.6064654514</x:v>
       </x:c>
-      <x:c r="I90" s="30">
+      <x:c r="I90" s="31">
         <x:v>46118.6065117477</x:v>
       </x:c>
-      <x:c r="J90" s="29" t="s">
+      <x:c r="J90" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K90" s="31" t="n">
+      <x:c r="K90" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L90" s="32">
+      <x:c r="L90" s="33">
         <x:v>46118.6077792245</x:v>
       </x:c>
-      <x:c r="M90" s="28" t="s">
+      <x:c r="M90" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B91" s="28" t="s">
+      <x:c r="B91" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C91" s="28" t="s">
+      <x:c r="C91" s="29" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="D91" s="29" t="s">
+      <x:c r="D91" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E91" s="28" t="s">
+      <x:c r="E91" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F91" s="28" t="s">
+      <x:c r="F91" s="29" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="G91" s="28" t="s">
+      <x:c r="G91" s="29" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="H91" s="30">
+      <x:c r="H91" s="31">
         <x:v>46118.7029973032</x:v>
       </x:c>
-      <x:c r="I91" s="30">
+      <x:c r="I91" s="31">
         <x:v>46118.7030397569</x:v>
       </x:c>
-      <x:c r="J91" s="29" t="s">
+      <x:c r="J91" s="30" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="K91" s="31" t="n">
+      <x:c r="K91" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L91" s="32">
+      <x:c r="L91" s="33">
         <x:v>46118.7054991898</x:v>
       </x:c>
-      <x:c r="M91" s="28" t="s">
+      <x:c r="M91" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B92" s="28" t="s">
+      <x:c r="B92" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C92" s="28" t="s">
+      <x:c r="C92" s="29" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="D92" s="29" t="s">
+      <x:c r="D92" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E92" s="28" t="s">
+      <x:c r="E92" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F92" s="28" t="s">
+      <x:c r="F92" s="29" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="G92" s="28" t="s">
+      <x:c r="G92" s="29" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="H92" s="30">
+      <x:c r="H92" s="31">
         <x:v>46118.7372774306</x:v>
       </x:c>
-      <x:c r="I92" s="30">
+      <x:c r="I92" s="31">
         <x:v>46118.7373236806</x:v>
       </x:c>
-      <x:c r="J92" s="29" t="s">
+      <x:c r="J92" s="30" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="K92" s="31" t="n">
+      <x:c r="K92" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L92" s="32">
+      <x:c r="L92" s="33">
         <x:v>46118.7388858565</x:v>
       </x:c>
-      <x:c r="M92" s="28" t="s">
+      <x:c r="M92" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B93" s="28" t="s">
+      <x:c r="B93" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C93" s="28" t="s">
+      <x:c r="C93" s="29" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="D93" s="29" t="s">
+      <x:c r="D93" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E93" s="28" t="s">
+      <x:c r="E93" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F93" s="28" t="s">
+      <x:c r="F93" s="29" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="G93" s="28" t="s">
+      <x:c r="G93" s="29" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="H93" s="30">
+      <x:c r="H93" s="31">
         <x:v>46118.6471475926</x:v>
       </x:c>
-      <x:c r="I93" s="30">
+      <x:c r="I93" s="31">
         <x:v>46118.647188044</x:v>
       </x:c>
-      <x:c r="J93" s="29" t="s">
+      <x:c r="J93" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K93" s="31" t="n">
+      <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L93" s="32">
+      <x:c r="L93" s="33">
         <x:v>46118.6489296181</x:v>
       </x:c>
-      <x:c r="M93" s="28" t="s">
+      <x:c r="M93" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B94" s="28" t="s">
+      <x:c r="B94" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C94" s="28" t="s">
+      <x:c r="C94" s="29" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="D94" s="29" t="s">
+      <x:c r="D94" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E94" s="28" t="s">
+      <x:c r="E94" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F94" s="28" t="s">
+      <x:c r="F94" s="29" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="G94" s="28" t="s">
+      <x:c r="G94" s="29" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="H94" s="30">
+      <x:c r="H94" s="31">
         <x:v>46118.7761679514</x:v>
       </x:c>
-      <x:c r="I94" s="30">
+      <x:c r="I94" s="31">
         <x:v>46118.7762103819</x:v>
       </x:c>
-      <x:c r="J94" s="29" t="s">
+      <x:c r="J94" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K94" s="31" t="n">
+      <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L94" s="32">
+      <x:c r="L94" s="33">
         <x:v>46118.7774822107</x:v>
       </x:c>
-      <x:c r="M94" s="28" t="s">
+      <x:c r="M94" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B95" s="28" t="s">
+      <x:c r="B95" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C95" s="28" t="s">
+      <x:c r="C95" s="29" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="D95" s="29" t="s">
+      <x:c r="D95" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E95" s="28" t="s">
+      <x:c r="E95" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F95" s="28" t="s">
+      <x:c r="F95" s="29" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="G95" s="28" t="s">
+      <x:c r="G95" s="29" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="H95" s="30">
+      <x:c r="H95" s="31">
         <x:v>46118.439490081</x:v>
       </x:c>
-      <x:c r="I95" s="30">
+      <x:c r="I95" s="31">
         <x:v>46118.4395309375</x:v>
       </x:c>
-      <x:c r="J95" s="29" t="s">
+      <x:c r="J95" s="30" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="K95" s="31" t="n">
+      <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L95" s="32">
+      <x:c r="L95" s="33">
         <x:v>46118.4416909375</x:v>
       </x:c>
-      <x:c r="M95" s="28" t="s">
+      <x:c r="M95" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B96" s="28" t="s">
+      <x:c r="B96" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C96" s="28" t="s">
+      <x:c r="C96" s="29" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D96" s="29" t="s">
+      <x:c r="D96" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E96" s="28" t="s">
+      <x:c r="E96" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F96" s="28" t="s">
+      <x:c r="F96" s="29" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G96" s="28" t="s">
+      <x:c r="G96" s="29" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="H96" s="30">
+      <x:c r="H96" s="31">
         <x:v>46119.4833706713</x:v>
       </x:c>
-      <x:c r="I96" s="30">
+      <x:c r="I96" s="31">
         <x:v>46119.4833991435</x:v>
       </x:c>
-      <x:c r="J96" s="29" t="s">
+      <x:c r="J96" s="30" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K96" s="31" t="n">
+      <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L96" s="32">
+      <x:c r="L96" s="33">
         <x:v>46119.4846717477</x:v>
       </x:c>
-      <x:c r="M96" s="28" t="s">
+      <x:c r="M96" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B97" s="28" t="s">
+      <x:c r="B97" s="29" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="C97" s="28" t="s">
+      <x:c r="C97" s="29" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="D97" s="29" t="s"/>
-      <x:c r="E97" s="28" t="s">
+      <x:c r="D97" s="30" t="s"/>
+      <x:c r="E97" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F97" s="28" t="s">
+      <x:c r="F97" s="29" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="G97" s="28" t="s">
+      <x:c r="G97" s="29" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="H97" s="30">
+      <x:c r="H97" s="31">
         <x:v>46124.1588481829</x:v>
       </x:c>
-      <x:c r="I97" s="30">
+      <x:c r="I97" s="31">
         <x:v>46124.1588689236</x:v>
       </x:c>
-      <x:c r="J97" s="29" t="s">
+      <x:c r="J97" s="30" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="K97" s="31" t="n">
+      <x:c r="K97" s="32" t="n">
         <x:v>5070</x:v>
       </x:c>
-      <x:c r="L97" s="32">
+      <x:c r="L97" s="33">
         <x:v>46124.1622106481</x:v>
       </x:c>
-      <x:c r="M97" s="28" t="s">
+      <x:c r="M97" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B98" s="28" t="s">
+      <x:c r="B98" s="29" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="C98" s="28" t="s">
+      <x:c r="C98" s="29" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="D98" s="29" t="s">
+      <x:c r="D98" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E98" s="28" t="s">
+      <x:c r="E98" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F98" s="28" t="s">
+      <x:c r="F98" s="29" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="G98" s="28" t="s">
+      <x:c r="G98" s="29" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="H98" s="30">
+      <x:c r="H98" s="31">
         <x:v>46124.1607868981</x:v>
       </x:c>
-      <x:c r="I98" s="30">
+      <x:c r="I98" s="31">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J98" s="29" t="s">
+      <x:c r="J98" s="30" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="K98" s="31" t="n">
+      <x:c r="K98" s="32" t="n">
         <x:v>3100</x:v>
       </x:c>
-      <x:c r="L98" s="32">
+      <x:c r="L98" s="33">
         <x:v>46124.1624131829</x:v>
       </x:c>
-      <x:c r="M98" s="28" t="s">
+      <x:c r="M98" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B99" s="28" t="s">
+      <x:c r="B99" s="29" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="C99" s="28" t="s">
+      <x:c r="C99" s="29" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="D99" s="29" t="s">
+      <x:c r="D99" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E99" s="28" t="s">
+      <x:c r="E99" s="29" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="F99" s="28" t="s">
+      <x:c r="F99" s="29" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="G99" s="28" t="s">
+      <x:c r="G99" s="29" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="H99" s="30">
+      <x:c r="H99" s="31">
         <x:v>46125.0306295139</x:v>
       </x:c>
-      <x:c r="I99" s="30">
+      <x:c r="I99" s="31">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="J99" s="29" t="s">
+      <x:c r="J99" s="30" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="K99" s="31" t="n">
+      <x:c r="K99" s="32" t="n">
         <x:v>3006</x:v>
       </x:c>
-      <x:c r="L99" s="32">
+      <x:c r="L99" s="33">
         <x:v>46125.0821987731</x:v>
       </x:c>
-      <x:c r="M99" s="28" t="s">
+      <x:c r="M99" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="102" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B102" s="16" t="s">
+      <x:c r="B102" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C102" s="17" t="s"/>
-      <x:c r="D102" s="17" t="s"/>
-      <x:c r="E102" s="18" t="s"/>
-      <x:c r="F102" s="18" t="s"/>
+      <x:c r="C102" s="18" t="s"/>
+      <x:c r="D102" s="18" t="s"/>
+      <x:c r="E102" s="19" t="s"/>
+      <x:c r="F102" s="19" t="s"/>
     </x:row>
     <x:row r="103" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B103" s="19" t="s">
+      <x:c r="B103" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C103" s="20" t="s"/>
-      <x:c r="D103" s="20" t="s"/>
-      <x:c r="E103" s="20" t="s"/>
-      <x:c r="F103" s="21" t="s">
+      <x:c r="C103" s="21" t="s"/>
+      <x:c r="D103" s="21" t="s"/>
+      <x:c r="E103" s="21" t="s"/>
+      <x:c r="F103" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B104" s="22" t="s">
+      <x:c r="B104" s="23" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C104" s="23" t="s"/>
-      <x:c r="D104" s="23" t="s"/>
-      <x:c r="E104" s="23" t="s"/>
-      <x:c r="F104" s="24" t="n">
+      <x:c r="C104" s="24" t="s"/>
+      <x:c r="D104" s="24" t="s"/>
+      <x:c r="E104" s="24" t="s"/>
+      <x:c r="F104" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B105" s="22" t="s">
+      <x:c r="B105" s="23" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C105" s="23" t="s"/>
-      <x:c r="D105" s="23" t="s"/>
-      <x:c r="E105" s="23" t="s"/>
-      <x:c r="F105" s="24" t="n">
+      <x:c r="C105" s="24" t="s"/>
+      <x:c r="D105" s="24" t="s"/>
+      <x:c r="E105" s="24" t="s"/>
+      <x:c r="F105" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B106" s="22" t="s">
+      <x:c r="B106" s="23" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C106" s="23" t="s"/>
-      <x:c r="D106" s="23" t="s"/>
-      <x:c r="E106" s="23" t="s"/>
-      <x:c r="F106" s="24" t="n">
+      <x:c r="C106" s="24" t="s"/>
+      <x:c r="D106" s="24" t="s"/>
+      <x:c r="E106" s="24" t="s"/>
+      <x:c r="F106" s="25" t="n">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B107" s="22" t="s">
+      <x:c r="B107" s="23" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="C107" s="23" t="s"/>
-      <x:c r="D107" s="23" t="s"/>
-      <x:c r="E107" s="23" t="s"/>
-      <x:c r="F107" s="24" t="n">
+      <x:c r="C107" s="24" t="s"/>
+      <x:c r="D107" s="24" t="s"/>
+      <x:c r="E107" s="24" t="s"/>
+      <x:c r="F107" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B108" s="22" t="s">
+      <x:c r="B108" s="23" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="C108" s="23" t="s"/>
-      <x:c r="D108" s="23" t="s"/>
-      <x:c r="E108" s="23" t="s"/>
-      <x:c r="F108" s="24" t="n">
+      <x:c r="C108" s="24" t="s"/>
+      <x:c r="D108" s="24" t="s"/>
+      <x:c r="E108" s="24" t="s"/>
+      <x:c r="F108" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B109" s="22" t="s">
+      <x:c r="B109" s="23" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="C109" s="23" t="s"/>
-      <x:c r="D109" s="23" t="s"/>
-      <x:c r="E109" s="23" t="s"/>
-      <x:c r="F109" s="24" t="n">
+      <x:c r="C109" s="24" t="s"/>
+      <x:c r="D109" s="24" t="s"/>
+      <x:c r="E109" s="24" t="s"/>
+      <x:c r="F109" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B110" s="25" t="s">
+      <x:c r="B110" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C110" s="26" t="s"/>
-      <x:c r="D110" s="26" t="s"/>
-      <x:c r="E110" s="26" t="s"/>
-      <x:c r="F110" s="27" t="n">
+      <x:c r="C110" s="27" t="s"/>
+      <x:c r="D110" s="27" t="s"/>
+      <x:c r="E110" s="27" t="s"/>
+      <x:c r="F110" s="28" t="n">
         <x:v>92</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -186,6 +186,15 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08281</x:t>
   </x:si>
   <x:si>
@@ -204,6 +213,24 @@
     <x:t>sczxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08296</x:t>
   </x:si>
   <x:si>
@@ -213,22 +240,22 @@
     <x:t>zxcasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1316-566</x:t>
-  </x:si>
-  <x:si>
-    <x:t>szdasdqweq</x:t>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08338</x:t>
@@ -240,31 +267,91 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1325-890</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdxzcasd</x:t>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -273,52 +360,19 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
@@ -330,58 +384,148 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -390,148 +534,49 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
@@ -543,13 +588,73 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08369</x:t>
@@ -558,37 +663,10 @@
     <x:t>61-4-2026-1334-994</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08212</x:t>
@@ -597,69 +675,48 @@
     <x:t>61-4-2026-1312-712</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08188</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1299-939</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08187</x:t>
   </x:si>
   <x:si>
@@ -669,13 +726,64 @@
     <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -687,91 +795,10 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08181</x:t>
@@ -783,27 +810,6 @@
     <x:t>tesg213</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -883,6 +889,15 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1239-459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1343-633</x:t>
+  </x:si>
+  <x:si>
+    <x:t>czxc</x:t>
   </x:si>
   <x:si>
     <x:t>Permit to PURCHASE/POSSESS</x:t>
@@ -5816,19 +5831,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>20</x:v>
@@ -5854,10 +5869,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>58</x:v>
@@ -5866,7 +5881,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>20</x:v>
@@ -5892,10 +5907,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>61</x:v>
@@ -5904,7 +5919,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>20</x:v>
@@ -5968,19 +5983,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>20</x:v>
@@ -6006,10 +6021,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>70</x:v>
@@ -6018,7 +6033,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>20</x:v>
@@ -6120,10 +6135,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
         <x:v>79</x:v>
@@ -6132,7 +6147,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>20</x:v>
@@ -6158,19 +6173,19 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>20</x:v>
@@ -6196,19 +6211,19 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>20</x:v>
@@ -6234,19 +6249,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>20</x:v>
@@ -6266,25 +6281,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>20</x:v>
@@ -6310,19 +6325,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
@@ -6424,10 +6439,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>100</x:v>
@@ -6436,7 +6451,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
@@ -6538,19 +6553,19 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
@@ -6570,16 +6585,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="H31" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>52</x:v>
@@ -6588,7 +6603,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>20</x:v>
@@ -6608,10 +6623,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="G32" s="29" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="31">
         <x:v>46121.5183984954</x:v>
@@ -6620,7 +6635,7 @@
         <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
@@ -6646,10 +6661,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="G33" s="29" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="31">
         <x:v>46122.1299166204</x:v>
@@ -6684,25 +6699,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G34" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G34" s="29" t="s">
+      <x:c r="H34" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I34" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H34" s="31">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I34" s="31">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J34" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
@@ -6728,19 +6743,19 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
@@ -6766,10 +6781,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
         <x:v>123</x:v>
@@ -6778,7 +6793,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>20</x:v>
@@ -6804,19 +6819,19 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
@@ -6836,10 +6851,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G38" s="29" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="G38" s="29" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="31">
         <x:v>46118.4219285995</x:v>
@@ -6848,7 +6863,7 @@
         <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
@@ -6874,10 +6889,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G39" s="29" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="G39" s="29" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="H39" s="31">
         <x:v>46118.7424944097</x:v>
@@ -6886,7 +6901,7 @@
         <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
@@ -6912,10 +6927,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="G40" s="29" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="H40" s="31">
         <x:v>46118.7562945255</x:v>
@@ -6924,7 +6939,7 @@
         <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
@@ -6950,10 +6965,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="G41" s="29" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="H41" s="31">
         <x:v>46119.0668949653</x:v>
@@ -6962,7 +6977,7 @@
         <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
@@ -6988,10 +7003,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="G42" s="29" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="H42" s="31">
         <x:v>46119.0739296412</x:v>
@@ -7000,7 +7015,7 @@
         <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
@@ -7026,10 +7041,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="G43" s="29" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="H43" s="31">
         <x:v>46119.1921340856</x:v>
@@ -7038,7 +7053,7 @@
         <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
@@ -7064,25 +7079,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
-        <x:v>146</x:v>
-      </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>20</x:v>
@@ -7102,25 +7117,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
+      <x:c r="H45" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>20</x:v>
@@ -7222,19 +7237,19 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
@@ -7254,25 +7269,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G49" s="29" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
@@ -7304,7 +7319,7 @@
         <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
@@ -7374,10 +7389,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
         <x:v>166</x:v>
@@ -7386,7 +7401,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
@@ -7412,19 +7427,19 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>20</x:v>
@@ -7450,19 +7465,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>20</x:v>
@@ -7482,25 +7497,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G55" s="29" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G55" s="29" t="s">
-        <x:v>173</x:v>
-      </x:c>
       <x:c r="H55" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>20</x:v>
@@ -7520,25 +7535,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G56" s="29" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H56" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I56" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J56" s="30" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="G56" s="29" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H56" s="31">
-        <x:v>46127.1221474769</x:v>
-      </x:c>
-      <x:c r="I56" s="31">
-        <x:v>46127.1231965625</x:v>
-      </x:c>
-      <x:c r="J56" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>20</x:v>
@@ -7558,25 +7573,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G57" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G57" s="29" t="s">
-        <x:v>178</x:v>
-      </x:c>
       <x:c r="H57" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>20</x:v>
@@ -7596,25 +7611,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G58" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G58" s="29" t="s">
+      <x:c r="H58" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I58" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J58" s="30" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="H58" s="31">
-        <x:v>46124.7035032407</x:v>
-      </x:c>
-      <x:c r="I58" s="31">
-        <x:v>46124.704475463</x:v>
-      </x:c>
-      <x:c r="J58" s="30" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>20</x:v>
@@ -7634,25 +7649,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G59" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G59" s="29" t="s">
+      <x:c r="H59" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I59" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J59" s="30" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="H59" s="31">
-        <x:v>46124.7029179398</x:v>
-      </x:c>
-      <x:c r="I59" s="31">
-        <x:v>46124.7046092014</x:v>
-      </x:c>
-      <x:c r="J59" s="30" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>20</x:v>
@@ -7672,25 +7687,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G60" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G60" s="29" t="s">
+      <x:c r="H60" s="31">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I60" s="31">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J60" s="30" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="H60" s="31">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I60" s="31">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J60" s="30" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>20</x:v>
@@ -7710,25 +7725,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G61" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G61" s="29" t="s">
+      <x:c r="H61" s="31">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I61" s="31">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J61" s="30" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="H61" s="31">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I61" s="31">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J61" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>20</x:v>
@@ -7754,10 +7769,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
         <x:v>192</x:v>
@@ -7766,7 +7781,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>20</x:v>
@@ -7792,10 +7807,10 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
         <x:v>195</x:v>
@@ -7804,7 +7819,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>20</x:v>
@@ -7830,10 +7845,10 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
         <x:v>198</x:v>
@@ -7842,7 +7857,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>20</x:v>
@@ -7868,19 +7883,19 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>20</x:v>
@@ -7900,25 +7915,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>20</x:v>
@@ -7938,25 +7953,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>20</x:v>
@@ -7976,25 +7991,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>20</x:v>
@@ -8014,25 +8029,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G69" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>20</x:v>
@@ -8052,25 +8067,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>20</x:v>
@@ -8096,19 +8111,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>20</x:v>
@@ -8128,25 +8143,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G72" s="29" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="H72" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>20</x:v>
@@ -8166,25 +8181,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>20</x:v>
@@ -8204,25 +8219,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G74" s="29" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H74" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I74" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J74" s="30" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="G74" s="29" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H74" s="31">
-        <x:v>46122.3885020718</x:v>
-      </x:c>
-      <x:c r="I74" s="31">
-        <x:v>46122.3892655903</x:v>
-      </x:c>
-      <x:c r="J74" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>20</x:v>
@@ -8242,25 +8257,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G75" s="29" t="s">
-        <x:v>225</x:v>
-      </x:c>
       <x:c r="H75" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>20</x:v>
@@ -8280,25 +8295,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G76" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G76" s="29" t="s">
-        <x:v>227</x:v>
-      </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>228</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>20</x:v>
@@ -8318,25 +8333,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H77" s="31">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I77" s="31">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="G77" s="29" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H77" s="31">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I77" s="31">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J77" s="30" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>20</x:v>
@@ -8356,25 +8371,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H78" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="G78" s="29" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46122.5911383796</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46122.5921380556</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>20</x:v>
@@ -8394,25 +8409,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H79" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>20</x:v>
@@ -8432,25 +8447,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
-        <x:v>238</x:v>
-      </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>20</x:v>
@@ -8470,25 +8485,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>20</x:v>
@@ -8508,25 +8523,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>242</x:v>
-      </x:c>
       <x:c r="H82" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>243</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>20</x:v>
@@ -8546,25 +8561,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H83" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I83" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J83" s="30" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="G83" s="29" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="H83" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I83" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J83" s="30" t="s">
-        <x:v>246</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>20</x:v>
@@ -8584,10 +8599,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H84" s="31">
         <x:v>46122.6795081481</x:v>
@@ -8622,25 +8637,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H85" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="G85" s="29" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>20</x:v>
@@ -8660,25 +8675,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G86" s="29" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H86" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I86" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J86" s="30" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="G86" s="29" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="H86" s="31">
-        <x:v>46128.4605351157</x:v>
-      </x:c>
-      <x:c r="I86" s="31">
-        <x:v>46128.4612873727</x:v>
-      </x:c>
-      <x:c r="J86" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>20</x:v>
@@ -8698,25 +8713,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G87" s="29" t="s">
+      <x:c r="H87" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I87" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="H87" s="31">
-        <x:v>46122.6819179514</x:v>
-      </x:c>
-      <x:c r="I87" s="31">
-        <x:v>46122.6826717361</x:v>
-      </x:c>
-      <x:c r="J87" s="30" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>20</x:v>
@@ -8736,10 +8751,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="G88" s="29" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="H88" s="31">
         <x:v>46122.7261372338</x:v>
@@ -8762,10 +8777,10 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C89" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D89" s="30" t="s">
         <x:v>15</x:v>
@@ -8774,25 +8789,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>20</x:v>
@@ -8800,10 +8815,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C90" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D90" s="30" t="s">
         <x:v>15</x:v>
@@ -8812,25 +8827,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H90" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="G90" s="29" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H90" s="31">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I90" s="31">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J90" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>20</x:v>
@@ -8838,10 +8853,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>15</x:v>
@@ -8850,25 +8865,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="G91" s="29" t="s">
-        <x:v>269</x:v>
-      </x:c>
       <x:c r="H91" s="31">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>270</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>20</x:v>
@@ -8876,10 +8891,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>15</x:v>
@@ -8888,25 +8903,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G92" s="29" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H92" s="31">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I92" s="31">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J92" s="30" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="G92" s="29" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H92" s="31">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I92" s="31">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J92" s="30" t="s">
-        <x:v>274</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>20</x:v>
@@ -8914,10 +8929,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>15</x:v>
@@ -8926,25 +8941,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>20</x:v>
@@ -8952,10 +8967,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>15</x:v>
@@ -8964,25 +8979,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="G94" s="29" t="s">
-        <x:v>280</x:v>
-      </x:c>
       <x:c r="H94" s="31">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I94" s="31">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J94" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>20</x:v>
@@ -8990,10 +9005,10 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>15</x:v>
@@ -9008,19 +9023,19 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>283</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>20</x:v>
@@ -9028,10 +9043,10 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>15</x:v>
@@ -9040,25 +9055,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
+      <x:c r="H96" s="31">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>20</x:v>
@@ -9066,35 +9081,37 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>286</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="D97" s="30" t="s"/>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D97" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E97" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G97" s="29" t="s">
-        <x:v>289</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="H97" s="31">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>290</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>20</x:v>
@@ -9102,10 +9119,10 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>292</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>40</x:v>
@@ -9114,25 +9131,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
-        <x:v>293</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G98" s="29" t="s">
-        <x:v>294</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="H98" s="31">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46132.3879904745</x:v>
       </x:c>
       <x:c r="I98" s="31">
         <x:v>46023</x:v>
       </x:c>
       <x:c r="J98" s="30" t="s">
-        <x:v>295</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>20</x:v>
@@ -9143,141 +9160,223 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D99" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D99" s="30" t="s"/>
       <x:c r="E99" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
-        <x:v>298</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G99" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H99" s="31">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I99" s="31">
-        <x:v>46215</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J99" s="30" t="s">
-        <x:v>300</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>3006</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B102" s="17" t="s">
+    <x:row r="100" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B100" s="29" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C100" s="29" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E100" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F100" s="29" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G100" s="29" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H100" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I100" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J100" s="30" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="K100" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L100" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M100" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B101" s="29" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C101" s="29" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="D101" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E101" s="29" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F101" s="29" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G101" s="29" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H101" s="31">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I101" s="31">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J101" s="30" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="K101" s="32" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L101" s="33">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M101" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B104" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C102" s="18" t="s"/>
-      <x:c r="D102" s="18" t="s"/>
-      <x:c r="E102" s="19" t="s"/>
-      <x:c r="F102" s="19" t="s"/>
-    </x:row>
-    <x:row r="103" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B103" s="20" t="s">
+      <x:c r="C104" s="18" t="s"/>
+      <x:c r="D104" s="18" t="s"/>
+      <x:c r="E104" s="19" t="s"/>
+      <x:c r="F104" s="19" t="s"/>
+    </x:row>
+    <x:row r="105" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B105" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C103" s="21" t="s"/>
-      <x:c r="D103" s="21" t="s"/>
-      <x:c r="E103" s="21" t="s"/>
-      <x:c r="F103" s="22" t="s">
+      <x:c r="C105" s="21" t="s"/>
+      <x:c r="D105" s="21" t="s"/>
+      <x:c r="E105" s="21" t="s"/>
+      <x:c r="F105" s="22" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B104" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C104" s="24" t="s"/>
-      <x:c r="D104" s="24" t="s"/>
-      <x:c r="E104" s="24" t="s"/>
-      <x:c r="F104" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B105" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C105" s="24" t="s"/>
-      <x:c r="D105" s="24" t="s"/>
-      <x:c r="E105" s="24" t="s"/>
-      <x:c r="F105" s="25" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="23" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="24" t="s"/>
       <x:c r="D106" s="24" t="s"/>
       <x:c r="E106" s="24" t="s"/>
       <x:c r="F106" s="25" t="n">
-        <x:v>78</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="23" t="s">
-        <x:v>259</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s"/>
       <x:c r="D107" s="24" t="s"/>
       <x:c r="E107" s="24" t="s"/>
       <x:c r="F107" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="23" t="s">
-        <x:v>286</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s"/>
       <x:c r="D108" s="24" t="s"/>
       <x:c r="E108" s="24" t="s"/>
       <x:c r="F108" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
       <x:c r="B109" s="23" t="s">
-        <x:v>291</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C109" s="24" t="s"/>
       <x:c r="D109" s="24" t="s"/>
       <x:c r="E109" s="24" t="s"/>
       <x:c r="F109" s="25" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B110" s="23" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C110" s="24" t="s"/>
+      <x:c r="D110" s="24" t="s"/>
+      <x:c r="E110" s="24" t="s"/>
+      <x:c r="F110" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B111" s="23" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C111" s="24" t="s"/>
+      <x:c r="D111" s="24" t="s"/>
+      <x:c r="E111" s="24" t="s"/>
+      <x:c r="F111" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B112" s="23" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C112" s="24" t="s"/>
+      <x:c r="D112" s="24" t="s"/>
+      <x:c r="E112" s="24" t="s"/>
+      <x:c r="F112" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B110" s="26" t="s">
+    <x:row r="113" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B113" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C110" s="27" t="s"/>
-      <x:c r="D110" s="27" t="s"/>
-      <x:c r="E110" s="27" t="s"/>
-      <x:c r="F110" s="28" t="n">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C113" s="27" t="s"/>
+      <x:c r="D113" s="27" t="s"/>
+      <x:c r="E113" s="27" t="s"/>
+      <x:c r="F113" s="28" t="n">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
     <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10159,19 +10258,20 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
+  <x:mergeCells count="13">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B102:F102"/>
-    <x:mergeCell ref="B103:E103"/>
-    <x:mergeCell ref="B104:E104"/>
+    <x:mergeCell ref="B104:F104"/>
     <x:mergeCell ref="B105:E105"/>
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
     <x:mergeCell ref="B109:E109"/>
     <x:mergeCell ref="B110:E110"/>
+    <x:mergeCell ref="B111:E111"/>
+    <x:mergeCell ref="B112:E112"/>
+    <x:mergeCell ref="B113:E113"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="309">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -213,6 +213,24 @@
     <x:t>sczxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08335</x:t>
   </x:si>
   <x:si>
@@ -222,24 +240,6 @@
     <x:t>123wesdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1325-890</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdxzcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08339</x:t>
   </x:si>
   <x:si>
@@ -267,49 +267,109 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -321,15 +381,6 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08145</x:t>
   </x:si>
   <x:si>
@@ -339,51 +390,6 @@
     <x:t>sdf</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
@@ -501,10 +507,10 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
@@ -534,10 +540,13 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -546,6 +555,90 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -555,57 +648,30 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08190</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1301-555</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08189</x:t>
   </x:si>
   <x:si>
@@ -615,64 +681,40 @@
     <x:t>zsdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08188</x:t>
@@ -681,10 +723,82 @@
     <x:t>61-4-2026-1299-939</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -696,120 +810,6 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -865,6 +865,15 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1228-788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08621-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1342-777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdasd</x:t>
   </x:si>
   <x:si>
     <x:t>TEST</x:t>
@@ -5945,10 +5954,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>64</x:v>
@@ -5957,7 +5966,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>20</x:v>
@@ -6021,10 +6030,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>70</x:v>
@@ -6033,7 +6042,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>20</x:v>
@@ -6173,19 +6182,19 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>20</x:v>
@@ -6205,25 +6214,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>20</x:v>
@@ -6243,25 +6252,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>20</x:v>
@@ -6281,10 +6290,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="31">
         <x:v>46120.7129542245</x:v>
@@ -6319,25 +6328,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G24" s="29" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
@@ -6357,25 +6366,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>20</x:v>
@@ -6395,25 +6404,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="29" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>20</x:v>
@@ -6439,19 +6448,19 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
@@ -6471,25 +6480,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="29" t="s">
+      <x:c r="H28" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I28" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J28" s="30" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="H28" s="31">
-        <x:v>46121.4966047917</x:v>
-      </x:c>
-      <x:c r="I28" s="31">
-        <x:v>46121.4974146412</x:v>
-      </x:c>
-      <x:c r="J28" s="30" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>20</x:v>
@@ -6509,10 +6518,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="G29" s="29" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="H29" s="31">
         <x:v>46121.5149441551</x:v>
@@ -6521,7 +6530,7 @@
         <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
@@ -6547,25 +6556,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G30" s="29" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="H30" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
@@ -6585,10 +6594,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="G31" s="29" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="31">
         <x:v>46119.8029380671</x:v>
@@ -6623,10 +6632,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="G32" s="29" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="H32" s="31">
         <x:v>46121.5183984954</x:v>
@@ -6635,7 +6644,7 @@
         <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
@@ -6661,10 +6670,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="G33" s="29" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="31">
         <x:v>46122.1299166204</x:v>
@@ -6699,25 +6708,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G34" s="29" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G34" s="29" t="s">
+      <x:c r="H34" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I34" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="H34" s="31">
-        <x:v>46121.2464636111</x:v>
-      </x:c>
-      <x:c r="I34" s="31">
-        <x:v>46121.3217277662</x:v>
-      </x:c>
-      <x:c r="J34" s="30" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
@@ -6737,25 +6746,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G35" s="29" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G35" s="29" t="s">
+      <x:c r="H35" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I35" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="H35" s="31">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I35" s="31">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J35" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
@@ -6781,19 +6790,19 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>20</x:v>
@@ -6813,25 +6822,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G37" s="29" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G37" s="29" t="s">
+      <x:c r="H37" s="31">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I37" s="31">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J37" s="30" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="H37" s="31">
-        <x:v>46119.7297941435</x:v>
-      </x:c>
-      <x:c r="I37" s="31">
-        <x:v>46119.731450544</x:v>
-      </x:c>
-      <x:c r="J37" s="30" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
@@ -6857,19 +6866,19 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>20</x:v>
@@ -6889,25 +6898,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G39" s="29" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G39" s="29" t="s">
+      <x:c r="H39" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I39" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J39" s="30" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="H39" s="31">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I39" s="31">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J39" s="30" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>20</x:v>
@@ -6927,25 +6936,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G40" s="29" t="s">
+      <x:c r="H40" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I40" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J40" s="30" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="H40" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I40" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J40" s="30" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>20</x:v>
@@ -6965,25 +6974,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G41" s="29" t="s">
+      <x:c r="H41" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>20</x:v>
@@ -7003,25 +7012,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G42" s="29" t="s">
+      <x:c r="H42" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I42" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="H42" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I42" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J42" s="30" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>20</x:v>
@@ -7041,25 +7050,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G43" s="29" t="s">
+      <x:c r="H43" s="31">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I43" s="31">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="H43" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I43" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J43" s="30" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>20</x:v>
@@ -7079,25 +7088,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
+      <x:c r="H44" s="31">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>20</x:v>
@@ -7123,19 +7132,19 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>20</x:v>
@@ -7155,25 +7164,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G46" s="29" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G46" s="29" t="s">
+      <x:c r="H46" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I46" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J46" s="30" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="H46" s="31">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I46" s="31">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J46" s="30" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>20</x:v>
@@ -7193,25 +7202,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G47" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G47" s="29" t="s">
+      <x:c r="H47" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I47" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="H47" s="31">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I47" s="31">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J47" s="30" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>20</x:v>
@@ -7231,25 +7240,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G48" s="29" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="G48" s="29" t="s">
+      <x:c r="H48" s="31">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I48" s="31">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J48" s="30" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="H48" s="31">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I48" s="31">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J48" s="30" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
@@ -7269,25 +7278,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G49" s="29" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G49" s="29" t="s">
+      <x:c r="H49" s="31">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I49" s="31">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J49" s="30" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="H49" s="31">
-        <x:v>46122.3569147569</x:v>
-      </x:c>
-      <x:c r="I49" s="31">
-        <x:v>46122.3577305324</x:v>
-      </x:c>
-      <x:c r="J49" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
@@ -7313,19 +7322,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>20</x:v>
@@ -7351,19 +7360,19 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>20</x:v>
@@ -7389,19 +7398,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
@@ -7421,25 +7430,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G53" s="29" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G53" s="29" t="s">
+      <x:c r="H53" s="31">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I53" s="31">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J53" s="30" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="H53" s="31">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I53" s="31">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J53" s="30" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>20</x:v>
@@ -7465,19 +7474,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>20</x:v>
@@ -7503,19 +7512,19 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>20</x:v>
@@ -7535,25 +7544,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>20</x:v>
@@ -7579,19 +7588,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>20</x:v>
@@ -7617,19 +7626,19 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>20</x:v>
@@ -7649,25 +7658,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G59" s="29" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="G59" s="29" t="s">
-        <x:v>182</x:v>
-      </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>20</x:v>
@@ -7687,25 +7696,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>20</x:v>
@@ -7725,25 +7734,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>20</x:v>
@@ -7763,25 +7772,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>20</x:v>
@@ -7801,25 +7810,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>20</x:v>
@@ -7839,25 +7848,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>198</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>20</x:v>
@@ -7877,25 +7886,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>20</x:v>
@@ -7915,25 +7924,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>20</x:v>
@@ -7953,25 +7962,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>20</x:v>
@@ -7991,25 +8000,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>209</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>20</x:v>
@@ -8029,25 +8038,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G69" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>20</x:v>
@@ -8067,25 +8076,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H70" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I70" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="G70" s="29" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H70" s="31">
-        <x:v>46128.4605351157</x:v>
-      </x:c>
-      <x:c r="I70" s="31">
-        <x:v>46128.4612873727</x:v>
-      </x:c>
-      <x:c r="J70" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>20</x:v>
@@ -8105,25 +8114,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G71" s="29" t="s">
-        <x:v>215</x:v>
-      </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>20</x:v>
@@ -8143,25 +8152,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="G72" s="29" t="s">
+      <x:c r="H72" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I72" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J72" s="30" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="H72" s="31">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I72" s="31">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J72" s="30" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>20</x:v>
@@ -8225,10 +8234,10 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
         <x:v>222</x:v>
@@ -8237,7 +8246,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>20</x:v>
@@ -8263,19 +8272,19 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>20</x:v>
@@ -8301,19 +8310,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>20</x:v>
@@ -8333,25 +8342,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>229</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>20</x:v>
@@ -8377,19 +8386,19 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>232</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>20</x:v>
@@ -8409,25 +8418,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>235</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>20</x:v>
@@ -8447,25 +8456,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G80" s="29" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>20</x:v>
@@ -8485,25 +8494,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G81" s="29" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>20</x:v>
@@ -8523,25 +8532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H82" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I82" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J82" s="30" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H82" s="31">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I82" s="31">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J82" s="30" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>20</x:v>
@@ -8561,25 +8570,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G83" s="29" t="s">
-        <x:v>243</x:v>
-      </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>244</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>20</x:v>
@@ -8599,25 +8608,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H84" s="31">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I84" s="31">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J84" s="30" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H84" s="31">
-        <x:v>46122.6795081481</x:v>
-      </x:c>
-      <x:c r="I84" s="31">
-        <x:v>46122.6802186921</x:v>
-      </x:c>
-      <x:c r="J84" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>20</x:v>
@@ -8637,25 +8646,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G85" s="29" t="s">
+      <x:c r="H85" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>20</x:v>
@@ -8675,25 +8684,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G86" s="29" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="G86" s="29" t="s">
+      <x:c r="H86" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I86" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J86" s="30" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="H86" s="31">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I86" s="31">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J86" s="30" t="s">
-        <x:v>252</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>20</x:v>
@@ -8713,10 +8722,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="G87" s="29" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="H87" s="31">
         <x:v>46123.4162791088</x:v>
@@ -8725,7 +8734,7 @@
         <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
@@ -8751,25 +8760,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G88" s="29" t="s">
+      <x:c r="H88" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I88" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J88" s="30" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="H88" s="31">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I88" s="31">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J88" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>20</x:v>
@@ -8795,10 +8804,10 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
         <x:v>260</x:v>
@@ -8807,7 +8816,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>20</x:v>
@@ -9008,34 +9017,34 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>280</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E95" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G95" s="29" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="G95" s="29" t="s">
+      <x:c r="H95" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I95" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J95" s="30" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="H95" s="31">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I95" s="31">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J95" s="30" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="K95" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>20</x:v>
@@ -9046,7 +9055,7 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>15</x:v>
@@ -9055,25 +9064,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G96" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H96" s="31">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I96" s="31">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J96" s="30" t="s">
-        <x:v>285</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>20</x:v>
@@ -9084,7 +9093,7 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>15</x:v>
@@ -9099,19 +9108,19 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="H97" s="31">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.439490081</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>20</x:v>
@@ -9119,37 +9128,37 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>288</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>280</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E98" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G98" s="29" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H98" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I98" s="31">
-        <x:v>46023</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J98" s="30" t="s">
-        <x:v>290</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>20</x:v>
@@ -9160,32 +9169,34 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D99" s="30" t="s"/>
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D99" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="E99" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G99" s="29" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H99" s="31">
+        <x:v>46132.3879904745</x:v>
+      </x:c>
+      <x:c r="I99" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J99" s="30" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="G99" s="29" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="H99" s="31">
-        <x:v>46124.1588481829</x:v>
-      </x:c>
-      <x:c r="I99" s="31">
-        <x:v>46124.1588689236</x:v>
-      </x:c>
-      <x:c r="J99" s="30" t="s">
-        <x:v>295</x:v>
-      </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>20</x:v>
@@ -9193,37 +9204,35 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="D100" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="s"/>
       <x:c r="E100" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G100" s="29" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H100" s="31">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I100" s="31">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J100" s="30" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="G100" s="29" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H100" s="31">
-        <x:v>46124.1607868981</x:v>
-      </x:c>
-      <x:c r="I100" s="31">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="J100" s="30" t="s">
-        <x:v>300</x:v>
-      </x:c>
       <x:c r="K100" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>20</x:v>
@@ -9231,117 +9240,144 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>301</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="D101" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E101" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F101" s="29" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G101" s="29" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="F101" s="29" t="s">
+      <x:c r="H101" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I101" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J101" s="30" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="G101" s="29" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H101" s="31">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I101" s="31">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J101" s="30" t="s">
-        <x:v>305</x:v>
-      </x:c>
       <x:c r="K101" s="32" t="n">
-        <x:v>3006</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1624131829</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B102" s="29" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C102" s="29" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="D102" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E102" s="29" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F102" s="29" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G102" s="29" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H102" s="31">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I102" s="31">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J102" s="30" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="K102" s="32" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L102" s="33">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M102" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B104" s="17" t="s">
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B105" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C104" s="18" t="s"/>
-      <x:c r="D104" s="18" t="s"/>
-      <x:c r="E104" s="19" t="s"/>
-      <x:c r="F104" s="19" t="s"/>
-    </x:row>
-    <x:row r="105" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B105" s="20" t="s">
+      <x:c r="C105" s="18" t="s"/>
+      <x:c r="D105" s="18" t="s"/>
+      <x:c r="E105" s="19" t="s"/>
+      <x:c r="F105" s="19" t="s"/>
+    </x:row>
+    <x:row r="106" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B106" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C105" s="21" t="s"/>
-      <x:c r="D105" s="21" t="s"/>
-      <x:c r="E105" s="21" t="s"/>
-      <x:c r="F105" s="22" t="s">
+      <x:c r="C106" s="21" t="s"/>
+      <x:c r="D106" s="21" t="s"/>
+      <x:c r="E106" s="21" t="s"/>
+      <x:c r="F106" s="22" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B106" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C106" s="24" t="s"/>
-      <x:c r="D106" s="24" t="s"/>
-      <x:c r="E106" s="24" t="s"/>
-      <x:c r="F106" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="23" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s"/>
       <x:c r="D107" s="24" t="s"/>
       <x:c r="E107" s="24" t="s"/>
       <x:c r="F107" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="23" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s"/>
       <x:c r="D108" s="24" t="s"/>
       <x:c r="E108" s="24" t="s"/>
       <x:c r="F108" s="25" t="n">
-        <x:v>79</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
       <x:c r="B109" s="23" t="s">
-        <x:v>261</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C109" s="24" t="s"/>
       <x:c r="D109" s="24" t="s"/>
       <x:c r="E109" s="24" t="s"/>
       <x:c r="F109" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
       <x:c r="B110" s="23" t="s">
-        <x:v>288</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s"/>
       <x:c r="D110" s="24" t="s"/>
       <x:c r="E110" s="24" t="s"/>
       <x:c r="F110" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
@@ -9357,27 +9393,37 @@
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
       <x:c r="E112" s="24" t="s"/>
       <x:c r="F112" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B113" s="23" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C113" s="24" t="s"/>
+      <x:c r="D113" s="24" t="s"/>
+      <x:c r="E113" s="24" t="s"/>
+      <x:c r="F113" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B113" s="26" t="s">
+    <x:row r="114" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B114" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C113" s="27" t="s"/>
-      <x:c r="D113" s="27" t="s"/>
-      <x:c r="E113" s="27" t="s"/>
-      <x:c r="F113" s="28" t="n">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C114" s="27" t="s"/>
+      <x:c r="D114" s="27" t="s"/>
+      <x:c r="E114" s="27" t="s"/>
+      <x:c r="F114" s="28" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
     <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10262,8 +10308,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B104:F104"/>
-    <x:mergeCell ref="B105:E105"/>
+    <x:mergeCell ref="B105:F105"/>
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
@@ -10272,6 +10317,7 @@
     <x:mergeCell ref="B111:E111"/>
     <x:mergeCell ref="B112:E112"/>
     <x:mergeCell ref="B113:E113"/>
+    <x:mergeCell ref="B114:E114"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="309">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="311">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -222,6 +222,15 @@
     <x:t>zxcasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08337</x:t>
   </x:si>
   <x:si>
@@ -231,13 +240,10 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08339</x:t>
@@ -267,6 +273,51 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
   </x:si>
   <x:si>
@@ -276,49 +327,232 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
@@ -327,226 +561,91 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -555,138 +654,45 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08169</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1283-909</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08187</x:t>
   </x:si>
   <x:si>
@@ -696,12 +702,90 @@
     <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08173</x:t>
   </x:si>
   <x:si>
@@ -711,103 +795,25 @@
     <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08174</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5992,10 +5998,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>67</x:v>
@@ -6004,7 +6010,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>20</x:v>
@@ -6030,10 +6036,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>70</x:v>
@@ -6042,7 +6048,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>20</x:v>
@@ -6068,19 +6074,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>20</x:v>
@@ -6100,25 +6106,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G18" s="29" t="s">
+      <x:c r="H18" s="31">
+        <x:v>46126.4716621296</x:v>
+      </x:c>
+      <x:c r="I18" s="31">
+        <x:v>46126.4737503704</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46126.4798427199</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>46126.4809562153</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>20</x:v>
@@ -6138,25 +6144,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G19" s="29" t="s">
+      <x:c r="H19" s="31">
+        <x:v>46126.4798427199</x:v>
+      </x:c>
+      <x:c r="I19" s="31">
+        <x:v>46126.4809562153</x:v>
+      </x:c>
+      <x:c r="J19" s="30" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="H19" s="31">
-        <x:v>46126.455832662</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
-        <x:v>46126.4740829051</x:v>
-      </x:c>
-      <x:c r="J19" s="30" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>20</x:v>
@@ -6167,34 +6173,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D20" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="s">
+      <x:c r="H20" s="31">
+        <x:v>46126.455832662</x:v>
+      </x:c>
+      <x:c r="I20" s="31">
+        <x:v>46126.4740829051</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="H20" s="31">
-        <x:v>46121.2464636111</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>46121.3217277662</x:v>
-      </x:c>
-      <x:c r="J20" s="30" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>20</x:v>
@@ -6214,25 +6220,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G21" s="29" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G21" s="29" t="s">
+      <x:c r="H21" s="31">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I21" s="31">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J21" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H21" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I21" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J21" s="30" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>20</x:v>
@@ -6252,10 +6258,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G22" s="29" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="G22" s="29" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="31">
         <x:v>46120.2362105324</x:v>
@@ -6264,7 +6270,7 @@
         <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
@@ -6290,25 +6296,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="29" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H23" s="31">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I23" s="31">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="G23" s="29" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H23" s="31">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I23" s="31">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J23" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>20</x:v>
@@ -6328,25 +6334,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G24" s="29" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G24" s="29" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="H24" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
@@ -6366,25 +6372,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H25" s="31">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I25" s="31">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J25" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G25" s="29" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H25" s="31">
-        <x:v>46120.2349196412</x:v>
-      </x:c>
-      <x:c r="I25" s="31">
-        <x:v>46120.5229746296</x:v>
-      </x:c>
-      <x:c r="J25" s="30" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>20</x:v>
@@ -6404,10 +6410,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G26" s="29" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
         <x:v>46121.2273626852</x:v>
@@ -6442,25 +6448,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G27" s="29" t="s">
+      <x:c r="H27" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
@@ -6486,10 +6492,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
         <x:v>102</x:v>
@@ -6498,7 +6504,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>20</x:v>
@@ -6562,19 +6568,19 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
@@ -6594,25 +6600,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G31" s="29" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>20</x:v>
@@ -6632,25 +6638,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G32" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>20</x:v>
@@ -6670,25 +6676,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G33" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>20</x:v>
@@ -6708,25 +6714,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G34" s="29" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
@@ -6746,25 +6752,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G35" s="29" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
@@ -6828,19 +6834,19 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
@@ -6860,10 +6866,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G38" s="29" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="G38" s="29" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="H38" s="31">
         <x:v>46119.7297941435</x:v>
@@ -6872,7 +6878,7 @@
         <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
@@ -6898,10 +6904,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G39" s="29" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="G39" s="29" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="H39" s="31">
         <x:v>46118.4219285995</x:v>
@@ -6910,7 +6916,7 @@
         <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
@@ -6936,10 +6942,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="G40" s="29" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="31">
         <x:v>46118.7424944097</x:v>
@@ -6948,7 +6954,7 @@
         <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
@@ -6974,10 +6980,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="G41" s="29" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="H41" s="31">
         <x:v>46118.7562945255</x:v>
@@ -6986,7 +6992,7 @@
         <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
@@ -7012,10 +7018,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="G42" s="29" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="H42" s="31">
         <x:v>46119.0668949653</x:v>
@@ -7024,7 +7030,7 @@
         <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
@@ -7050,10 +7056,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="G43" s="29" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="H43" s="31">
         <x:v>46119.0739296412</x:v>
@@ -7062,7 +7068,7 @@
         <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
@@ -7088,10 +7094,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="G44" s="29" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="H44" s="31">
         <x:v>46119.1921340856</x:v>
@@ -7100,7 +7106,7 @@
         <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
@@ -7126,10 +7132,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="G45" s="29" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="H45" s="31">
         <x:v>46119.4681336458</x:v>
@@ -7164,25 +7170,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G46" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G46" s="29" t="s">
-        <x:v>149</x:v>
-      </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>20</x:v>
@@ -7202,25 +7208,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G47" s="29" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H47" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I47" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="G47" s="29" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H47" s="31">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I47" s="31">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J47" s="30" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>20</x:v>
@@ -7240,25 +7246,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G48" s="29" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H48" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I48" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J48" s="30" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="G48" s="29" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H48" s="31">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I48" s="31">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J48" s="30" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
@@ -7278,25 +7284,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G49" s="29" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H49" s="31">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I49" s="31">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J49" s="30" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="G49" s="29" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H49" s="31">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I49" s="31">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J49" s="30" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
@@ -7316,25 +7322,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G50" s="29" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H50" s="31">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I50" s="31">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="G50" s="29" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H50" s="31">
-        <x:v>46122.36782125</x:v>
-      </x:c>
-      <x:c r="I50" s="31">
-        <x:v>46122.3686719907</x:v>
-      </x:c>
-      <x:c r="J50" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>20</x:v>
@@ -7354,25 +7360,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G51" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G51" s="29" t="s">
+      <x:c r="H51" s="31">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I51" s="31">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J51" s="30" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="H51" s="31">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I51" s="31">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J51" s="30" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>20</x:v>
@@ -7398,19 +7404,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
@@ -7436,19 +7442,19 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>20</x:v>
@@ -7468,25 +7474,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G54" s="29" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G54" s="29" t="s">
+      <x:c r="H54" s="31">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I54" s="31">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J54" s="30" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="H54" s="31">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I54" s="31">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J54" s="30" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>20</x:v>
@@ -7512,19 +7518,19 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>20</x:v>
@@ -7544,25 +7550,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G56" s="29" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="G56" s="29" t="s">
+      <x:c r="H56" s="31">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I56" s="31">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J56" s="30" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="H56" s="31">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I56" s="31">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J56" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>20</x:v>
@@ -7588,19 +7594,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>20</x:v>
@@ -7626,19 +7632,19 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>20</x:v>
@@ -7658,16 +7664,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
         <x:v>29</x:v>
@@ -7676,7 +7682,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>20</x:v>
@@ -7696,16 +7702,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>29</x:v>
@@ -7714,7 +7720,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>20</x:v>
@@ -7734,25 +7740,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>20</x:v>
@@ -7778,10 +7784,10 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
         <x:v>189</x:v>
@@ -7790,7 +7796,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>20</x:v>
@@ -7816,10 +7822,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
         <x:v>192</x:v>
@@ -7828,7 +7834,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>20</x:v>
@@ -7854,19 +7860,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>20</x:v>
@@ -7886,25 +7892,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>197</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>20</x:v>
@@ -7930,10 +7936,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>200</x:v>
@@ -7942,7 +7948,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>20</x:v>
@@ -7968,10 +7974,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
         <x:v>203</x:v>
@@ -7980,7 +7986,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>20</x:v>
@@ -8006,10 +8012,10 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
         <x:v>206</x:v>
@@ -8018,7 +8024,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>20</x:v>
@@ -8044,19 +8050,19 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>20</x:v>
@@ -8076,25 +8082,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
+      <x:c r="H70" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I70" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="H70" s="31">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I70" s="31">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J70" s="30" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>20</x:v>
@@ -8114,25 +8120,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G71" s="29" t="s">
+      <x:c r="H71" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I71" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J71" s="30" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="H71" s="31">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I71" s="31">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J71" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>20</x:v>
@@ -8158,19 +8164,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>217</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>20</x:v>
@@ -8190,25 +8196,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G73" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G73" s="29" t="s">
+      <x:c r="H73" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I73" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J73" s="30" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="H73" s="31">
-        <x:v>46132.4200429282</x:v>
-      </x:c>
-      <x:c r="I73" s="31">
-        <x:v>46132.4214079282</x:v>
-      </x:c>
-      <x:c r="J73" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>20</x:v>
@@ -8234,19 +8240,19 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>20</x:v>
@@ -8266,25 +8272,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G75" s="29" t="s">
+      <x:c r="H75" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I75" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J75" s="30" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="H75" s="31">
-        <x:v>46122.3974322338</x:v>
-      </x:c>
-      <x:c r="I75" s="31">
-        <x:v>46122.3980999421</x:v>
-      </x:c>
-      <x:c r="J75" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>20</x:v>
@@ -8310,10 +8316,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
         <x:v>227</x:v>
@@ -8322,7 +8328,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>20</x:v>
@@ -8348,19 +8354,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>20</x:v>
@@ -8380,25 +8386,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G78" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>20</x:v>
@@ -8418,25 +8424,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G79" s="29" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>20</x:v>
@@ -8456,25 +8462,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G80" s="29" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>20</x:v>
@@ -8494,25 +8500,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G81" s="29" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>20</x:v>
@@ -8532,25 +8538,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
-        <x:v>238</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G82" s="29" t="s">
-        <x:v>239</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>240</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>20</x:v>
@@ -8570,25 +8576,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G83" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>20</x:v>
@@ -8608,25 +8614,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>245</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>20</x:v>
@@ -8646,25 +8652,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>248</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>20</x:v>
@@ -8684,25 +8690,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>251</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>20</x:v>
@@ -8722,25 +8728,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>20</x:v>
@@ -8760,25 +8766,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>20</x:v>
@@ -8798,25 +8804,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>260</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>20</x:v>
@@ -8824,10 +8830,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C90" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D90" s="30" t="s">
         <x:v>15</x:v>
@@ -8836,25 +8842,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G90" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>265</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>20</x:v>
@@ -8862,10 +8868,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>15</x:v>
@@ -8874,25 +8880,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H91" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I91" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J91" s="30" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="G91" s="29" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H91" s="31">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I91" s="31">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J91" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>20</x:v>
@@ -8900,10 +8906,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>15</x:v>
@@ -8912,25 +8918,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G92" s="29" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="G92" s="29" t="s">
-        <x:v>271</x:v>
-      </x:c>
       <x:c r="H92" s="31">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>272</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>20</x:v>
@@ -8938,10 +8944,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>15</x:v>
@@ -8950,25 +8956,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>276</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>20</x:v>
@@ -8976,10 +8982,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>15</x:v>
@@ -8988,25 +8994,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H94" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I94" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J94" s="30" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="G94" s="29" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H94" s="31">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I94" s="31">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J94" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>20</x:v>
@@ -9014,16 +9020,16 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>45</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E95" s="29" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
         <x:v>280</x:v>
@@ -9032,19 +9038,19 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46132.3798789699</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46132.3799006944</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>282</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
-        <x:v>3031</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46133.1738098148</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>20</x:v>
@@ -9052,37 +9058,37 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>283</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E96" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H96" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="K96" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>20</x:v>
@@ -9090,10 +9096,10 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>15</x:v>
@@ -9108,19 +9114,19 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="H97" s="31">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>288</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>20</x:v>
@@ -9128,10 +9134,10 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>15</x:v>
@@ -9140,25 +9146,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G98" s="29" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="G98" s="29" t="s">
+      <x:c r="H98" s="31">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I98" s="31">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J98" s="30" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="H98" s="31">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I98" s="31">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J98" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>20</x:v>
@@ -9166,37 +9172,37 @@
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
       <x:c r="B99" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>283</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D99" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E99" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G99" s="29" t="s">
         <x:v>292</x:v>
       </x:c>
       <x:c r="H99" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I99" s="31">
-        <x:v>46023</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J99" s="30" t="s">
-        <x:v>293</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>20</x:v>
@@ -9204,35 +9210,37 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="D100" s="30" t="s"/>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="E100" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
-        <x:v>296</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G100" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H100" s="31">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46132.3879904745</x:v>
       </x:c>
       <x:c r="I100" s="31">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46023</x:v>
       </x:c>
       <x:c r="J100" s="30" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>20</x:v>
@@ -9240,37 +9248,35 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="D101" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D101" s="30" t="s"/>
       <x:c r="E101" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F101" s="29" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="G101" s="29" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="H101" s="31">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I101" s="31">
-        <x:v>46023</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J101" s="30" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>20</x:v>
@@ -9278,122 +9284,149 @@
     </x:row>
     <x:row r="102" spans="1:28" ht="30" customHeight="1">
       <x:c r="B102" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C102" s="29" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D102" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E102" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F102" s="29" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G102" s="29" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H102" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I102" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J102" s="30" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="F102" s="29" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="G102" s="29" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="H102" s="31">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I102" s="31">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J102" s="30" t="s">
-        <x:v>308</x:v>
-      </x:c>
       <x:c r="K102" s="32" t="n">
-        <x:v>3006</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="L102" s="33">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1624131829</x:v>
       </x:c>
       <x:c r="M102" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B103" s="29" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C103" s="29" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D103" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E103" s="29" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F103" s="29" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G103" s="29" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H103" s="31">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I103" s="31">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J103" s="30" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="K103" s="32" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L103" s="33">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M103" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B105" s="17" t="s">
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B106" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C105" s="18" t="s"/>
-      <x:c r="D105" s="18" t="s"/>
-      <x:c r="E105" s="19" t="s"/>
-      <x:c r="F105" s="19" t="s"/>
-    </x:row>
-    <x:row r="106" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B106" s="20" t="s">
+      <x:c r="C106" s="18" t="s"/>
+      <x:c r="D106" s="18" t="s"/>
+      <x:c r="E106" s="19" t="s"/>
+      <x:c r="F106" s="19" t="s"/>
+    </x:row>
+    <x:row r="107" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B107" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C106" s="21" t="s"/>
-      <x:c r="D106" s="21" t="s"/>
-      <x:c r="E106" s="21" t="s"/>
-      <x:c r="F106" s="22" t="s">
+      <x:c r="C107" s="21" t="s"/>
+      <x:c r="D107" s="21" t="s"/>
+      <x:c r="E107" s="21" t="s"/>
+      <x:c r="F107" s="22" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B107" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C107" s="24" t="s"/>
-      <x:c r="D107" s="24" t="s"/>
-      <x:c r="E107" s="24" t="s"/>
-      <x:c r="F107" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="23" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s"/>
       <x:c r="D108" s="24" t="s"/>
       <x:c r="E108" s="24" t="s"/>
       <x:c r="F108" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
       <x:c r="B109" s="23" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C109" s="24" t="s"/>
       <x:c r="D109" s="24" t="s"/>
       <x:c r="E109" s="24" t="s"/>
       <x:c r="F109" s="25" t="n">
-        <x:v>79</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
       <x:c r="B110" s="23" t="s">
-        <x:v>261</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s"/>
       <x:c r="D110" s="24" t="s"/>
       <x:c r="E110" s="24" t="s"/>
       <x:c r="F110" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>291</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
       <x:c r="E111" s="24" t="s"/>
       <x:c r="F111" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
@@ -9404,27 +9437,37 @@
     </x:row>
     <x:row r="113" spans="1:28" ht="18" customHeight="1">
       <x:c r="B113" s="23" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C113" s="24" t="s"/>
       <x:c r="D113" s="24" t="s"/>
       <x:c r="E113" s="24" t="s"/>
       <x:c r="F113" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B114" s="23" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C114" s="24" t="s"/>
+      <x:c r="D114" s="24" t="s"/>
+      <x:c r="E114" s="24" t="s"/>
+      <x:c r="F114" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B114" s="26" t="s">
+    <x:row r="115" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B115" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C114" s="27" t="s"/>
-      <x:c r="D114" s="27" t="s"/>
-      <x:c r="E114" s="27" t="s"/>
-      <x:c r="F114" s="28" t="n">
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C115" s="27" t="s"/>
+      <x:c r="D115" s="27" t="s"/>
+      <x:c r="E115" s="27" t="s"/>
+      <x:c r="F115" s="28" t="n">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
     <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10308,8 +10351,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B105:F105"/>
-    <x:mergeCell ref="B106:E106"/>
+    <x:mergeCell ref="B106:F106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
     <x:mergeCell ref="B109:E109"/>
@@ -10318,6 +10360,7 @@
     <x:mergeCell ref="B112:E112"/>
     <x:mergeCell ref="B113:E113"/>
     <x:mergeCell ref="B114:E114"/>
+    <x:mergeCell ref="B115:E115"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="311">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -240,39 +240,54 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08682</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1346-976</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
@@ -468,76 +483,115 @@
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08625</x:t>
@@ -546,19 +600,112 @@
     <x:t>61-4-2026-1344-095</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -570,136 +717,64 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -720,6 +795,15 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
   </x:si>
   <x:si>
@@ -729,12 +813,6 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
   </x:si>
   <x:si>
@@ -751,69 +829,6 @@
   </x:si>
   <x:si>
     <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -6074,19 +6089,19 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46133.5419909606</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46133.5429334722</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46133.5457238194</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>20</x:v>
@@ -6106,25 +6121,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G18" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>20</x:v>
@@ -6188,10 +6203,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
         <x:v>81</x:v>
@@ -6200,7 +6215,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>20</x:v>
@@ -6211,13 +6226,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D21" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
         <x:v>82</x:v>
@@ -6226,19 +6241,19 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46133.0575652778</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46134.4615905556</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>20</x:v>
@@ -6249,13 +6264,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
         <x:v>85</x:v>
@@ -6264,19 +6279,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>20</x:v>
@@ -6302,19 +6317,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>20</x:v>
@@ -6340,19 +6355,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
@@ -6378,10 +6393,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
         <x:v>94</x:v>
@@ -6390,7 +6405,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>20</x:v>
@@ -6416,10 +6431,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
         <x:v>29</x:v>
@@ -6428,7 +6443,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>20</x:v>
@@ -6454,10 +6469,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>99</x:v>
@@ -6466,7 +6481,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
@@ -6492,19 +6507,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>20</x:v>
@@ -6524,25 +6539,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G29" s="29" t="s">
+      <x:c r="H29" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I29" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J29" s="30" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="H29" s="31">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I29" s="31">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J29" s="30" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>20</x:v>
@@ -6562,25 +6577,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G30" s="29" t="s">
+      <x:c r="H30" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I30" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J30" s="30" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="H30" s="31">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I30" s="31">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J30" s="30" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
@@ -6600,25 +6615,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
+      <x:c r="H31" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I31" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J31" s="30" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="H31" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I31" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J31" s="30" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>20</x:v>
@@ -6638,25 +6653,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G32" s="29" t="s">
+      <x:c r="H32" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I32" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J32" s="30" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="H32" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I32" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J32" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>20</x:v>
@@ -6682,10 +6697,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
         <x:v>116</x:v>
@@ -6694,7 +6709,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>20</x:v>
@@ -6720,19 +6735,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
@@ -6758,19 +6773,19 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
@@ -6790,25 +6805,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G36" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>20</x:v>
@@ -6828,25 +6843,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
@@ -6866,25 +6881,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>20</x:v>
@@ -6904,25 +6919,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>20</x:v>
@@ -6948,19 +6963,19 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>20</x:v>
@@ -6980,25 +6995,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G41" s="29" t="s">
+      <x:c r="H41" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>20</x:v>
@@ -7018,25 +7033,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G42" s="29" t="s">
+      <x:c r="H42" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I42" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="H42" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I42" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J42" s="30" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>20</x:v>
@@ -7056,25 +7071,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G43" s="29" t="s">
+      <x:c r="H43" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I43" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="H43" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I43" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J43" s="30" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>20</x:v>
@@ -7094,25 +7109,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
+      <x:c r="H44" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>20</x:v>
@@ -7132,25 +7147,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
+      <x:c r="H45" s="31">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>20</x:v>
@@ -7176,19 +7191,19 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>20</x:v>
@@ -7208,25 +7223,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G47" s="29" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>20</x:v>
@@ -7252,10 +7267,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
         <x:v>154</x:v>
@@ -7264,7 +7279,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
@@ -7290,10 +7305,10 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
         <x:v>157</x:v>
@@ -7302,7 +7317,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
@@ -7328,10 +7343,10 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
         <x:v>160</x:v>
@@ -7340,7 +7355,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>20</x:v>
@@ -7366,10 +7381,10 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
         <x:v>163</x:v>
@@ -7378,7 +7393,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>20</x:v>
@@ -7404,19 +7419,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
@@ -7436,25 +7451,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G53" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>20</x:v>
@@ -7474,25 +7489,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>20</x:v>
@@ -7518,19 +7533,19 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>20</x:v>
@@ -7550,25 +7565,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>20</x:v>
@@ -7594,19 +7609,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>20</x:v>
@@ -7626,25 +7641,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>20</x:v>
@@ -7670,19 +7685,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>20</x:v>
@@ -7708,10 +7723,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>29</x:v>
@@ -7720,7 +7735,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>20</x:v>
@@ -7746,10 +7761,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
         <x:v>29</x:v>
@@ -7758,7 +7773,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>20</x:v>
@@ -7784,19 +7799,19 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>20</x:v>
@@ -7816,25 +7831,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G63" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G63" s="29" t="s">
-        <x:v>191</x:v>
-      </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>20</x:v>
@@ -7854,25 +7869,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G64" s="29" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H64" s="31">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I64" s="31">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J64" s="30" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="G64" s="29" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H64" s="31">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I64" s="31">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J64" s="30" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>20</x:v>
@@ -7892,25 +7907,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G65" s="29" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H65" s="31">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I65" s="31">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J65" s="30" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="G65" s="29" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H65" s="31">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I65" s="31">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J65" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>20</x:v>
@@ -7930,25 +7945,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G66" s="29" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G66" s="29" t="s">
+      <x:c r="H66" s="31">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I66" s="31">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J66" s="30" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="H66" s="31">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I66" s="31">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J66" s="30" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>20</x:v>
@@ -7968,25 +7983,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G67" s="29" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G67" s="29" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>20</x:v>
@@ -8006,25 +8021,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G68" s="29" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H68" s="31">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I68" s="31">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J68" s="30" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="G68" s="29" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H68" s="31">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I68" s="31">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J68" s="30" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>20</x:v>
@@ -8044,25 +8059,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G69" s="29" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H69" s="31">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I69" s="31">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J69" s="30" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="G69" s="29" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H69" s="31">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I69" s="31">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J69" s="30" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>20</x:v>
@@ -8082,25 +8097,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
-        <x:v>210</x:v>
-      </x:c>
       <x:c r="H70" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>20</x:v>
@@ -8120,25 +8135,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H71" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I71" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J71" s="30" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="G71" s="29" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H71" s="31">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I71" s="31">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J71" s="30" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>20</x:v>
@@ -8158,25 +8173,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H72" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I72" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J72" s="30" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="G72" s="29" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H72" s="31">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I72" s="31">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J72" s="30" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>20</x:v>
@@ -8196,25 +8211,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G73" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G73" s="29" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="H73" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>20</x:v>
@@ -8234,25 +8249,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G74" s="29" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H74" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I74" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J74" s="30" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="G74" s="29" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H74" s="31">
-        <x:v>46122.3885020718</x:v>
-      </x:c>
-      <x:c r="I74" s="31">
-        <x:v>46122.3892655903</x:v>
-      </x:c>
-      <x:c r="J74" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>20</x:v>
@@ -8272,25 +8287,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G75" s="29" t="s">
+      <x:c r="H75" s="31">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I75" s="31">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J75" s="30" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="H75" s="31">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I75" s="31">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J75" s="30" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>20</x:v>
@@ -8310,25 +8325,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G76" s="29" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="G76" s="29" t="s">
+      <x:c r="H76" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I76" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J76" s="30" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="H76" s="31">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I76" s="31">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J76" s="30" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>20</x:v>
@@ -8348,25 +8363,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="G77" s="29" t="s">
+      <x:c r="H77" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I77" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="H77" s="31">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I77" s="31">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J77" s="30" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>20</x:v>
@@ -8386,25 +8401,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
+      <x:c r="H78" s="31">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>20</x:v>
@@ -8424,25 +8439,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>235</x:v>
-      </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>20</x:v>
@@ -8462,25 +8477,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
+      <x:c r="H80" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I80" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J80" s="30" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="H80" s="31">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I80" s="31">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J80" s="30" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>20</x:v>
@@ -8500,25 +8515,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>241</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>20</x:v>
@@ -8538,16 +8553,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G82" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
         <x:v>29</x:v>
@@ -8556,7 +8571,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>20</x:v>
@@ -8576,25 +8591,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G83" s="29" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>246</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>20</x:v>
@@ -8614,10 +8629,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H84" s="31">
         <x:v>46122.6795081481</x:v>
@@ -8652,25 +8667,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>20</x:v>
@@ -8690,16 +8705,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
         <x:v>29</x:v>
@@ -8708,7 +8723,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>20</x:v>
@@ -8728,25 +8743,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>20</x:v>
@@ -8766,25 +8781,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>20</x:v>
@@ -8804,25 +8819,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>20</x:v>
@@ -8842,25 +8857,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H90" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="G90" s="29" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H90" s="31">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I90" s="31">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J90" s="30" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>20</x:v>
@@ -8868,10 +8883,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>15</x:v>
@@ -8880,25 +8895,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G91" s="29" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>20</x:v>
@@ -8906,10 +8921,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>15</x:v>
@@ -8918,25 +8933,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G92" s="29" t="s">
-        <x:v>270</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>20</x:v>
@@ -8944,10 +8959,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>15</x:v>
@@ -8956,25 +8971,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>274</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>20</x:v>
@@ -8982,10 +8997,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>15</x:v>
@@ -8994,25 +9009,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G94" s="29" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="H94" s="31">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I94" s="31">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J94" s="30" t="s">
-        <x:v>278</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>20</x:v>
@@ -9020,10 +9035,10 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>15</x:v>
@@ -9032,25 +9047,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
-        <x:v>280</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G95" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>20</x:v>
@@ -9058,37 +9073,37 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>45</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E96" s="29" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
+      <x:c r="H96" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46132.3798789699</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46132.3799006944</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>284</x:v>
-      </x:c>
       <x:c r="K96" s="32" t="n">
-        <x:v>3031</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46133.1738098148</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>20</x:v>
@@ -9096,10 +9111,10 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>15</x:v>
@@ -9108,25 +9123,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G97" s="29" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="G97" s="29" t="s">
-        <x:v>287</x:v>
-      </x:c>
       <x:c r="H97" s="31">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>20</x:v>
@@ -9134,37 +9149,37 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>285</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E98" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G98" s="29" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="G98" s="29" t="s">
+      <x:c r="H98" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I98" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J98" s="30" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="H98" s="31">
-        <x:v>46118.439490081</x:v>
-      </x:c>
-      <x:c r="I98" s="31">
-        <x:v>46118.4395309375</x:v>
-      </x:c>
-      <x:c r="J98" s="30" t="s">
-        <x:v>290</x:v>
-      </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>20</x:v>
@@ -9172,10 +9187,10 @@
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
       <x:c r="B99" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D99" s="30" t="s">
         <x:v>15</x:v>
@@ -9190,19 +9205,19 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="H99" s="31">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I99" s="31">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J99" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K99" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>20</x:v>
@@ -9210,37 +9225,37 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>293</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>285</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D100" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E100" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G100" s="29" t="s">
         <x:v>294</x:v>
       </x:c>
       <x:c r="H100" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46118.439490081</x:v>
       </x:c>
       <x:c r="I100" s="31">
-        <x:v>46023</x:v>
+        <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J100" s="30" t="s">
         <x:v>295</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>20</x:v>
@@ -9248,35 +9263,37 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>296</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="D101" s="30" t="s"/>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D101" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E101" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F101" s="29" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="G101" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H101" s="31">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I101" s="31">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J101" s="30" t="s">
-        <x:v>300</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>20</x:v>
@@ -9284,10 +9301,10 @@
     </x:row>
     <x:row r="102" spans="1:28" ht="30" customHeight="1">
       <x:c r="B102" s="29" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C102" s="29" t="s">
-        <x:v>302</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D102" s="30" t="s">
         <x:v>40</x:v>
@@ -9296,25 +9313,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F102" s="29" t="s">
-        <x:v>303</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G102" s="29" t="s">
-        <x:v>304</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="H102" s="31">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46132.3879904745</x:v>
       </x:c>
       <x:c r="I102" s="31">
         <x:v>46023</x:v>
       </x:c>
       <x:c r="J102" s="30" t="s">
-        <x:v>305</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="K102" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L102" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M102" s="29" t="s">
         <x:v>20</x:v>
@@ -9325,151 +9342,223 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="C103" s="29" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D103" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="D103" s="30" t="s"/>
       <x:c r="E103" s="29" t="s">
-        <x:v>307</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F103" s="29" t="s">
-        <x:v>308</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="G103" s="29" t="s">
-        <x:v>309</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H103" s="31">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I103" s="31">
-        <x:v>46215</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J103" s="30" t="s">
-        <x:v>310</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="K103" s="32" t="n">
-        <x:v>3006</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L103" s="33">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M103" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B106" s="17" t="s">
+    <x:row r="104" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B104" s="29" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C104" s="29" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D104" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E104" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F104" s="29" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G104" s="29" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H104" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I104" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J104" s="30" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="K104" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L104" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M104" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B105" s="29" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C105" s="29" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="D105" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E105" s="29" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F105" s="29" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="G105" s="29" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H105" s="31">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I105" s="31">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J105" s="30" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="K105" s="32" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L105" s="33">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M105" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B108" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C106" s="18" t="s"/>
-      <x:c r="D106" s="18" t="s"/>
-      <x:c r="E106" s="19" t="s"/>
-      <x:c r="F106" s="19" t="s"/>
-    </x:row>
-    <x:row r="107" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B107" s="20" t="s">
+      <x:c r="C108" s="18" t="s"/>
+      <x:c r="D108" s="18" t="s"/>
+      <x:c r="E108" s="19" t="s"/>
+      <x:c r="F108" s="19" t="s"/>
+    </x:row>
+    <x:row r="109" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B109" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C107" s="21" t="s"/>
-      <x:c r="D107" s="21" t="s"/>
-      <x:c r="E107" s="21" t="s"/>
-      <x:c r="F107" s="22" t="s">
+      <x:c r="C109" s="21" t="s"/>
+      <x:c r="D109" s="21" t="s"/>
+      <x:c r="E109" s="21" t="s"/>
+      <x:c r="F109" s="22" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B108" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C108" s="24" t="s"/>
-      <x:c r="D108" s="24" t="s"/>
-      <x:c r="E108" s="24" t="s"/>
-      <x:c r="F108" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B109" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C109" s="24" t="s"/>
-      <x:c r="D109" s="24" t="s"/>
-      <x:c r="E109" s="24" t="s"/>
-      <x:c r="F109" s="25" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
       <x:c r="B110" s="23" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s"/>
       <x:c r="D110" s="24" t="s"/>
       <x:c r="E110" s="24" t="s"/>
       <x:c r="F110" s="25" t="n">
-        <x:v>80</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>263</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
       <x:c r="E111" s="24" t="s"/>
       <x:c r="F111" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>293</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
       <x:c r="E112" s="24" t="s"/>
       <x:c r="F112" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:28" ht="18" customHeight="1">
       <x:c r="B113" s="23" t="s">
-        <x:v>296</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C113" s="24" t="s"/>
       <x:c r="D113" s="24" t="s"/>
       <x:c r="E113" s="24" t="s"/>
       <x:c r="F113" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:28" ht="18" customHeight="1">
       <x:c r="B114" s="23" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C114" s="24" t="s"/>
       <x:c r="D114" s="24" t="s"/>
       <x:c r="E114" s="24" t="s"/>
       <x:c r="F114" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B115" s="23" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C115" s="24" t="s"/>
+      <x:c r="D115" s="24" t="s"/>
+      <x:c r="E115" s="24" t="s"/>
+      <x:c r="F115" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B116" s="23" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C116" s="24" t="s"/>
+      <x:c r="D116" s="24" t="s"/>
+      <x:c r="E116" s="24" t="s"/>
+      <x:c r="F116" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B115" s="26" t="s">
+    <x:row r="117" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B117" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C115" s="27" t="s"/>
-      <x:c r="D115" s="27" t="s"/>
-      <x:c r="E115" s="27" t="s"/>
-      <x:c r="F115" s="28" t="n">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C117" s="27" t="s"/>
+      <x:c r="D117" s="27" t="s"/>
+      <x:c r="E117" s="27" t="s"/>
+      <x:c r="F117" s="28" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
     <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10351,9 +10440,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B106:F106"/>
-    <x:mergeCell ref="B107:E107"/>
-    <x:mergeCell ref="B108:E108"/>
+    <x:mergeCell ref="B108:F108"/>
     <x:mergeCell ref="B109:E109"/>
     <x:mergeCell ref="B110:E110"/>
     <x:mergeCell ref="B111:E111"/>
@@ -10361,6 +10448,8 @@
     <x:mergeCell ref="B113:E113"/>
     <x:mergeCell ref="B114:E114"/>
     <x:mergeCell ref="B115:E115"/>
+    <x:mergeCell ref="B116:E116"/>
+    <x:mergeCell ref="B117:E117"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="319">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -249,43 +249,58 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08729</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1347-280</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
@@ -411,150 +426,150 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
   </x:si>
   <x:si>
@@ -576,12 +591,6 @@
     <x:t>61-4-2026-1283-909</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08369</x:t>
   </x:si>
   <x:si>
@@ -651,6 +660,15 @@
     <x:t>zcasdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
   </x:si>
   <x:si>
@@ -690,13 +708,10 @@
     <x:t>zsdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08187</x:t>
@@ -708,6 +723,105 @@
     <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -717,102 +831,6 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
   </x:si>
   <x:si>
@@ -822,15 +840,6 @@
     <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -900,19 +909,19 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08045-26</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1233-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08034-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1223-617</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123431</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -6127,19 +6136,19 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46134.4519824769</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46134.4543351736</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46134.4551470833</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>20</x:v>
@@ -6159,25 +6168,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G19" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>20</x:v>
@@ -6197,25 +6206,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>20</x:v>
@@ -6235,10 +6244,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H21" s="31">
         <x:v>46133.0575652778</x:v>
@@ -6247,7 +6256,7 @@
         <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>361</x:v>
@@ -6273,10 +6282,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="31">
         <x:v>46133.5419909606</x:v>
@@ -6302,34 +6311,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D23" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>20</x:v>
@@ -6355,19 +6364,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
@@ -6393,19 +6402,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>20</x:v>
@@ -6431,19 +6440,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>20</x:v>
@@ -6469,10 +6478,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>99</x:v>
@@ -6481,7 +6490,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
@@ -6507,10 +6516,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
         <x:v>29</x:v>
@@ -6519,7 +6528,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>20</x:v>
@@ -6545,10 +6554,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>104</x:v>
@@ -6557,7 +6566,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>20</x:v>
@@ -6583,19 +6592,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
@@ -6615,25 +6624,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
+      <x:c r="H31" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I31" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J31" s="30" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="H31" s="31">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I31" s="31">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J31" s="30" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>20</x:v>
@@ -6653,25 +6662,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G32" s="29" t="s">
+      <x:c r="H32" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I32" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J32" s="30" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="H32" s="31">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I32" s="31">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J32" s="30" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>20</x:v>
@@ -6691,25 +6700,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G33" s="29" t="s">
+      <x:c r="H33" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I33" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J33" s="30" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="H33" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I33" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J33" s="30" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>20</x:v>
@@ -6729,25 +6738,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G34" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G34" s="29" t="s">
+      <x:c r="H34" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I34" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H34" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I34" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J34" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
@@ -6773,10 +6782,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
         <x:v>121</x:v>
@@ -6785,7 +6794,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
@@ -6811,19 +6820,19 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>20</x:v>
@@ -6849,19 +6858,19 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
@@ -6881,25 +6890,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>20</x:v>
@@ -6919,25 +6928,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>20</x:v>
@@ -6957,25 +6966,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>20</x:v>
@@ -6995,25 +7004,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>20</x:v>
@@ -7039,19 +7048,19 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>20</x:v>
@@ -7071,25 +7080,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G43" s="29" t="s">
+      <x:c r="H43" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I43" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="H43" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I43" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J43" s="30" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>20</x:v>
@@ -7109,25 +7118,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
+      <x:c r="H44" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>20</x:v>
@@ -7147,25 +7156,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
+      <x:c r="H45" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>20</x:v>
@@ -7185,25 +7194,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G46" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G46" s="29" t="s">
+      <x:c r="H46" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I46" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J46" s="30" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="H46" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I46" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J46" s="30" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>20</x:v>
@@ -7223,25 +7232,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G47" s="29" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G47" s="29" t="s">
+      <x:c r="H47" s="31">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I47" s="31">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="H47" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I47" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J47" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>20</x:v>
@@ -7267,10 +7276,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
         <x:v>154</x:v>
@@ -7279,7 +7288,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
@@ -7305,19 +7314,19 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
@@ -7337,25 +7346,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G50" s="29" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G50" s="29" t="s">
+      <x:c r="H50" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I50" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="H50" s="31">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I50" s="31">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J50" s="30" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>20</x:v>
@@ -7375,25 +7384,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G51" s="29" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G51" s="29" t="s">
+      <x:c r="H51" s="31">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I51" s="31">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J51" s="30" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="H51" s="31">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I51" s="31">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J51" s="30" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>20</x:v>
@@ -7413,25 +7422,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F52" s="29" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G52" s="29" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="G52" s="29" t="s">
+      <x:c r="H52" s="31">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I52" s="31">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J52" s="30" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="H52" s="31">
-        <x:v>46119.5439653357</x:v>
-      </x:c>
-      <x:c r="I52" s="31">
-        <x:v>46119.5452984143</x:v>
-      </x:c>
-      <x:c r="J52" s="30" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
@@ -7451,25 +7460,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G53" s="29" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G53" s="29" t="s">
+      <x:c r="H53" s="31">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I53" s="31">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J53" s="30" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="H53" s="31">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I53" s="31">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J53" s="30" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>20</x:v>
@@ -7495,19 +7504,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>20</x:v>
@@ -7527,25 +7536,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>20</x:v>
@@ -7571,10 +7580,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
         <x:v>52</x:v>
@@ -7583,7 +7592,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>20</x:v>
@@ -7609,10 +7618,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
         <x:v>178</x:v>
@@ -7621,7 +7630,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>20</x:v>
@@ -7647,19 +7656,19 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>20</x:v>
@@ -7685,19 +7694,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>20</x:v>
@@ -7717,25 +7726,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>20</x:v>
@@ -7755,25 +7764,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>20</x:v>
@@ -7793,16 +7802,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
         <x:v>29</x:v>
@@ -7811,7 +7820,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>20</x:v>
@@ -7831,25 +7840,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>20</x:v>
@@ -7869,25 +7878,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>20</x:v>
@@ -7913,10 +7922,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
         <x:v>196</x:v>
@@ -7925,7 +7934,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>20</x:v>
@@ -7951,10 +7960,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>199</x:v>
@@ -7963,7 +7972,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>20</x:v>
@@ -7989,19 +7998,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>20</x:v>
@@ -8021,25 +8030,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>20</x:v>
@@ -8065,10 +8074,10 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
         <x:v>207</x:v>
@@ -8077,7 +8086,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>20</x:v>
@@ -8103,19 +8112,19 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>20</x:v>
@@ -8135,25 +8144,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G71" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>20</x:v>
@@ -8173,25 +8182,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>20</x:v>
@@ -8217,19 +8226,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>20</x:v>
@@ -8249,25 +8258,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>20</x:v>
@@ -8287,25 +8296,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>20</x:v>
@@ -8331,10 +8340,10 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
         <x:v>226</x:v>
@@ -8343,7 +8352,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>20</x:v>
@@ -8369,19 +8378,19 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>229</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>20</x:v>
@@ -8401,25 +8410,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
+      <x:c r="H78" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46122.5587807523</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46122.5602428125</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>232</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>20</x:v>
@@ -8439,25 +8448,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
+      <x:c r="H79" s="31">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>20</x:v>
@@ -8483,19 +8492,19 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>237</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>20</x:v>
@@ -8515,10 +8524,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="H81" s="31">
         <x:v>46124.1449755903</x:v>
@@ -8527,7 +8536,7 @@
         <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
@@ -8553,10 +8562,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="H82" s="31">
         <x:v>46122.5945434491</x:v>
@@ -8591,10 +8600,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="G83" s="29" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="H83" s="31">
         <x:v>46122.6182774306</x:v>
@@ -8603,7 +8612,7 @@
         <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
@@ -8629,10 +8638,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="H84" s="31">
         <x:v>46122.6795081481</x:v>
@@ -8667,25 +8676,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G85" s="29" t="s">
+      <x:c r="H85" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46122.3974322338</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46122.3980999421</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>20</x:v>
@@ -8711,19 +8720,19 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>20</x:v>
@@ -8743,25 +8752,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>20</x:v>
@@ -8781,25 +8790,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>20</x:v>
@@ -8819,25 +8828,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>20</x:v>
@@ -8863,10 +8872,10 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
         <x:v>261</x:v>
@@ -8875,7 +8884,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>20</x:v>
@@ -8901,10 +8910,10 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
         <x:v>264</x:v>
@@ -8913,7 +8922,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>20</x:v>
@@ -8939,10 +8948,10 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
         <x:v>267</x:v>
@@ -8951,7 +8960,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>20</x:v>
@@ -8959,10 +8968,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>15</x:v>
@@ -8971,25 +8980,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>272</x:v>
-      </x:c>
       <x:c r="K93" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>20</x:v>
@@ -8997,10 +9006,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>15</x:v>
@@ -9009,25 +9018,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="G94" s="29" t="s">
+      <x:c r="H94" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I94" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J94" s="30" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="H94" s="31">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I94" s="31">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J94" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>20</x:v>
@@ -9035,7 +9044,7 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
         <x:v>276</x:v>
@@ -9053,19 +9062,19 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>279</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>20</x:v>
@@ -9073,10 +9082,10 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>15</x:v>
@@ -9085,25 +9094,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
+      <x:c r="H96" s="31">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>20</x:v>
@@ -9111,10 +9120,10 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>15</x:v>
@@ -9123,25 +9132,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G97" s="29" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G97" s="29" t="s">
+      <x:c r="H97" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I97" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J97" s="30" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="H97" s="31">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I97" s="31">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J97" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>20</x:v>
@@ -9149,37 +9158,37 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>45</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E98" s="29" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="G98" s="29" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="H98" s="31">
-        <x:v>46132.3798789699</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I98" s="31">
-        <x:v>46132.3799006944</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J98" s="30" t="s">
-        <x:v>289</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>3031</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46133.1738098148</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>20</x:v>
@@ -9187,37 +9196,37 @@
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
       <x:c r="B99" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>290</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D99" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E99" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="G99" s="29" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="G99" s="29" t="s">
+      <x:c r="H99" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I99" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J99" s="30" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="H99" s="31">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I99" s="31">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J99" s="30" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>20</x:v>
@@ -9225,10 +9234,10 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D100" s="30" t="s">
         <x:v>15</x:v>
@@ -9237,10 +9246,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G100" s="29" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H100" s="31">
         <x:v>46118.439490081</x:v>
@@ -9249,7 +9258,7 @@
         <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J100" s="30" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
         <x:v>3530</x:v>
@@ -9263,10 +9272,10 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D101" s="30" t="s">
         <x:v>15</x:v>
@@ -9275,25 +9284,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F101" s="29" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G101" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="H101" s="31">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I101" s="31">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J101" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>20</x:v>
@@ -9301,37 +9310,37 @@
     </x:row>
     <x:row r="102" spans="1:28" ht="30" customHeight="1">
       <x:c r="B102" s="29" t="s">
-        <x:v>298</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C102" s="29" t="s">
-        <x:v>290</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D102" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E102" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F102" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="G102" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H102" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I102" s="31">
-        <x:v>46023</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J102" s="30" t="s">
-        <x:v>300</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K102" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L102" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M102" s="29" t="s">
         <x:v>20</x:v>
@@ -9342,32 +9351,34 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="C103" s="29" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="D103" s="30" t="s"/>
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D103" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="E103" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F103" s="29" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G103" s="29" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H103" s="31">
+        <x:v>46132.3879904745</x:v>
+      </x:c>
+      <x:c r="I103" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J103" s="30" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="G103" s="29" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H103" s="31">
-        <x:v>46124.1588481829</x:v>
-      </x:c>
-      <x:c r="I103" s="31">
-        <x:v>46124.1588689236</x:v>
-      </x:c>
-      <x:c r="J103" s="30" t="s">
-        <x:v>305</x:v>
-      </x:c>
       <x:c r="K103" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L103" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M103" s="29" t="s">
         <x:v>20</x:v>
@@ -9375,37 +9386,35 @@
     </x:row>
     <x:row r="104" spans="1:28" ht="30" customHeight="1">
       <x:c r="B104" s="29" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C104" s="29" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D104" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="D104" s="30" t="s"/>
       <x:c r="E104" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F104" s="29" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G104" s="29" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H104" s="31">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I104" s="31">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J104" s="30" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="G104" s="29" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="H104" s="31">
-        <x:v>46124.1607868981</x:v>
-      </x:c>
-      <x:c r="I104" s="31">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="J104" s="30" t="s">
-        <x:v>310</x:v>
-      </x:c>
       <x:c r="K104" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L104" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M104" s="29" t="s">
         <x:v>20</x:v>
@@ -9413,117 +9422,144 @@
     </x:row>
     <x:row r="105" spans="1:28" ht="30" customHeight="1">
       <x:c r="B105" s="29" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C105" s="29" t="s">
-        <x:v>311</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D105" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E105" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F105" s="29" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="G105" s="29" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="F105" s="29" t="s">
+      <x:c r="H105" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I105" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J105" s="30" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="G105" s="29" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="H105" s="31">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I105" s="31">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J105" s="30" t="s">
-        <x:v>315</x:v>
-      </x:c>
       <x:c r="K105" s="32" t="n">
-        <x:v>3006</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="L105" s="33">
-        <x:v>46125.0821987731</x:v>
+        <x:v>46124.1624131829</x:v>
       </x:c>
       <x:c r="M105" s="29" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B106" s="29" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C106" s="29" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D106" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E106" s="29" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="F106" s="29" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="G106" s="29" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="H106" s="31">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I106" s="31">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J106" s="30" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="K106" s="32" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="L106" s="33">
+        <x:v>46125.0821987731</x:v>
+      </x:c>
+      <x:c r="M106" s="29" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B108" s="17" t="s">
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B109" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C108" s="18" t="s"/>
-      <x:c r="D108" s="18" t="s"/>
-      <x:c r="E108" s="19" t="s"/>
-      <x:c r="F108" s="19" t="s"/>
-    </x:row>
-    <x:row r="109" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B109" s="20" t="s">
+      <x:c r="C109" s="18" t="s"/>
+      <x:c r="D109" s="18" t="s"/>
+      <x:c r="E109" s="19" t="s"/>
+      <x:c r="F109" s="19" t="s"/>
+    </x:row>
+    <x:row r="110" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B110" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C109" s="21" t="s"/>
-      <x:c r="D109" s="21" t="s"/>
-      <x:c r="E109" s="21" t="s"/>
-      <x:c r="F109" s="22" t="s">
+      <x:c r="C110" s="21" t="s"/>
+      <x:c r="D110" s="21" t="s"/>
+      <x:c r="E110" s="21" t="s"/>
+      <x:c r="F110" s="22" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B110" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C110" s="24" t="s"/>
-      <x:c r="D110" s="24" t="s"/>
-      <x:c r="E110" s="24" t="s"/>
-      <x:c r="F110" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
       <x:c r="E111" s="24" t="s"/>
       <x:c r="F111" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
       <x:c r="E112" s="24" t="s"/>
       <x:c r="F112" s="25" t="n">
-        <x:v>82</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:28" ht="18" customHeight="1">
       <x:c r="B113" s="23" t="s">
-        <x:v>268</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C113" s="24" t="s"/>
       <x:c r="D113" s="24" t="s"/>
       <x:c r="E113" s="24" t="s"/>
       <x:c r="F113" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:28" ht="18" customHeight="1">
       <x:c r="B114" s="23" t="s">
-        <x:v>298</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C114" s="24" t="s"/>
       <x:c r="D114" s="24" t="s"/>
       <x:c r="E114" s="24" t="s"/>
       <x:c r="F114" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:28" ht="18" customHeight="1">
@@ -9539,27 +9575,37 @@
     </x:row>
     <x:row r="116" spans="1:28" ht="18" customHeight="1">
       <x:c r="B116" s="23" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C116" s="24" t="s"/>
       <x:c r="D116" s="24" t="s"/>
       <x:c r="E116" s="24" t="s"/>
       <x:c r="F116" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B117" s="23" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C117" s="24" t="s"/>
+      <x:c r="D117" s="24" t="s"/>
+      <x:c r="E117" s="24" t="s"/>
+      <x:c r="F117" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B117" s="26" t="s">
+    <x:row r="118" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B118" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C117" s="27" t="s"/>
-      <x:c r="D117" s="27" t="s"/>
-      <x:c r="E117" s="27" t="s"/>
-      <x:c r="F117" s="28" t="n">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C118" s="27" t="s"/>
+      <x:c r="D118" s="27" t="s"/>
+      <x:c r="E118" s="27" t="s"/>
+      <x:c r="F118" s="28" t="n">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
     <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10440,8 +10486,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B108:F108"/>
-    <x:mergeCell ref="B109:E109"/>
+    <x:mergeCell ref="B109:F109"/>
     <x:mergeCell ref="B110:E110"/>
     <x:mergeCell ref="B111:E111"/>
     <x:mergeCell ref="B112:E112"/>
@@ -10450,6 +10495,7 @@
     <x:mergeCell ref="B115:E115"/>
     <x:mergeCell ref="B116:E116"/>
     <x:mergeCell ref="B117:E117"/>
+    <x:mergeCell ref="B118:E118"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="319">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -258,6 +258,45 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1354-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08756</x:t>
   </x:si>
   <x:si>
@@ -267,36 +306,6 @@
     <x:t>1555</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08344</x:t>
   </x:si>
   <x:si>
@@ -357,6 +366,60 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08145</x:t>
   </x:si>
   <x:si>
@@ -366,46 +429,163 @@
     <x:t>sdf</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
@@ -414,177 +594,6 @@
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08169</x:t>
   </x:si>
   <x:si>
@@ -708,127 +717,127 @@
     <x:t>zsdasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
@@ -6174,19 +6183,19 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46134.9871842824</x:v>
+        <x:v>46139.4236006019</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46135.0270460764</x:v>
+        <x:v>46139.424377581</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46135.0715283333</x:v>
+        <x:v>46139.4248658449</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>20</x:v>
@@ -6349,13 +6358,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C24" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D24" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E24" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
         <x:v>90</x:v>
@@ -6364,19 +6373,19 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>20</x:v>
@@ -6396,25 +6405,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>20</x:v>
@@ -6440,19 +6449,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>20</x:v>
@@ -6472,25 +6481,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H27" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="G27" s="29" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>20</x:v>
@@ -6516,19 +6525,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>20</x:v>
@@ -6548,25 +6557,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G29" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>20</x:v>
@@ -6592,19 +6601,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>20</x:v>
@@ -6624,25 +6633,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G31" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>20</x:v>
@@ -6668,10 +6677,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>112</x:v>
@@ -6680,7 +6689,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>20</x:v>
@@ -6744,19 +6753,19 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>20</x:v>
@@ -6776,25 +6785,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G35" s="29" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G35" s="29" t="s">
+      <x:c r="H35" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I35" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="H35" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I35" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J35" s="30" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>20</x:v>
@@ -6814,25 +6823,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G36" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G36" s="29" t="s">
+      <x:c r="H36" s="31">
+        <x:v>46121.5183984954</x:v>
+      </x:c>
+      <x:c r="I36" s="31">
+        <x:v>46122.2061737153</x:v>
+      </x:c>
+      <x:c r="J36" s="30" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="H36" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I36" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J36" s="30" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>20</x:v>
@@ -6858,19 +6867,19 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>20</x:v>
@@ -6890,25 +6899,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G38" s="29" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G38" s="29" t="s">
+      <x:c r="H38" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I38" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J38" s="30" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="H38" s="31">
-        <x:v>46122.3569147569</x:v>
-      </x:c>
-      <x:c r="I38" s="31">
-        <x:v>46122.3577305324</x:v>
-      </x:c>
-      <x:c r="J38" s="30" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>20</x:v>
@@ -6934,19 +6943,19 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>20</x:v>
@@ -6972,19 +6981,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>20</x:v>
@@ -7004,25 +7013,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>20</x:v>
@@ -7042,25 +7051,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G42" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>20</x:v>
@@ -7080,25 +7089,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G43" s="29" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>20</x:v>
@@ -7124,10 +7133,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>142</x:v>
@@ -7136,7 +7145,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>20</x:v>
@@ -7162,10 +7171,10 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
         <x:v>145</x:v>
@@ -7174,7 +7183,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>20</x:v>
@@ -7200,10 +7209,10 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
         <x:v>148</x:v>
@@ -7212,7 +7221,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>20</x:v>
@@ -7238,10 +7247,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
         <x:v>151</x:v>
@@ -7250,7 +7259,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>20</x:v>
@@ -7276,10 +7285,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
         <x:v>154</x:v>
@@ -7288,7 +7297,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>20</x:v>
@@ -7314,19 +7323,19 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>20</x:v>
@@ -7346,25 +7355,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G50" s="29" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>20</x:v>
@@ -7390,10 +7399,10 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
         <x:v>162</x:v>
@@ -7402,7 +7411,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>20</x:v>
@@ -7428,10 +7437,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
         <x:v>165</x:v>
@@ -7440,7 +7449,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>20</x:v>
@@ -7466,10 +7475,10 @@
         <x:v>167</x:v